--- a/panel.xlsx
+++ b/panel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E421"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,6965 +445,6683 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>10.107</v>
+      </c>
+      <c r="B2" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1862702164434696</v>
+      </c>
+      <c r="D2" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="E2" t="n">
         <v>9.975</v>
       </c>
-      <c r="B2" t="n">
-        <v>132.4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.1800520311772192</v>
-      </c>
-      <c r="D2" t="n">
-        <v>84.45999999999999</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>9.962</v>
+      </c>
+      <c r="B3" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1925092185951393</v>
+      </c>
+      <c r="D3" t="n">
+        <v>82.54000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>10.107</v>
-      </c>
-      <c r="B3" t="n">
-        <v>129.3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.1862702164434696</v>
-      </c>
-      <c r="D3" t="n">
-        <v>84.36</v>
-      </c>
-      <c r="E3" t="n">
-        <v>9.975</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>9.835000000000001</v>
+      </c>
+      <c r="B4" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1980113905493617</v>
+      </c>
+      <c r="D4" t="n">
+        <v>81.94</v>
+      </c>
+      <c r="E4" t="n">
         <v>9.962</v>
-      </c>
-      <c r="B4" t="n">
-        <v>128.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1925092185951393</v>
-      </c>
-      <c r="D4" t="n">
-        <v>82.54000000000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>10.107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>10.032</v>
+      </c>
+      <c r="B5" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2009143587662127</v>
+      </c>
+      <c r="D5" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="E5" t="n">
         <v>9.835000000000001</v>
-      </c>
-      <c r="B5" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1980113905493617</v>
-      </c>
-      <c r="D5" t="n">
-        <v>81.94</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9.962</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="B6" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2040064922037118</v>
+      </c>
+      <c r="D6" t="n">
+        <v>85.78</v>
+      </c>
+      <c r="E6" t="n">
         <v>10.032</v>
-      </c>
-      <c r="B6" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.2009143587662127</v>
-      </c>
-      <c r="D6" t="n">
-        <v>83.48</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9.835000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>10.831</v>
+      </c>
+      <c r="B7" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2066170619228758</v>
+      </c>
+      <c r="D7" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="E7" t="n">
         <v>10.97</v>
-      </c>
-      <c r="B7" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2040064922037118</v>
-      </c>
-      <c r="D7" t="n">
-        <v>85.78</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10.032</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>10.521</v>
+      </c>
+      <c r="B8" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.206631704132772</v>
+      </c>
+      <c r="D8" t="n">
+        <v>90.64</v>
+      </c>
+      <c r="E8" t="n">
         <v>10.831</v>
-      </c>
-      <c r="B8" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.2066170619228758</v>
-      </c>
-      <c r="D8" t="n">
-        <v>89.27</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>10.594</v>
+      </c>
+      <c r="B9" t="n">
+        <v>134</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2066957059751344</v>
+      </c>
+      <c r="D9" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="E9" t="n">
         <v>10.521</v>
-      </c>
-      <c r="B9" t="n">
-        <v>132.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.206631704132772</v>
-      </c>
-      <c r="D9" t="n">
-        <v>90.64</v>
-      </c>
-      <c r="E9" t="n">
-        <v>10.831</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>10.743</v>
+      </c>
+      <c r="B10" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2075804446554188</v>
+      </c>
+      <c r="D10" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="E10" t="n">
         <v>10.594</v>
-      </c>
-      <c r="B10" t="n">
-        <v>134</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.2066957059751344</v>
-      </c>
-      <c r="D10" t="n">
-        <v>90.81</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10.521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>10.768</v>
+      </c>
+      <c r="B11" t="n">
+        <v>137.7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.208658404932194</v>
+      </c>
+      <c r="D11" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="E11" t="n">
         <v>10.743</v>
-      </c>
-      <c r="B11" t="n">
-        <v>135.6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2075804446554188</v>
-      </c>
-      <c r="D11" t="n">
-        <v>94.69</v>
-      </c>
-      <c r="E11" t="n">
-        <v>10.594</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>10.923</v>
+      </c>
+      <c r="B12" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2104584896460591</v>
+      </c>
+      <c r="D12" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="E12" t="n">
         <v>10.768</v>
-      </c>
-      <c r="B12" t="n">
-        <v>137.7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.208658404932194</v>
-      </c>
-      <c r="D12" t="n">
-        <v>96.62</v>
-      </c>
-      <c r="E12" t="n">
-        <v>10.743</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>10.971</v>
+      </c>
+      <c r="B13" t="n">
+        <v>137</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2105267295371706</v>
+      </c>
+      <c r="D13" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="E13" t="n">
         <v>10.923</v>
-      </c>
-      <c r="B13" t="n">
-        <v>136.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.2104584896460591</v>
-      </c>
-      <c r="D13" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10.768</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10.971</v>
+        <v>11.051</v>
       </c>
       <c r="B14" t="n">
         <v>137</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2105267295371706</v>
+        <v>0.2121831587644033</v>
       </c>
       <c r="D14" t="n">
-        <v>95.16</v>
+        <v>96.42</v>
       </c>
       <c r="E14" t="n">
-        <v>10.923</v>
+        <v>10.971</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>11.184</v>
+      </c>
+      <c r="B15" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2139051589439706</v>
+      </c>
+      <c r="D15" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="E15" t="n">
         <v>11.051</v>
-      </c>
-      <c r="B15" t="n">
-        <v>137</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.2121831587644033</v>
-      </c>
-      <c r="D15" t="n">
-        <v>96.42</v>
-      </c>
-      <c r="E15" t="n">
-        <v>10.971</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>11.428</v>
+      </c>
+      <c r="B16" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2154143764287431</v>
+      </c>
+      <c r="D16" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="E16" t="n">
         <v>11.184</v>
-      </c>
-      <c r="B16" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.2139051589439706</v>
-      </c>
-      <c r="D16" t="n">
-        <v>97.37</v>
-      </c>
-      <c r="E16" t="n">
-        <v>11.051</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>12.468</v>
+      </c>
+      <c r="B17" t="n">
+        <v>137.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2175231145067165</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100.87</v>
+      </c>
+      <c r="E17" t="n">
         <v>11.428</v>
-      </c>
-      <c r="B17" t="n">
-        <v>135.8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.2154143764287431</v>
-      </c>
-      <c r="D17" t="n">
-        <v>98.98999999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11.184</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>12.724</v>
+      </c>
+      <c r="B18" t="n">
+        <v>135</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2197297719725461</v>
+      </c>
+      <c r="D18" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="E18" t="n">
         <v>12.468</v>
-      </c>
-      <c r="B18" t="n">
-        <v>137.7</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.2175231145067165</v>
-      </c>
-      <c r="D18" t="n">
-        <v>100.87</v>
-      </c>
-      <c r="E18" t="n">
-        <v>11.428</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>12.447</v>
+      </c>
+      <c r="B19" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.2214937051405092</v>
+      </c>
+      <c r="D19" t="n">
+        <v>103.02</v>
+      </c>
+      <c r="E19" t="n">
         <v>12.724</v>
-      </c>
-      <c r="B19" t="n">
-        <v>135</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.2197297719725461</v>
-      </c>
-      <c r="D19" t="n">
-        <v>101.77</v>
-      </c>
-      <c r="E19" t="n">
-        <v>12.468</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>11.744</v>
+      </c>
+      <c r="B20" t="n">
+        <v>132</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2224559367354327</v>
+      </c>
+      <c r="D20" t="n">
+        <v>106.07</v>
+      </c>
+      <c r="E20" t="n">
         <v>12.447</v>
-      </c>
-      <c r="B20" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.2214937051405092</v>
-      </c>
-      <c r="D20" t="n">
-        <v>103.02</v>
-      </c>
-      <c r="E20" t="n">
-        <v>12.724</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>12.267</v>
+      </c>
+      <c r="B21" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.2241730602019303</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
         <v>11.744</v>
-      </c>
-      <c r="B21" t="n">
-        <v>132</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.2224559367354327</v>
-      </c>
-      <c r="D21" t="n">
-        <v>106.07</v>
-      </c>
-      <c r="E21" t="n">
-        <v>12.447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12.267</v>
+        <v>9.718</v>
       </c>
       <c r="B22" t="n">
-        <v>129.8</v>
+        <v>138.8</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2241730602019303</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>0.1594790570684688</v>
+      </c>
+      <c r="D22" t="n">
+        <v>136.19</v>
+      </c>
       <c r="E22" t="n">
-        <v>11.744</v>
+        <v>9.815</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9.815</v>
+        <v>9.641</v>
       </c>
       <c r="B23" t="n">
-        <v>138.5</v>
+        <v>137.9</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1548526491564767</v>
+        <v>0.1644703159493394</v>
       </c>
       <c r="D23" t="n">
-        <v>132.72</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>140.97</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.718</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9.718</v>
+        <v>9.605</v>
       </c>
       <c r="B24" t="n">
-        <v>138.8</v>
+        <v>137.9</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1594790570684688</v>
+        <v>0.168852070703022</v>
       </c>
       <c r="D24" t="n">
-        <v>136.19</v>
+        <v>143.64</v>
       </c>
       <c r="E24" t="n">
-        <v>9.815</v>
+        <v>9.641</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9.641</v>
+        <v>9.834</v>
       </c>
       <c r="B25" t="n">
-        <v>137.9</v>
+        <v>138.1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1644703159493394</v>
+        <v>0.1714044156774883</v>
       </c>
       <c r="D25" t="n">
-        <v>140.97</v>
+        <v>143.76</v>
       </c>
       <c r="E25" t="n">
-        <v>9.718</v>
+        <v>9.605</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9.605</v>
+        <v>10.312</v>
       </c>
       <c r="B26" t="n">
-        <v>137.9</v>
+        <v>141.7</v>
       </c>
       <c r="C26" t="n">
-        <v>0.168852070703022</v>
+        <v>0.1738544065311074</v>
       </c>
       <c r="D26" t="n">
-        <v>143.64</v>
+        <v>146.51</v>
       </c>
       <c r="E26" t="n">
-        <v>9.641</v>
+        <v>9.834</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9.834</v>
+        <v>10.316</v>
       </c>
       <c r="B27" t="n">
-        <v>138.1</v>
+        <v>140.1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1714044156774883</v>
+        <v>0.1764185801524323</v>
       </c>
       <c r="D27" t="n">
-        <v>143.76</v>
+        <v>149.22</v>
       </c>
       <c r="E27" t="n">
-        <v>9.605</v>
+        <v>10.312</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10.312</v>
+        <v>10.137</v>
       </c>
       <c r="B28" t="n">
-        <v>141.7</v>
+        <v>142</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1738544065311074</v>
+        <v>0.1764262765481369</v>
       </c>
       <c r="D28" t="n">
-        <v>146.51</v>
+        <v>151.3</v>
       </c>
       <c r="E28" t="n">
-        <v>9.834</v>
+        <v>10.316</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10.316</v>
+        <v>10.302</v>
       </c>
       <c r="B29" t="n">
-        <v>140.1</v>
+        <v>144.6</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1764185801524323</v>
+        <v>0.1779656834148795</v>
       </c>
       <c r="D29" t="n">
-        <v>149.22</v>
+        <v>154.16</v>
       </c>
       <c r="E29" t="n">
-        <v>10.312</v>
+        <v>10.137</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10.137</v>
+        <v>10.406</v>
       </c>
       <c r="B30" t="n">
-        <v>142</v>
+        <v>144.3</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1764262765481369</v>
+        <v>0.1807006978345595</v>
       </c>
       <c r="D30" t="n">
-        <v>151.3</v>
+        <v>157.18</v>
       </c>
       <c r="E30" t="n">
-        <v>10.316</v>
+        <v>10.302</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10.302</v>
+        <v>10.512</v>
       </c>
       <c r="B31" t="n">
-        <v>144.6</v>
+        <v>143.9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1779656834148795</v>
+        <v>0.1829686360235201</v>
       </c>
       <c r="D31" t="n">
-        <v>154.16</v>
+        <v>159.5</v>
       </c>
       <c r="E31" t="n">
-        <v>10.137</v>
+        <v>10.406</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>10.406</v>
+        <v>10.517</v>
       </c>
       <c r="B32" t="n">
-        <v>144.3</v>
+        <v>142.6</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1807006978345595</v>
+        <v>0.1845010661711004</v>
       </c>
       <c r="D32" t="n">
-        <v>157.18</v>
+        <v>161.14</v>
       </c>
       <c r="E32" t="n">
-        <v>10.302</v>
+        <v>10.512</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10.512</v>
+        <v>10.517</v>
       </c>
       <c r="B33" t="n">
-        <v>143.9</v>
+        <v>142.8</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1829686360235201</v>
+        <v>0.1844689787483919</v>
       </c>
       <c r="D33" t="n">
-        <v>159.5</v>
+        <v>156.16</v>
       </c>
       <c r="E33" t="n">
-        <v>10.406</v>
+        <v>10.517</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>10.571</v>
+      </c>
+      <c r="B34" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1852891843200596</v>
+      </c>
+      <c r="D34" t="n">
+        <v>155.16</v>
+      </c>
+      <c r="E34" t="n">
         <v>10.517</v>
-      </c>
-      <c r="B34" t="n">
-        <v>142.6</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.1845010661711004</v>
-      </c>
-      <c r="D34" t="n">
-        <v>161.14</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10.512</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10.517</v>
+        <v>10.516</v>
       </c>
       <c r="B35" t="n">
-        <v>142.8</v>
+        <v>141.5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1844689787483919</v>
-      </c>
-      <c r="D35" t="n">
-        <v>156.16</v>
-      </c>
+        <v>0.1866858030934679</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>10.517</v>
+        <v>10.571</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10.571</v>
+        <v>10.625</v>
       </c>
       <c r="B36" t="n">
-        <v>140.8</v>
+        <v>140.6</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1852891843200596</v>
+        <v>0.1883509853224627</v>
       </c>
       <c r="D36" t="n">
-        <v>155.16</v>
+        <v>152.94</v>
       </c>
       <c r="E36" t="n">
-        <v>10.517</v>
+        <v>10.516</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>10.516</v>
+        <v>11.413</v>
       </c>
       <c r="B37" t="n">
-        <v>141.5</v>
+        <v>139.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1866858030934679</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>0.1902724213644571</v>
+      </c>
+      <c r="D37" t="n">
+        <v>148.93</v>
+      </c>
       <c r="E37" t="n">
-        <v>10.571</v>
+        <v>10.625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>10.625</v>
+        <v>12.185</v>
       </c>
       <c r="B38" t="n">
-        <v>140.6</v>
+        <v>136.4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1883509853224627</v>
+        <v>0.1921360749715874</v>
       </c>
       <c r="D38" t="n">
-        <v>152.94</v>
+        <v>148.25</v>
       </c>
       <c r="E38" t="n">
-        <v>10.516</v>
+        <v>11.413</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>11.413</v>
+        <v>11.225</v>
       </c>
       <c r="B39" t="n">
-        <v>139.8</v>
+        <v>137.4</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1902724213644571</v>
+        <v>0.1944207377071363</v>
       </c>
       <c r="D39" t="n">
-        <v>148.93</v>
+        <v>146.14</v>
       </c>
       <c r="E39" t="n">
-        <v>10.625</v>
+        <v>12.185</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12.185</v>
+        <v>11.153</v>
       </c>
       <c r="B40" t="n">
         <v>136.4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1921360749715874</v>
+        <v>0.1955790875378318</v>
       </c>
       <c r="D40" t="n">
-        <v>148.25</v>
+        <v>142.64</v>
       </c>
       <c r="E40" t="n">
-        <v>11.413</v>
+        <v>11.225</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11.225</v>
+        <v>11.777</v>
       </c>
       <c r="B41" t="n">
-        <v>137.4</v>
+        <v>134.8</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1944207377071363</v>
+        <v>0.198405677630681</v>
       </c>
       <c r="D41" t="n">
-        <v>146.14</v>
+        <v>141.94</v>
       </c>
       <c r="E41" t="n">
-        <v>12.185</v>
+        <v>11.153</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11.153</v>
+        <v>9.25</v>
       </c>
       <c r="B42" t="n">
-        <v>136.4</v>
+        <v>133.8</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1955790875378318</v>
+        <v>0.1722693371493297</v>
       </c>
       <c r="D42" t="n">
-        <v>142.64</v>
+        <v>108.29</v>
       </c>
       <c r="E42" t="n">
-        <v>11.225</v>
+        <v>9.355</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11.777</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="B43" t="n">
-        <v>134.8</v>
+        <v>132.2</v>
       </c>
       <c r="C43" t="n">
-        <v>0.198405677630681</v>
+        <v>0.1721007760920495</v>
       </c>
       <c r="D43" t="n">
-        <v>141.94</v>
+        <v>108.38</v>
       </c>
       <c r="E43" t="n">
-        <v>11.153</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>9.355</v>
+        <v>9.138999999999999</v>
       </c>
       <c r="B44" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1712243088270473</v>
+        <v>0.1710100794234304</v>
       </c>
       <c r="D44" t="n">
-        <v>108.35</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>107.69</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9.132999999999999</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>9.25</v>
+        <v>9.6</v>
       </c>
       <c r="B45" t="n">
-        <v>133.8</v>
+        <v>129.3</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1722693371493297</v>
+        <v>0.1705961244849237</v>
       </c>
       <c r="D45" t="n">
-        <v>108.29</v>
+        <v>107.14</v>
       </c>
       <c r="E45" t="n">
-        <v>9.355</v>
+        <v>9.138999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9.132999999999999</v>
+        <v>10.544</v>
       </c>
       <c r="B46" t="n">
-        <v>132.2</v>
+        <v>132.9</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1721007760920495</v>
+        <v>0.1708141295331198</v>
       </c>
       <c r="D46" t="n">
-        <v>108.38</v>
+        <v>107.25</v>
       </c>
       <c r="E46" t="n">
-        <v>9.25</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>9.138999999999999</v>
+        <v>10.413</v>
       </c>
       <c r="B47" t="n">
-        <v>131</v>
+        <v>132.8</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1710100794234304</v>
+        <v>0.1716028876636834</v>
       </c>
       <c r="D47" t="n">
-        <v>107.69</v>
+        <v>106.74</v>
       </c>
       <c r="E47" t="n">
-        <v>9.132999999999999</v>
+        <v>10.544</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>9.6</v>
+        <v>10.413</v>
       </c>
       <c r="B48" t="n">
-        <v>129.3</v>
+        <v>132.6</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1705961244849237</v>
+        <v>0.1711884347071506</v>
       </c>
       <c r="D48" t="n">
-        <v>107.14</v>
+        <v>107.28</v>
       </c>
       <c r="E48" t="n">
-        <v>9.138999999999999</v>
+        <v>10.413</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10.544</v>
+        <v>10.587</v>
       </c>
       <c r="B49" t="n">
-        <v>132.9</v>
+        <v>134.4</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1708141295331198</v>
+        <v>0.1737773825649571</v>
       </c>
       <c r="D49" t="n">
-        <v>107.25</v>
+        <v>107.92</v>
       </c>
       <c r="E49" t="n">
-        <v>9.6</v>
+        <v>10.413</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10.413</v>
+        <v>10.638</v>
       </c>
       <c r="B50" t="n">
-        <v>132.8</v>
+        <v>134.7</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1716028876636834</v>
+        <v>0.17592589101034</v>
       </c>
       <c r="D50" t="n">
-        <v>106.74</v>
+        <v>108.97</v>
       </c>
       <c r="E50" t="n">
-        <v>10.544</v>
+        <v>10.587</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10.413</v>
+        <v>10.62</v>
       </c>
       <c r="B51" t="n">
-        <v>132.6</v>
+        <v>134.6</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1711884347071506</v>
+        <v>0.1783564562233249</v>
       </c>
       <c r="D51" t="n">
-        <v>107.28</v>
+        <v>109.64</v>
       </c>
       <c r="E51" t="n">
-        <v>10.413</v>
+        <v>10.638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10.587</v>
+        <v>10.884</v>
       </c>
       <c r="B52" t="n">
-        <v>134.4</v>
+        <v>132.6</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1737773825649571</v>
+        <v>0.1807328004994806</v>
       </c>
       <c r="D52" t="n">
-        <v>107.92</v>
+        <v>110.8</v>
       </c>
       <c r="E52" t="n">
-        <v>10.413</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10.638</v>
+        <v>10.898</v>
       </c>
       <c r="B53" t="n">
-        <v>134.7</v>
+        <v>132.7</v>
       </c>
       <c r="C53" t="n">
-        <v>0.17592589101034</v>
+        <v>0.182378274400309</v>
       </c>
       <c r="D53" t="n">
-        <v>108.97</v>
+        <v>112.86</v>
       </c>
       <c r="E53" t="n">
-        <v>10.587</v>
+        <v>10.884</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10.62</v>
+        <v>10.94</v>
       </c>
       <c r="B54" t="n">
-        <v>134.6</v>
+        <v>131.5</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1783564562233249</v>
+        <v>0.1845748228441364</v>
       </c>
       <c r="D54" t="n">
-        <v>109.64</v>
+        <v>113.41</v>
       </c>
       <c r="E54" t="n">
-        <v>10.638</v>
+        <v>10.898</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10.884</v>
+        <v>10.994</v>
       </c>
       <c r="B55" t="n">
-        <v>132.6</v>
+        <v>131.2</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1807328004994806</v>
+        <v>0.1869226971864676</v>
       </c>
       <c r="D55" t="n">
-        <v>110.8</v>
+        <v>115.04</v>
       </c>
       <c r="E55" t="n">
-        <v>10.62</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10.898</v>
+        <v>10.858</v>
       </c>
       <c r="B56" t="n">
-        <v>132.7</v>
+        <v>131.7</v>
       </c>
       <c r="C56" t="n">
-        <v>0.182378274400309</v>
+        <v>0.1890319417217151</v>
       </c>
       <c r="D56" t="n">
-        <v>112.86</v>
+        <v>116.85</v>
       </c>
       <c r="E56" t="n">
-        <v>10.884</v>
+        <v>10.994</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10.94</v>
+        <v>11.463</v>
       </c>
       <c r="B57" t="n">
-        <v>131.5</v>
+        <v>131.7</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1845748228441364</v>
+        <v>0.191334647869722</v>
       </c>
       <c r="D57" t="n">
-        <v>113.41</v>
+        <v>118.71</v>
       </c>
       <c r="E57" t="n">
-        <v>10.898</v>
+        <v>10.858</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10.994</v>
+        <v>11.288</v>
       </c>
       <c r="B58" t="n">
-        <v>131.2</v>
+        <v>131.3</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1869226971864676</v>
+        <v>0.1929401086149119</v>
       </c>
       <c r="D58" t="n">
-        <v>115.04</v>
+        <v>120.42</v>
       </c>
       <c r="E58" t="n">
-        <v>10.94</v>
+        <v>11.463</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10.858</v>
+        <v>10.74</v>
       </c>
       <c r="B59" t="n">
-        <v>131.7</v>
+        <v>133</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1890319417217151</v>
+        <v>0.1953482222654324</v>
       </c>
       <c r="D59" t="n">
-        <v>116.85</v>
+        <v>120.21</v>
       </c>
       <c r="E59" t="n">
-        <v>10.994</v>
+        <v>11.288</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>11.463</v>
+        <v>10.804</v>
       </c>
       <c r="B60" t="n">
-        <v>131.7</v>
+        <v>133.2</v>
       </c>
       <c r="C60" t="n">
-        <v>0.191334647869722</v>
+        <v>0.1967919735640473</v>
       </c>
       <c r="D60" t="n">
-        <v>118.71</v>
+        <v>123.56</v>
       </c>
       <c r="E60" t="n">
-        <v>10.858</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11.288</v>
+        <v>10.969</v>
       </c>
       <c r="B61" t="n">
-        <v>131.3</v>
+        <v>131</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1929401086149119</v>
-      </c>
-      <c r="D61" t="n">
-        <v>120.42</v>
-      </c>
+        <v>0.1994595795786037</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>11.463</v>
+        <v>10.804</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10.74</v>
+        <v>9.067</v>
       </c>
       <c r="B62" t="n">
-        <v>133</v>
+        <v>178.1</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1953482222654324</v>
+        <v>0.1501464037528147</v>
       </c>
       <c r="D62" t="n">
-        <v>120.21</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>11.288</v>
+        <v>8.986000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10.804</v>
+        <v>9.153</v>
       </c>
       <c r="B63" t="n">
-        <v>133.2</v>
+        <v>178.2</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1967919735640473</v>
+        <v>0.1516413113392473</v>
       </c>
       <c r="D63" t="n">
-        <v>123.56</v>
+        <v>72.11</v>
       </c>
       <c r="E63" t="n">
-        <v>10.74</v>
+        <v>9.067</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10.969</v>
+        <v>9.302</v>
       </c>
       <c r="B64" t="n">
-        <v>131</v>
+        <v>173.6</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1994595795786037</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>0.1532462139375857</v>
+      </c>
+      <c r="D64" t="n">
+        <v>72.11</v>
+      </c>
       <c r="E64" t="n">
-        <v>10.804</v>
+        <v>9.153</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>8.986000000000001</v>
+        <v>9.468</v>
       </c>
       <c r="B65" t="n">
-        <v>176.7</v>
+        <v>174</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1490610711347923</v>
+        <v>0.155784068456959</v>
       </c>
       <c r="D65" t="n">
-        <v>72.23</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>74.81999999999999</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9.302</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>9.067</v>
+        <v>10.629</v>
       </c>
       <c r="B66" t="n">
-        <v>178.1</v>
+        <v>173.6</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1501464037528147</v>
+        <v>0.1588503644503054</v>
       </c>
       <c r="D66" t="n">
-        <v>71.79000000000001</v>
+        <v>74.92</v>
       </c>
       <c r="E66" t="n">
-        <v>8.986000000000001</v>
+        <v>9.468</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>9.153</v>
+        <v>10.579</v>
       </c>
       <c r="B67" t="n">
-        <v>178.2</v>
+        <v>174.9</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1516413113392473</v>
+        <v>0.1631258787678839</v>
       </c>
       <c r="D67" t="n">
-        <v>72.11</v>
+        <v>75.73</v>
       </c>
       <c r="E67" t="n">
-        <v>9.067</v>
+        <v>10.629</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>9.302</v>
+        <v>10.378</v>
       </c>
       <c r="B68" t="n">
-        <v>173.6</v>
+        <v>172.1</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1532462139375857</v>
+        <v>0.1679272556984571</v>
       </c>
       <c r="D68" t="n">
-        <v>72.11</v>
+        <v>76.16</v>
       </c>
       <c r="E68" t="n">
-        <v>9.153</v>
+        <v>10.579</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>9.468</v>
+        <v>10.517</v>
       </c>
       <c r="B69" t="n">
-        <v>174</v>
+        <v>175.1</v>
       </c>
       <c r="C69" t="n">
-        <v>0.155784068456959</v>
+        <v>0.1734757144321421</v>
       </c>
       <c r="D69" t="n">
-        <v>74.81999999999999</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>9.302</v>
+        <v>10.378</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>10.629</v>
+        <v>10.279</v>
       </c>
       <c r="B70" t="n">
-        <v>173.6</v>
+        <v>176.1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1588503644503054</v>
+        <v>0.1784521478134904</v>
       </c>
       <c r="D70" t="n">
-        <v>74.92</v>
+        <v>76.8</v>
       </c>
       <c r="E70" t="n">
-        <v>9.468</v>
+        <v>10.517</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>10.579</v>
+        <v>10.297</v>
       </c>
       <c r="B71" t="n">
-        <v>174.9</v>
+        <v>175.3</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1631258787678839</v>
+        <v>0.1824579922466362</v>
       </c>
       <c r="D71" t="n">
-        <v>75.73</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>10.629</v>
+        <v>10.279</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>10.378</v>
+        <v>10.359</v>
       </c>
       <c r="B72" t="n">
-        <v>172.1</v>
+        <v>172.3</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1679272556984571</v>
+        <v>0.1857211891411493</v>
       </c>
       <c r="D72" t="n">
-        <v>76.16</v>
+        <v>78.8</v>
       </c>
       <c r="E72" t="n">
-        <v>10.579</v>
+        <v>10.297</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>10.517</v>
+        <v>10.268</v>
       </c>
       <c r="B73" t="n">
-        <v>175.1</v>
+        <v>172.9</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1734757144321421</v>
+        <v>0.1882556067711057</v>
       </c>
       <c r="D73" t="n">
-        <v>77.18000000000001</v>
+        <v>78.97</v>
       </c>
       <c r="E73" t="n">
-        <v>10.378</v>
+        <v>10.359</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>10.279</v>
+        <v>10.114</v>
       </c>
       <c r="B74" t="n">
-        <v>176.1</v>
+        <v>172.2</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1784521478134904</v>
+        <v>0.1905054803906715</v>
       </c>
       <c r="D74" t="n">
-        <v>76.8</v>
+        <v>79.52</v>
       </c>
       <c r="E74" t="n">
-        <v>10.517</v>
+        <v>10.268</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>10.297</v>
+        <v>10.142</v>
       </c>
       <c r="B75" t="n">
-        <v>175.3</v>
+        <v>169.6</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1824579922466362</v>
+        <v>0.1930507386887475</v>
       </c>
       <c r="D75" t="n">
-        <v>77.48999999999999</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>10.279</v>
+        <v>10.114</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>10.359</v>
+        <v>10.185</v>
       </c>
       <c r="B76" t="n">
-        <v>172.3</v>
+        <v>167.3</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1857211891411493</v>
+        <v>0.195667783484247</v>
       </c>
       <c r="D76" t="n">
-        <v>78.8</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>10.297</v>
+        <v>10.142</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10.268</v>
+        <v>10.692</v>
       </c>
       <c r="B77" t="n">
-        <v>172.9</v>
+        <v>175.5</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1882556067711057</v>
+        <v>0.1985296327533853</v>
       </c>
       <c r="D77" t="n">
-        <v>78.97</v>
+        <v>79.53</v>
       </c>
       <c r="E77" t="n">
-        <v>10.359</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10.114</v>
+        <v>10.656</v>
       </c>
       <c r="B78" t="n">
-        <v>172.2</v>
+        <v>176.3</v>
       </c>
       <c r="C78" t="n">
-        <v>0.1905054803906715</v>
+        <v>0.2014148863578962</v>
       </c>
       <c r="D78" t="n">
-        <v>79.52</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>10.268</v>
+        <v>10.692</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>10.142</v>
+        <v>9.474</v>
       </c>
       <c r="B79" t="n">
-        <v>169.6</v>
+        <v>178.3</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1930507386887475</v>
+        <v>0.2034957486438906</v>
       </c>
       <c r="D79" t="n">
-        <v>80.06999999999999</v>
+        <v>71.81</v>
       </c>
       <c r="E79" t="n">
-        <v>10.114</v>
+        <v>10.656</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>10.185</v>
+        <v>9.513</v>
       </c>
       <c r="B80" t="n">
-        <v>167.3</v>
+        <v>163.9</v>
       </c>
       <c r="C80" t="n">
-        <v>0.195667783484247</v>
+        <v>0.2045170677406773</v>
       </c>
       <c r="D80" t="n">
-        <v>79.81999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>10.142</v>
+        <v>9.474</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>10.692</v>
+        <v>9.388</v>
       </c>
       <c r="B81" t="n">
-        <v>175.5</v>
+        <v>164.4</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1985296327533853</v>
-      </c>
-      <c r="D81" t="n">
-        <v>79.53</v>
-      </c>
+        <v>0.2065765077083678</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>10.185</v>
+        <v>9.513</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>10.656</v>
+        <v>7.778</v>
       </c>
       <c r="B82" t="n">
-        <v>176.3</v>
+        <v>96.2</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2014148863578962</v>
+        <v>0.165600240833301</v>
       </c>
       <c r="D82" t="n">
-        <v>80.15000000000001</v>
+        <v>66.52</v>
       </c>
       <c r="E82" t="n">
-        <v>10.692</v>
+        <v>7.684</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>9.474</v>
+        <v>7.871</v>
       </c>
       <c r="B83" t="n">
-        <v>178.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2034957486438906</v>
+        <v>0.166420196005128</v>
       </c>
       <c r="D83" t="n">
-        <v>71.81</v>
+        <v>68.2</v>
       </c>
       <c r="E83" t="n">
-        <v>10.656</v>
+        <v>7.778</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>9.513</v>
+        <v>7.962</v>
       </c>
       <c r="B84" t="n">
-        <v>163.9</v>
+        <v>96.5</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2045170677406773</v>
+        <v>0.1653950260564632</v>
       </c>
       <c r="D84" t="n">
-        <v>68.93000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="E84" t="n">
-        <v>9.474</v>
+        <v>7.871</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9.388</v>
+        <v>8.429</v>
       </c>
       <c r="B85" t="n">
-        <v>164.4</v>
+        <v>95.3</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2065765077083678</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
+        <v>0.1643632228898508</v>
+      </c>
+      <c r="D85" t="n">
+        <v>71.08</v>
+      </c>
       <c r="E85" t="n">
-        <v>9.513</v>
+        <v>7.962</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7.684</v>
+        <v>9.153</v>
       </c>
       <c r="B86" t="n">
-        <v>94.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1679695923499624</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+        <v>0.1656160986787141</v>
+      </c>
+      <c r="D86" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="E86" t="n">
+        <v>8.429</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>7.778</v>
+        <v>9.17</v>
       </c>
       <c r="B87" t="n">
-        <v>96.2</v>
+        <v>92.2</v>
       </c>
       <c r="C87" t="n">
-        <v>0.165600240833301</v>
+        <v>0.1680139396672406</v>
       </c>
       <c r="D87" t="n">
-        <v>66.52</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E87" t="n">
-        <v>7.684</v>
+        <v>9.153</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>7.871</v>
+        <v>9.217000000000001</v>
       </c>
       <c r="B88" t="n">
-        <v>97.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C88" t="n">
-        <v>0.166420196005128</v>
+        <v>0.1710623188796476</v>
       </c>
       <c r="D88" t="n">
-        <v>68.2</v>
+        <v>74</v>
       </c>
       <c r="E88" t="n">
-        <v>7.778</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>7.962</v>
+        <v>9.218999999999999</v>
       </c>
       <c r="B89" t="n">
-        <v>96.5</v>
+        <v>85.3</v>
       </c>
       <c r="C89" t="n">
-        <v>0.1653950260564632</v>
+        <v>0.1736085048429544</v>
       </c>
       <c r="D89" t="n">
-        <v>67.33</v>
+        <v>74.73</v>
       </c>
       <c r="E89" t="n">
-        <v>7.871</v>
+        <v>9.217000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>8.429</v>
+        <v>9.137</v>
       </c>
       <c r="B90" t="n">
-        <v>95.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="C90" t="n">
-        <v>0.1643632228898508</v>
+        <v>0.1766742413457597</v>
       </c>
       <c r="D90" t="n">
-        <v>71.08</v>
+        <v>74.63</v>
       </c>
       <c r="E90" t="n">
-        <v>7.962</v>
+        <v>9.218999999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>9.153</v>
+        <v>9.151</v>
       </c>
       <c r="B91" t="n">
-        <v>95.5</v>
+        <v>83.3</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1656160986787141</v>
+        <v>0.1811493972437563</v>
       </c>
       <c r="D91" t="n">
-        <v>72.38</v>
+        <v>74.34</v>
       </c>
       <c r="E91" t="n">
-        <v>8.429</v>
+        <v>9.137</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>9.17</v>
+        <v>9.176</v>
       </c>
       <c r="B92" t="n">
-        <v>92.2</v>
+        <v>84.3</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1680139396672406</v>
+        <v>0.1844799311898693</v>
       </c>
       <c r="D92" t="n">
-        <v>73.79000000000001</v>
+        <v>74.03</v>
       </c>
       <c r="E92" t="n">
-        <v>9.153</v>
+        <v>9.151</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>9.217000000000001</v>
+        <v>9.013</v>
       </c>
       <c r="B93" t="n">
-        <v>88.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1710623188796476</v>
+        <v>0.1866525485619172</v>
       </c>
       <c r="D93" t="n">
-        <v>74</v>
+        <v>74.16</v>
       </c>
       <c r="E93" t="n">
-        <v>9.17</v>
+        <v>9.176</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>9.218999999999999</v>
+        <v>9.022</v>
       </c>
       <c r="B94" t="n">
-        <v>85.3</v>
+        <v>84.8</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1736085048429544</v>
+        <v>0.1889202476362492</v>
       </c>
       <c r="D94" t="n">
-        <v>74.73</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E94" t="n">
-        <v>9.217000000000001</v>
+        <v>9.013</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9.137</v>
+        <v>9.071</v>
       </c>
       <c r="B95" t="n">
-        <v>83.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1766742413457597</v>
+        <v>0.1911982123727116</v>
       </c>
       <c r="D95" t="n">
-        <v>74.63</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>9.218999999999999</v>
+        <v>9.022</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>9.151</v>
+        <v>9.215</v>
       </c>
       <c r="B96" t="n">
-        <v>83.3</v>
+        <v>84</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1811493972437563</v>
+        <v>0.1930333651321403</v>
       </c>
       <c r="D96" t="n">
-        <v>74.34</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="E96" t="n">
-        <v>9.137</v>
+        <v>9.071</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>9.176</v>
+        <v>10.795</v>
       </c>
       <c r="B97" t="n">
-        <v>84.3</v>
+        <v>78.2</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1844799311898693</v>
+        <v>0.1946707017723681</v>
       </c>
       <c r="D97" t="n">
-        <v>74.03</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="E97" t="n">
-        <v>9.151</v>
+        <v>9.215</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>9.013</v>
+        <v>10.344</v>
       </c>
       <c r="B98" t="n">
-        <v>84.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1866525485619172</v>
+        <v>0.1964415029468491</v>
       </c>
       <c r="D98" t="n">
-        <v>74.16</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="E98" t="n">
-        <v>9.176</v>
+        <v>10.795</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>9.022</v>
+        <v>9.68</v>
       </c>
       <c r="B99" t="n">
-        <v>84.8</v>
+        <v>79.7</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1889202476362492</v>
+        <v>0.1996723176564928</v>
       </c>
       <c r="D99" t="n">
-        <v>75.40000000000001</v>
+        <v>95.13</v>
       </c>
       <c r="E99" t="n">
-        <v>9.013</v>
+        <v>10.344</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>9.071</v>
+        <v>9.221</v>
       </c>
       <c r="B100" t="n">
-        <v>84.7</v>
+        <v>80.7</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1911982123727116</v>
+        <v>0.2014703809751995</v>
       </c>
       <c r="D100" t="n">
-        <v>88.93000000000001</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>9.022</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>9.215</v>
+        <v>9.173</v>
       </c>
       <c r="B101" t="n">
-        <v>84</v>
+        <v>81.7</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1930333651321403</v>
-      </c>
-      <c r="D101" t="n">
-        <v>91.54000000000001</v>
-      </c>
+        <v>0.204204654101594</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>9.071</v>
+        <v>9.221</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>10.795</v>
+        <v>5.294</v>
       </c>
       <c r="B102" t="n">
-        <v>78.2</v>
+        <v>37.8</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1946707017723681</v>
+        <v>0.1656842182728042</v>
       </c>
       <c r="D102" t="n">
-        <v>91.43000000000001</v>
+        <v>74.12</v>
       </c>
       <c r="E102" t="n">
-        <v>9.215</v>
+        <v>5.336</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>10.344</v>
+        <v>4.973</v>
       </c>
       <c r="B103" t="n">
-        <v>78.40000000000001</v>
+        <v>43.1</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1964415029468491</v>
+        <v>0.1687051158658473</v>
       </c>
       <c r="D103" t="n">
-        <v>94.34999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="E103" t="n">
-        <v>10.795</v>
+        <v>5.294</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>9.68</v>
+        <v>5.184</v>
       </c>
       <c r="B104" t="n">
-        <v>79.7</v>
+        <v>49.5</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1996723176564928</v>
+        <v>0.1728397819676526</v>
       </c>
       <c r="D104" t="n">
-        <v>95.13</v>
+        <v>76.77</v>
       </c>
       <c r="E104" t="n">
-        <v>10.344</v>
+        <v>4.973</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>9.221</v>
+        <v>5.957</v>
       </c>
       <c r="B105" t="n">
-        <v>80.7</v>
+        <v>48.9</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2014703809751995</v>
+        <v>0.1745763724933505</v>
       </c>
       <c r="D105" t="n">
-        <v>94.76000000000001</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="E105" t="n">
-        <v>9.68</v>
+        <v>5.184</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>9.173</v>
+        <v>6.844</v>
       </c>
       <c r="B106" t="n">
-        <v>81.7</v>
+        <v>43.7</v>
       </c>
       <c r="C106" t="n">
-        <v>0.204204654101594</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
+        <v>0.1742929013131298</v>
+      </c>
+      <c r="D106" t="n">
+        <v>73.90000000000001</v>
+      </c>
       <c r="E106" t="n">
-        <v>9.221</v>
+        <v>5.957</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5.336</v>
+        <v>6.594</v>
       </c>
       <c r="B107" t="n">
-        <v>33.7</v>
+        <v>44.1</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1619469350411711</v>
+        <v>0.1743431661529</v>
       </c>
       <c r="D107" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="E107" t="n">
+        <v>6.844</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>5.294</v>
+        <v>6.055</v>
       </c>
       <c r="B108" t="n">
-        <v>37.8</v>
+        <v>48.7</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1656842182728042</v>
+        <v>0.1744957357519968</v>
       </c>
       <c r="D108" t="n">
-        <v>74.12</v>
+        <v>75.56</v>
       </c>
       <c r="E108" t="n">
-        <v>5.336</v>
+        <v>6.594</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4.973</v>
+        <v>6.038</v>
       </c>
       <c r="B109" t="n">
-        <v>43.1</v>
+        <v>52.5</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1687051158658473</v>
+        <v>0.1770419486016253</v>
       </c>
       <c r="D109" t="n">
-        <v>74.5</v>
+        <v>72.39</v>
       </c>
       <c r="E109" t="n">
-        <v>5.294</v>
+        <v>6.055</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>5.184</v>
+        <v>6.198</v>
       </c>
       <c r="B110" t="n">
-        <v>49.5</v>
+        <v>55.3</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1728397819676526</v>
+        <v>0.1803194124410873</v>
       </c>
       <c r="D110" t="n">
-        <v>76.77</v>
+        <v>79.41</v>
       </c>
       <c r="E110" t="n">
-        <v>4.973</v>
+        <v>6.038</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>5.957</v>
+        <v>6.263</v>
       </c>
       <c r="B111" t="n">
-        <v>48.9</v>
+        <v>57.7</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1745763724933505</v>
+        <v>0.1837509566285332</v>
       </c>
       <c r="D111" t="n">
-        <v>76.98999999999999</v>
+        <v>79.78</v>
       </c>
       <c r="E111" t="n">
-        <v>5.184</v>
+        <v>6.198</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6.844</v>
+        <v>6.521</v>
       </c>
       <c r="B112" t="n">
-        <v>43.7</v>
+        <v>57.6</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1742929013131298</v>
+        <v>0.1875843239255592</v>
       </c>
       <c r="D112" t="n">
-        <v>73.90000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="E112" t="n">
-        <v>5.957</v>
+        <v>6.263</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>6.594</v>
+        <v>6.569</v>
       </c>
       <c r="B113" t="n">
-        <v>44.1</v>
+        <v>59.2</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1743431661529</v>
+        <v>0.1902246600159277</v>
       </c>
       <c r="D113" t="n">
-        <v>73.90000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E113" t="n">
-        <v>6.844</v>
+        <v>6.521</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6.055</v>
+        <v>6.466</v>
       </c>
       <c r="B114" t="n">
-        <v>48.7</v>
+        <v>62.3</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1744957357519968</v>
+        <v>0.1934229478540781</v>
       </c>
       <c r="D114" t="n">
-        <v>75.56</v>
+        <v>79.94</v>
       </c>
       <c r="E114" t="n">
-        <v>6.594</v>
+        <v>6.569</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6.038</v>
+        <v>6.563</v>
       </c>
       <c r="B115" t="n">
-        <v>52.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1770419486016253</v>
+        <v>0.1958725920737333</v>
       </c>
       <c r="D115" t="n">
-        <v>72.39</v>
+        <v>82.8</v>
       </c>
       <c r="E115" t="n">
-        <v>6.055</v>
+        <v>6.466</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6.198</v>
+        <v>6.648</v>
       </c>
       <c r="B116" t="n">
-        <v>55.3</v>
+        <v>67.8</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1803194124410873</v>
+        <v>0.197647982367416</v>
       </c>
       <c r="D116" t="n">
-        <v>79.41</v>
+        <v>83.05</v>
       </c>
       <c r="E116" t="n">
-        <v>6.038</v>
+        <v>6.563</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>6.263</v>
+        <v>7.472</v>
       </c>
       <c r="B117" t="n">
-        <v>57.7</v>
+        <v>68.7</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1837509566285332</v>
+        <v>0.2003708118130049</v>
       </c>
       <c r="D117" t="n">
-        <v>79.78</v>
+        <v>81.53</v>
       </c>
       <c r="E117" t="n">
-        <v>6.198</v>
+        <v>6.648</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>6.521</v>
+        <v>7.476</v>
       </c>
       <c r="B118" t="n">
-        <v>57.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1875843239255592</v>
+        <v>0.2034790702430252</v>
       </c>
       <c r="D118" t="n">
-        <v>79.41</v>
+        <v>86.86</v>
       </c>
       <c r="E118" t="n">
-        <v>6.263</v>
+        <v>7.472</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>6.569</v>
+        <v>6.936</v>
       </c>
       <c r="B119" t="n">
-        <v>59.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1902246600159277</v>
+        <v>0.2043451099117282</v>
       </c>
       <c r="D119" t="n">
-        <v>80.09</v>
+        <v>87.63</v>
       </c>
       <c r="E119" t="n">
-        <v>6.521</v>
+        <v>7.476</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>6.466</v>
+        <v>7.471</v>
       </c>
       <c r="B120" t="n">
-        <v>62.3</v>
+        <v>73.2</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1934229478540781</v>
+        <v>0.202398593145538</v>
       </c>
       <c r="D120" t="n">
-        <v>79.94</v>
+        <v>88.23</v>
       </c>
       <c r="E120" t="n">
-        <v>6.569</v>
+        <v>6.936</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>6.563</v>
+        <v>7.836</v>
       </c>
       <c r="B121" t="n">
-        <v>65.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1958725920737333</v>
-      </c>
-      <c r="D121" t="n">
-        <v>82.8</v>
-      </c>
+        <v>0.2047455166157824</v>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>6.466</v>
+        <v>7.471</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6.648</v>
+        <v>8.289</v>
       </c>
       <c r="B122" t="n">
-        <v>67.8</v>
+        <v>142</v>
       </c>
       <c r="C122" t="n">
-        <v>0.197647982367416</v>
+        <v>0.1586789624052656</v>
       </c>
       <c r="D122" t="n">
-        <v>83.05</v>
+        <v>130.38</v>
       </c>
       <c r="E122" t="n">
-        <v>6.563</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>7.472</v>
+        <v>8.286</v>
       </c>
       <c r="B123" t="n">
-        <v>68.7</v>
+        <v>140.7</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2003708118130049</v>
+        <v>0.1600517925709437</v>
       </c>
       <c r="D123" t="n">
-        <v>81.53</v>
+        <v>132.39</v>
       </c>
       <c r="E123" t="n">
-        <v>6.648</v>
+        <v>8.289</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>7.476</v>
+        <v>8.084</v>
       </c>
       <c r="B124" t="n">
-        <v>71.09999999999999</v>
+        <v>143.3</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2034790702430252</v>
+        <v>0.1646246746466475</v>
       </c>
       <c r="D124" t="n">
-        <v>86.86</v>
+        <v>133.17</v>
       </c>
       <c r="E124" t="n">
-        <v>7.472</v>
+        <v>8.286</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6.936</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="B125" t="n">
-        <v>75.40000000000001</v>
+        <v>144</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2043451099117282</v>
+        <v>0.1651228453854403</v>
       </c>
       <c r="D125" t="n">
-        <v>87.63</v>
+        <v>121.06</v>
       </c>
       <c r="E125" t="n">
-        <v>7.476</v>
+        <v>8.084</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>7.471</v>
+        <v>9.162000000000001</v>
       </c>
       <c r="B126" t="n">
-        <v>73.2</v>
+        <v>140.5</v>
       </c>
       <c r="C126" t="n">
-        <v>0.202398593145538</v>
+        <v>0.1674831787986964</v>
       </c>
       <c r="D126" t="n">
-        <v>88.23</v>
+        <v>115.86</v>
       </c>
       <c r="E126" t="n">
-        <v>6.936</v>
+        <v>8.343999999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>7.836</v>
+        <v>9.141999999999999</v>
       </c>
       <c r="B127" t="n">
-        <v>72.59999999999999</v>
+        <v>139.8</v>
       </c>
       <c r="C127" t="n">
-        <v>0.2047455166157824</v>
-      </c>
-      <c r="D127" t="inlineStr"/>
+        <v>0.1701305091146716</v>
+      </c>
+      <c r="D127" t="n">
+        <v>111.13</v>
+      </c>
       <c r="E127" t="n">
-        <v>7.471</v>
+        <v>9.162000000000001</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>8.06</v>
+        <v>9.239000000000001</v>
       </c>
       <c r="B128" t="n">
-        <v>142.9</v>
+        <v>141.8</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1557924812998062</v>
+        <v>0.1750684057897678</v>
       </c>
       <c r="D128" t="n">
-        <v>124.79</v>
-      </c>
-      <c r="E128" t="inlineStr"/>
+        <v>113.19</v>
+      </c>
+      <c r="E128" t="n">
+        <v>9.141999999999999</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>8.289</v>
+        <v>9.617000000000001</v>
       </c>
       <c r="B129" t="n">
-        <v>142</v>
+        <v>142.5</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1586789624052656</v>
+        <v>0.1813722595087412</v>
       </c>
       <c r="D129" t="n">
-        <v>130.38</v>
+        <v>119.54</v>
       </c>
       <c r="E129" t="n">
-        <v>8.06</v>
+        <v>9.239000000000001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>8.286</v>
+        <v>9.845000000000001</v>
       </c>
       <c r="B130" t="n">
-        <v>140.7</v>
+        <v>142.5</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1600517925709437</v>
+        <v>0.1876274491520957</v>
       </c>
       <c r="D130" t="n">
-        <v>132.39</v>
+        <v>121.55</v>
       </c>
       <c r="E130" t="n">
-        <v>8.289</v>
+        <v>9.617000000000001</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>8.084</v>
+        <v>9.831</v>
       </c>
       <c r="B131" t="n">
-        <v>143.3</v>
+        <v>140.4</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1646246746466475</v>
+        <v>0.1938166702438147</v>
       </c>
       <c r="D131" t="n">
-        <v>133.17</v>
+        <v>124.67</v>
       </c>
       <c r="E131" t="n">
-        <v>8.286</v>
+        <v>9.845000000000001</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>8.343999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="B132" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1651228453854403</v>
+        <v>0.1994585647415006</v>
       </c>
       <c r="D132" t="n">
-        <v>121.06</v>
+        <v>119.88</v>
       </c>
       <c r="E132" t="n">
-        <v>8.084</v>
+        <v>9.831</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>9.162000000000001</v>
+        <v>9.456</v>
       </c>
       <c r="B133" t="n">
-        <v>140.5</v>
+        <v>137.8</v>
       </c>
       <c r="C133" t="n">
-        <v>0.1674831787986964</v>
+        <v>0.2046728559796534</v>
       </c>
       <c r="D133" t="n">
-        <v>115.86</v>
+        <v>121.24</v>
       </c>
       <c r="E133" t="n">
-        <v>8.343999999999999</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>9.141999999999999</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="B134" t="n">
-        <v>139.8</v>
+        <v>137.6</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1701305091146716</v>
+        <v>0.2089611009545732</v>
       </c>
       <c r="D134" t="n">
-        <v>111.13</v>
+        <v>118.99</v>
       </c>
       <c r="E134" t="n">
-        <v>9.162000000000001</v>
+        <v>9.456</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>9.239000000000001</v>
+        <v>9.103</v>
       </c>
       <c r="B135" t="n">
-        <v>141.8</v>
+        <v>137.2</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1750684057897678</v>
+        <v>0.2139107911476784</v>
       </c>
       <c r="D135" t="n">
-        <v>113.19</v>
+        <v>121.46</v>
       </c>
       <c r="E135" t="n">
-        <v>9.141999999999999</v>
+        <v>9.191000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>9.617000000000001</v>
+        <v>9.223000000000001</v>
       </c>
       <c r="B136" t="n">
-        <v>142.5</v>
+        <v>136.3</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1813722595087412</v>
+        <v>0.2183498887895962</v>
       </c>
       <c r="D136" t="n">
-        <v>119.54</v>
+        <v>120.8</v>
       </c>
       <c r="E136" t="n">
-        <v>9.239000000000001</v>
+        <v>9.103</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>9.845000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="B137" t="n">
-        <v>142.5</v>
+        <v>140.1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1876274491520957</v>
+        <v>0.2228432452076741</v>
       </c>
       <c r="D137" t="n">
-        <v>121.55</v>
+        <v>118.96</v>
       </c>
       <c r="E137" t="n">
-        <v>9.617000000000001</v>
+        <v>9.223000000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>9.831</v>
+        <v>9.91</v>
       </c>
       <c r="B138" t="n">
-        <v>140.4</v>
+        <v>135</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1938166702438147</v>
+        <v>0.2269578930762318</v>
       </c>
       <c r="D138" t="n">
-        <v>124.67</v>
+        <v>123.84</v>
       </c>
       <c r="E138" t="n">
-        <v>9.845000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>9.699999999999999</v>
+        <v>9.742000000000001</v>
       </c>
       <c r="B139" t="n">
-        <v>138</v>
+        <v>132.5</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1994585647415006</v>
+        <v>0.2305300004091387</v>
       </c>
       <c r="D139" t="n">
-        <v>119.88</v>
+        <v>123.95</v>
       </c>
       <c r="E139" t="n">
-        <v>9.831</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>9.456</v>
+        <v>10.474</v>
       </c>
       <c r="B140" t="n">
-        <v>137.8</v>
+        <v>127.5</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2046728559796534</v>
+        <v>0.2326595937792619</v>
       </c>
       <c r="D140" t="n">
-        <v>121.24</v>
+        <v>125.99</v>
       </c>
       <c r="E140" t="n">
-        <v>9.699999999999999</v>
+        <v>9.742000000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>9.191000000000001</v>
+        <v>10.603</v>
       </c>
       <c r="B141" t="n">
-        <v>137.6</v>
+        <v>122.9</v>
       </c>
       <c r="C141" t="n">
-        <v>0.2089611009545732</v>
-      </c>
-      <c r="D141" t="n">
-        <v>118.99</v>
-      </c>
+        <v>0.2336564623149331</v>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>9.456</v>
+        <v>10.474</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>9.103</v>
+        <v>10.237</v>
       </c>
       <c r="B142" t="n">
-        <v>137.2</v>
+        <v>126.6</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2139107911476784</v>
+        <v>0.1630931802226025</v>
       </c>
       <c r="D142" t="n">
-        <v>121.46</v>
+        <v>154.06</v>
       </c>
       <c r="E142" t="n">
-        <v>9.191000000000001</v>
+        <v>10.212</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>9.223000000000001</v>
+        <v>10.398</v>
       </c>
       <c r="B143" t="n">
-        <v>136.3</v>
+        <v>124.8</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2183498887895962</v>
+        <v>0.1635523912165553</v>
       </c>
       <c r="D143" t="n">
-        <v>120.8</v>
+        <v>154.56</v>
       </c>
       <c r="E143" t="n">
-        <v>9.103</v>
+        <v>10.237</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>9.699999999999999</v>
+        <v>10.334</v>
       </c>
       <c r="B144" t="n">
-        <v>140.1</v>
+        <v>123.1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2228432452076741</v>
+        <v>0.163243073127508</v>
       </c>
       <c r="D144" t="n">
-        <v>118.96</v>
+        <v>154.43</v>
       </c>
       <c r="E144" t="n">
-        <v>9.223000000000001</v>
+        <v>10.398</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>9.91</v>
+        <v>10.513</v>
       </c>
       <c r="B145" t="n">
-        <v>135</v>
+        <v>122.2</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2269578930762318</v>
+        <v>0.1638660048722962</v>
       </c>
       <c r="D145" t="n">
-        <v>123.84</v>
+        <v>154.89</v>
       </c>
       <c r="E145" t="n">
-        <v>9.699999999999999</v>
+        <v>10.334</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>9.742000000000001</v>
+        <v>11.291</v>
       </c>
       <c r="B146" t="n">
-        <v>132.5</v>
+        <v>124</v>
       </c>
       <c r="C146" t="n">
-        <v>0.2305300004091387</v>
+        <v>0.1649578977391626</v>
       </c>
       <c r="D146" t="n">
-        <v>123.95</v>
+        <v>153.59</v>
       </c>
       <c r="E146" t="n">
-        <v>9.91</v>
+        <v>10.513</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>10.474</v>
+        <v>11.224</v>
       </c>
       <c r="B147" t="n">
-        <v>127.5</v>
+        <v>122.8</v>
       </c>
       <c r="C147" t="n">
-        <v>0.2326595937792619</v>
+        <v>0.1660920972681608</v>
       </c>
       <c r="D147" t="n">
-        <v>125.99</v>
+        <v>153.46</v>
       </c>
       <c r="E147" t="n">
-        <v>9.742000000000001</v>
+        <v>11.291</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>10.603</v>
+        <v>11.176</v>
       </c>
       <c r="B148" t="n">
-        <v>122.9</v>
+        <v>122.5</v>
       </c>
       <c r="C148" t="n">
-        <v>0.2336564623149331</v>
-      </c>
-      <c r="D148" t="inlineStr"/>
+        <v>0.1673862894285038</v>
+      </c>
+      <c r="D148" t="n">
+        <v>137.74</v>
+      </c>
       <c r="E148" t="n">
-        <v>10.474</v>
+        <v>11.224</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>10.212</v>
+        <v>11.337</v>
       </c>
       <c r="B149" t="n">
-        <v>127.7</v>
+        <v>123</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1619208080826631</v>
+        <v>0.1713932918744115</v>
       </c>
       <c r="D149" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="E149" t="inlineStr"/>
+        <v>138.01</v>
+      </c>
+      <c r="E149" t="n">
+        <v>11.176</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>10.237</v>
+        <v>11.478</v>
       </c>
       <c r="B150" t="n">
-        <v>126.6</v>
+        <v>123</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1630931802226025</v>
+        <v>0.1756759681922429</v>
       </c>
       <c r="D150" t="n">
-        <v>154.06</v>
+        <v>138.99</v>
       </c>
       <c r="E150" t="n">
-        <v>10.212</v>
+        <v>11.337</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>10.398</v>
+        <v>11.579</v>
       </c>
       <c r="B151" t="n">
-        <v>124.8</v>
+        <v>121.5</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1635523912165553</v>
+        <v>0.1796300606444581</v>
       </c>
       <c r="D151" t="n">
-        <v>154.56</v>
+        <v>139.35</v>
       </c>
       <c r="E151" t="n">
-        <v>10.237</v>
+        <v>11.478</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>10.334</v>
+        <v>11.5</v>
       </c>
       <c r="B152" t="n">
-        <v>123.1</v>
+        <v>119.4</v>
       </c>
       <c r="C152" t="n">
-        <v>0.163243073127508</v>
+        <v>0.184089633065788</v>
       </c>
       <c r="D152" t="n">
-        <v>154.43</v>
+        <v>139.35</v>
       </c>
       <c r="E152" t="n">
-        <v>10.398</v>
+        <v>11.579</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>10.513</v>
+        <v>11.57</v>
       </c>
       <c r="B153" t="n">
-        <v>122.2</v>
+        <v>117.7</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1638660048722962</v>
+        <v>0.1885813089334645</v>
       </c>
       <c r="D153" t="n">
-        <v>154.89</v>
+        <v>139.46</v>
       </c>
       <c r="E153" t="n">
-        <v>10.334</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>11.291</v>
+        <v>11.449</v>
       </c>
       <c r="B154" t="n">
-        <v>124</v>
+        <v>115.6</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1649578977391626</v>
+        <v>0.1929025968279871</v>
       </c>
       <c r="D154" t="n">
-        <v>153.59</v>
+        <v>140.25</v>
       </c>
       <c r="E154" t="n">
-        <v>10.513</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>11.224</v>
+        <v>11.308</v>
       </c>
       <c r="B155" t="n">
-        <v>122.8</v>
+        <v>114.5</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1660920972681608</v>
+        <v>0.1965427591445402</v>
       </c>
       <c r="D155" t="n">
-        <v>153.46</v>
+        <v>139.9</v>
       </c>
       <c r="E155" t="n">
-        <v>11.291</v>
+        <v>11.449</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>11.176</v>
+        <v>11.171</v>
       </c>
       <c r="B156" t="n">
-        <v>122.5</v>
+        <v>113.9</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1673862894285038</v>
+        <v>0.2000985399552338</v>
       </c>
       <c r="D156" t="n">
-        <v>137.74</v>
+        <v>140.15</v>
       </c>
       <c r="E156" t="n">
-        <v>11.224</v>
+        <v>11.308</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>11.337</v>
+        <v>12.129</v>
       </c>
       <c r="B157" t="n">
-        <v>123</v>
+        <v>112.3</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1713932918744115</v>
+        <v>0.2037363592493313</v>
       </c>
       <c r="D157" t="n">
-        <v>138.01</v>
+        <v>139.05</v>
       </c>
       <c r="E157" t="n">
-        <v>11.176</v>
+        <v>11.171</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>11.478</v>
+        <v>12.249</v>
       </c>
       <c r="B158" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1756759681922429</v>
+        <v>0.2062662981446766</v>
       </c>
       <c r="D158" t="n">
-        <v>138.99</v>
+        <v>138.02</v>
       </c>
       <c r="E158" t="n">
-        <v>11.337</v>
+        <v>12.129</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>11.579</v>
+        <v>11.835</v>
       </c>
       <c r="B159" t="n">
-        <v>121.5</v>
+        <v>107.7</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1796300606444581</v>
+        <v>0.2086942516329779</v>
       </c>
       <c r="D159" t="n">
-        <v>139.35</v>
+        <v>137.23</v>
       </c>
       <c r="E159" t="n">
-        <v>11.478</v>
+        <v>12.249</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>11.5</v>
+        <v>11.503</v>
       </c>
       <c r="B160" t="n">
-        <v>119.4</v>
+        <v>107.7</v>
       </c>
       <c r="C160" t="n">
-        <v>0.184089633065788</v>
+        <v>0.2112970198987334</v>
       </c>
       <c r="D160" t="n">
-        <v>139.35</v>
+        <v>139.08</v>
       </c>
       <c r="E160" t="n">
-        <v>11.579</v>
+        <v>11.835</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>11.57</v>
+        <v>11.541</v>
       </c>
       <c r="B161" t="n">
-        <v>117.7</v>
+        <v>106.6</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1885813089334645</v>
-      </c>
-      <c r="D161" t="n">
-        <v>139.46</v>
-      </c>
+        <v>0.2151933157090585</v>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>11.5</v>
+        <v>11.503</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>11.449</v>
+        <v>8.760999999999999</v>
       </c>
       <c r="B162" t="n">
-        <v>115.6</v>
+        <v>80.2</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1929025968279871</v>
+        <v>0.1828291785749968</v>
       </c>
       <c r="D162" t="n">
-        <v>140.25</v>
+        <v>27.14</v>
       </c>
       <c r="E162" t="n">
-        <v>11.57</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>11.308</v>
+        <v>8.396000000000001</v>
       </c>
       <c r="B163" t="n">
-        <v>114.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="C163" t="n">
-        <v>0.1965427591445402</v>
+        <v>0.184548787992348</v>
       </c>
       <c r="D163" t="n">
-        <v>139.9</v>
+        <v>25.85</v>
       </c>
       <c r="E163" t="n">
-        <v>11.449</v>
+        <v>8.760999999999999</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>11.171</v>
+        <v>8.523</v>
       </c>
       <c r="B164" t="n">
-        <v>113.9</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C164" t="n">
-        <v>0.2000985399552338</v>
+        <v>0.1858613186942235</v>
       </c>
       <c r="D164" t="n">
-        <v>140.15</v>
+        <v>32.63</v>
       </c>
       <c r="E164" t="n">
-        <v>11.308</v>
+        <v>8.396000000000001</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>12.129</v>
+        <v>8.948</v>
       </c>
       <c r="B165" t="n">
-        <v>112.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="C165" t="n">
-        <v>0.2037363592493313</v>
+        <v>0.1866335555477804</v>
       </c>
       <c r="D165" t="n">
-        <v>139.05</v>
+        <v>28.5</v>
       </c>
       <c r="E165" t="n">
-        <v>11.171</v>
+        <v>8.523</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>12.249</v>
+        <v>9.536</v>
       </c>
       <c r="B166" t="n">
-        <v>111</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="C166" t="n">
-        <v>0.2062662981446766</v>
+        <v>0.1877314890968652</v>
       </c>
       <c r="D166" t="n">
-        <v>138.02</v>
+        <v>29.13</v>
       </c>
       <c r="E166" t="n">
-        <v>12.129</v>
+        <v>8.948</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>11.835</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="B167" t="n">
-        <v>107.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>0.2086942516329779</v>
+        <v>0.189768968141758</v>
       </c>
       <c r="D167" t="n">
-        <v>137.23</v>
+        <v>31.62</v>
       </c>
       <c r="E167" t="n">
-        <v>12.249</v>
+        <v>9.536</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>11.503</v>
+        <v>9.186</v>
       </c>
       <c r="B168" t="n">
-        <v>107.7</v>
+        <v>70.8</v>
       </c>
       <c r="C168" t="n">
-        <v>0.2112970198987334</v>
+        <v>0.1929009604264598</v>
       </c>
       <c r="D168" t="n">
-        <v>139.08</v>
+        <v>31.41</v>
       </c>
       <c r="E168" t="n">
-        <v>11.835</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>11.541</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="B169" t="n">
-        <v>106.6</v>
+        <v>64.8</v>
       </c>
       <c r="C169" t="n">
-        <v>0.2151933157090585</v>
-      </c>
-      <c r="D169" t="inlineStr"/>
+        <v>0.1966787974389536</v>
+      </c>
+      <c r="D169" t="n">
+        <v>32.22</v>
+      </c>
       <c r="E169" t="n">
-        <v>11.503</v>
+        <v>9.186</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>8.300000000000001</v>
+        <v>8.522</v>
       </c>
       <c r="B170" t="n">
-        <v>81.09999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1803898936132776</v>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
+        <v>0.2006391535872529</v>
+      </c>
+      <c r="D170" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="E170" t="n">
+        <v>9.042999999999999</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>8.760999999999999</v>
+        <v>7.944</v>
       </c>
       <c r="B171" t="n">
-        <v>80.2</v>
+        <v>60.2</v>
       </c>
       <c r="C171" t="n">
-        <v>0.1828291785749968</v>
+        <v>0.2048656117015703</v>
       </c>
       <c r="D171" t="n">
-        <v>27.14</v>
+        <v>40.16</v>
       </c>
       <c r="E171" t="n">
-        <v>8.300000000000001</v>
+        <v>8.522</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>8.396000000000001</v>
+        <v>8.266999999999999</v>
       </c>
       <c r="B172" t="n">
-        <v>83.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="C172" t="n">
-        <v>0.184548787992348</v>
+        <v>0.2089767211658702</v>
       </c>
       <c r="D172" t="n">
-        <v>25.85</v>
+        <v>40.99</v>
       </c>
       <c r="E172" t="n">
-        <v>8.760999999999999</v>
+        <v>7.944</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>8.523</v>
+        <v>8.451000000000001</v>
       </c>
       <c r="B173" t="n">
-        <v>84.09999999999999</v>
+        <v>56.8</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1858613186942235</v>
+        <v>0.2126211591739718</v>
       </c>
       <c r="D173" t="n">
-        <v>32.63</v>
+        <v>42.16</v>
       </c>
       <c r="E173" t="n">
-        <v>8.396000000000001</v>
+        <v>8.266999999999999</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>8.948</v>
+        <v>8.113</v>
       </c>
       <c r="B174" t="n">
-        <v>84.90000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="C174" t="n">
-        <v>0.1866335555477804</v>
+        <v>0.2154252807318739</v>
       </c>
       <c r="D174" t="n">
-        <v>28.5</v>
+        <v>43.37</v>
       </c>
       <c r="E174" t="n">
-        <v>8.523</v>
+        <v>8.451000000000001</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>9.536</v>
+        <v>8.073</v>
       </c>
       <c r="B175" t="n">
-        <v>87.09999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1877314890968652</v>
+        <v>0.2178685459165742</v>
       </c>
       <c r="D175" t="n">
-        <v>29.13</v>
+        <v>40.93</v>
       </c>
       <c r="E175" t="n">
-        <v>8.948</v>
+        <v>8.113</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>9.619999999999999</v>
+        <v>8.117000000000001</v>
       </c>
       <c r="B176" t="n">
-        <v>80.09999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="C176" t="n">
-        <v>0.189768968141758</v>
+        <v>0.2203600339742307</v>
       </c>
       <c r="D176" t="n">
-        <v>31.62</v>
+        <v>44.14</v>
       </c>
       <c r="E176" t="n">
-        <v>9.536</v>
+        <v>8.073</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>9.186</v>
+        <v>9.381</v>
       </c>
       <c r="B177" t="n">
-        <v>70.8</v>
+        <v>51.3</v>
       </c>
       <c r="C177" t="n">
-        <v>0.1929009604264598</v>
+        <v>0.2226230843401145</v>
       </c>
       <c r="D177" t="n">
-        <v>31.41</v>
+        <v>44.58</v>
       </c>
       <c r="E177" t="n">
-        <v>9.619999999999999</v>
+        <v>8.117000000000001</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>9.042999999999999</v>
+        <v>9.032</v>
       </c>
       <c r="B178" t="n">
-        <v>64.8</v>
+        <v>52.2</v>
       </c>
       <c r="C178" t="n">
-        <v>0.1966787974389536</v>
+        <v>0.2254835638122936</v>
       </c>
       <c r="D178" t="n">
-        <v>32.22</v>
+        <v>46.81</v>
       </c>
       <c r="E178" t="n">
-        <v>9.186</v>
+        <v>9.381</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>8.522</v>
+        <v>8.449</v>
       </c>
       <c r="B179" t="n">
-        <v>61.9</v>
+        <v>54.1</v>
       </c>
       <c r="C179" t="n">
-        <v>0.2006391535872529</v>
+        <v>0.227671087871896</v>
       </c>
       <c r="D179" t="n">
-        <v>32.58</v>
+        <v>45.79</v>
       </c>
       <c r="E179" t="n">
-        <v>9.042999999999999</v>
+        <v>9.032</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>7.944</v>
+        <v>8.394</v>
       </c>
       <c r="B180" t="n">
-        <v>60.2</v>
+        <v>55.5</v>
       </c>
       <c r="C180" t="n">
-        <v>0.2048656117015703</v>
+        <v>0.2301800598464641</v>
       </c>
       <c r="D180" t="n">
-        <v>40.16</v>
+        <v>46.97</v>
       </c>
       <c r="E180" t="n">
-        <v>8.522</v>
+        <v>8.449</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>8.266999999999999</v>
+        <v>8.112</v>
       </c>
       <c r="B181" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.2089767211658702</v>
-      </c>
-      <c r="D181" t="n">
-        <v>40.99</v>
-      </c>
+        <v>56.3</v>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
-        <v>7.944</v>
+        <v>8.394</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>8.451000000000001</v>
+        <v>7.992</v>
       </c>
       <c r="B182" t="n">
-        <v>56.8</v>
+        <v>40.8</v>
       </c>
       <c r="C182" t="n">
-        <v>0.2126211591739718</v>
-      </c>
-      <c r="D182" t="n">
-        <v>42.16</v>
-      </c>
+        <v>0.156235835052645</v>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>8.266999999999999</v>
+        <v>7.766</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>8.113</v>
+        <v>7.786</v>
       </c>
       <c r="B183" t="n">
-        <v>55.6</v>
+        <v>39.2</v>
       </c>
       <c r="C183" t="n">
-        <v>0.2154252807318739</v>
-      </c>
-      <c r="D183" t="n">
-        <v>43.37</v>
-      </c>
+        <v>0.1578622749124926</v>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>8.451000000000001</v>
+        <v>7.992</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>8.073</v>
+        <v>7.207</v>
       </c>
       <c r="B184" t="n">
-        <v>54.9</v>
+        <v>41.2</v>
       </c>
       <c r="C184" t="n">
-        <v>0.2178685459165742</v>
-      </c>
-      <c r="D184" t="n">
-        <v>40.93</v>
-      </c>
+        <v>0.1594568652707418</v>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
-        <v>8.113</v>
+        <v>7.786</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>8.117000000000001</v>
+        <v>7.093</v>
       </c>
       <c r="B185" t="n">
-        <v>54.5</v>
+        <v>42.5</v>
       </c>
       <c r="C185" t="n">
-        <v>0.2203600339742307</v>
-      </c>
-      <c r="D185" t="n">
-        <v>44.14</v>
-      </c>
+        <v>0.1616555675577311</v>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="n">
-        <v>8.073</v>
+        <v>7.207</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>9.381</v>
+        <v>7.237</v>
       </c>
       <c r="B186" t="n">
-        <v>51.3</v>
+        <v>38.9</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2226230843401145</v>
-      </c>
-      <c r="D186" t="n">
-        <v>44.58</v>
-      </c>
+        <v>0.1635212927955657</v>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
-        <v>8.117000000000001</v>
+        <v>7.093</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>9.032</v>
+        <v>7.464</v>
       </c>
       <c r="B187" t="n">
-        <v>52.2</v>
+        <v>39.7</v>
       </c>
       <c r="C187" t="n">
-        <v>0.2254835638122936</v>
-      </c>
-      <c r="D187" t="n">
-        <v>46.81</v>
-      </c>
+        <v>0.1661103635153007</v>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
-        <v>9.381</v>
+        <v>7.237</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>8.449</v>
+        <v>7.493</v>
       </c>
       <c r="B188" t="n">
-        <v>54.1</v>
+        <v>39.5</v>
       </c>
       <c r="C188" t="n">
-        <v>0.227671087871896</v>
-      </c>
-      <c r="D188" t="n">
-        <v>45.79</v>
-      </c>
+        <v>0.1673524458221449</v>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="n">
-        <v>9.032</v>
+        <v>7.464</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>8.394</v>
+        <v>7.43</v>
       </c>
       <c r="B189" t="n">
-        <v>55.5</v>
+        <v>38.8</v>
       </c>
       <c r="C189" t="n">
-        <v>0.2301800598464641</v>
-      </c>
-      <c r="D189" t="n">
-        <v>46.97</v>
-      </c>
+        <v>0.1687400982186233</v>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="n">
-        <v>8.449</v>
+        <v>7.493</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>8.112</v>
+        <v>7.236</v>
       </c>
       <c r="B190" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="C190" t="inlineStr"/>
+        <v>39.4</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.1715394760112175</v>
+      </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
-        <v>8.394</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>7.766</v>
+        <v>7.042</v>
       </c>
       <c r="B191" t="n">
-        <v>39</v>
+        <v>40.3</v>
       </c>
       <c r="C191" t="n">
-        <v>0.1549006587298559</v>
+        <v>0.1749531000179996</v>
       </c>
       <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="n">
+        <v>7.236</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>7.992</v>
+        <v>6.85</v>
       </c>
       <c r="B192" t="n">
-        <v>40.8</v>
+        <v>41.4</v>
       </c>
       <c r="C192" t="n">
-        <v>0.156235835052645</v>
+        <v>0.178425462145031</v>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>7.766</v>
+        <v>7.042</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>7.786</v>
+        <v>6.968</v>
       </c>
       <c r="B193" t="n">
-        <v>39.2</v>
+        <v>41.9</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1578622749124926</v>
+        <v>0.1819223219803731</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="n">
-        <v>7.992</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>7.207</v>
+        <v>6.733</v>
       </c>
       <c r="B194" t="n">
-        <v>41.2</v>
+        <v>44.1</v>
       </c>
       <c r="C194" t="n">
-        <v>0.1594568652707418</v>
-      </c>
-      <c r="D194" t="inlineStr"/>
+        <v>0.1856813708866568</v>
+      </c>
+      <c r="D194" t="n">
+        <v>70.67</v>
+      </c>
       <c r="E194" t="n">
-        <v>7.786</v>
+        <v>6.968</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>7.093</v>
+        <v>6.555</v>
       </c>
       <c r="B195" t="n">
-        <v>42.5</v>
+        <v>45.9</v>
       </c>
       <c r="C195" t="n">
-        <v>0.1616555675577311</v>
-      </c>
-      <c r="D195" t="inlineStr"/>
+        <v>0.1883700831458395</v>
+      </c>
+      <c r="D195" t="n">
+        <v>73.15000000000001</v>
+      </c>
       <c r="E195" t="n">
-        <v>7.207</v>
+        <v>6.733</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>7.237</v>
+        <v>6.247</v>
       </c>
       <c r="B196" t="n">
-        <v>38.9</v>
+        <v>48</v>
       </c>
       <c r="C196" t="n">
-        <v>0.1635212927955657</v>
-      </c>
-      <c r="D196" t="inlineStr"/>
+        <v>0.192310483664788</v>
+      </c>
+      <c r="D196" t="n">
+        <v>75.31999999999999</v>
+      </c>
       <c r="E196" t="n">
-        <v>7.093</v>
+        <v>6.555</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>7.464</v>
+        <v>7.231</v>
       </c>
       <c r="B197" t="n">
-        <v>39.7</v>
+        <v>47.1</v>
       </c>
       <c r="C197" t="n">
-        <v>0.1661103635153007</v>
-      </c>
-      <c r="D197" t="inlineStr"/>
+        <v>0.197682699071643</v>
+      </c>
+      <c r="D197" t="n">
+        <v>66.56999999999999</v>
+      </c>
       <c r="E197" t="n">
-        <v>7.237</v>
+        <v>6.247</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>7.493</v>
+        <v>7.335</v>
       </c>
       <c r="B198" t="n">
-        <v>39.5</v>
+        <v>48.4</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1673524458221449</v>
-      </c>
-      <c r="D198" t="inlineStr"/>
+        <v>0.202040292138154</v>
+      </c>
+      <c r="D198" t="n">
+        <v>67.37</v>
+      </c>
       <c r="E198" t="n">
-        <v>7.464</v>
+        <v>7.231</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>7.43</v>
+        <v>6.647</v>
       </c>
       <c r="B199" t="n">
-        <v>38.8</v>
+        <v>48.6</v>
       </c>
       <c r="C199" t="n">
-        <v>0.1687400982186233</v>
-      </c>
-      <c r="D199" t="inlineStr"/>
+        <v>0.2043449166491769</v>
+      </c>
+      <c r="D199" t="n">
+        <v>69.2</v>
+      </c>
       <c r="E199" t="n">
-        <v>7.493</v>
+        <v>7.335</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>7.236</v>
+        <v>6.369</v>
       </c>
       <c r="B200" t="n">
-        <v>39.4</v>
+        <v>53.6</v>
       </c>
       <c r="C200" t="n">
-        <v>0.1715394760112175</v>
-      </c>
-      <c r="D200" t="inlineStr"/>
+        <v>0.2053733932904878</v>
+      </c>
+      <c r="D200" t="n">
+        <v>72.77</v>
+      </c>
       <c r="E200" t="n">
-        <v>7.43</v>
+        <v>6.647</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>7.042</v>
+        <v>6.497</v>
       </c>
       <c r="B201" t="n">
-        <v>40.3</v>
+        <v>53.9</v>
       </c>
       <c r="C201" t="n">
-        <v>0.1749531000179996</v>
+        <v>0.2069401344465465</v>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
-        <v>7.236</v>
+        <v>6.369</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>6.85</v>
+        <v>7.642</v>
       </c>
       <c r="B202" t="n">
-        <v>41.4</v>
+        <v>185.2</v>
       </c>
       <c r="C202" t="n">
-        <v>0.178425462145031</v>
-      </c>
-      <c r="D202" t="inlineStr"/>
+        <v>0.1110455795112062</v>
+      </c>
+      <c r="D202" t="n">
+        <v>245.88</v>
+      </c>
       <c r="E202" t="n">
-        <v>7.042</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>6.968</v>
+        <v>7.516</v>
       </c>
       <c r="B203" t="n">
-        <v>41.9</v>
+        <v>185.7</v>
       </c>
       <c r="C203" t="n">
-        <v>0.1819223219803731</v>
-      </c>
-      <c r="D203" t="inlineStr"/>
+        <v>0.1096663241571843</v>
+      </c>
+      <c r="D203" t="n">
+        <v>257.23</v>
+      </c>
       <c r="E203" t="n">
-        <v>6.85</v>
+        <v>7.642</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>6.733</v>
+        <v>7.808</v>
       </c>
       <c r="B204" t="n">
-        <v>44.1</v>
+        <v>181.5</v>
       </c>
       <c r="C204" t="n">
-        <v>0.1856813708866568</v>
+        <v>0.1080288600448191</v>
       </c>
       <c r="D204" t="n">
-        <v>70.67</v>
+        <v>277.84</v>
       </c>
       <c r="E204" t="n">
-        <v>6.968</v>
+        <v>7.516</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>6.555</v>
+        <v>9.125999999999999</v>
       </c>
       <c r="B205" t="n">
-        <v>45.9</v>
+        <v>164</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1883700831458395</v>
+        <v>0.1077643168717956</v>
       </c>
       <c r="D205" t="n">
-        <v>73.15000000000001</v>
+        <v>292.41</v>
       </c>
       <c r="E205" t="n">
-        <v>6.733</v>
+        <v>7.808</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>6.247</v>
+        <v>10.523</v>
       </c>
       <c r="B206" t="n">
-        <v>48</v>
+        <v>154.2</v>
       </c>
       <c r="C206" t="n">
-        <v>0.192310483664788</v>
+        <v>0.109439893907136</v>
       </c>
       <c r="D206" t="n">
-        <v>75.31999999999999</v>
+        <v>245.94</v>
       </c>
       <c r="E206" t="n">
-        <v>6.555</v>
+        <v>9.125999999999999</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>7.231</v>
+        <v>10.521</v>
       </c>
       <c r="B207" t="n">
-        <v>47.1</v>
+        <v>146.2</v>
       </c>
       <c r="C207" t="n">
-        <v>0.197682699071643</v>
+        <v>0.1121714641928612</v>
       </c>
       <c r="D207" t="n">
-        <v>66.56999999999999</v>
+        <v>252.51</v>
       </c>
       <c r="E207" t="n">
-        <v>6.247</v>
+        <v>10.523</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>7.335</v>
+        <v>10.489</v>
       </c>
       <c r="B208" t="n">
-        <v>48.4</v>
+        <v>146.1</v>
       </c>
       <c r="C208" t="n">
-        <v>0.202040292138154</v>
+        <v>0.1152655253987142</v>
       </c>
       <c r="D208" t="n">
-        <v>67.37</v>
+        <v>230.07</v>
       </c>
       <c r="E208" t="n">
-        <v>7.231</v>
+        <v>10.521</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>6.647</v>
+        <v>10.475</v>
       </c>
       <c r="B209" t="n">
-        <v>48.6</v>
+        <v>147.9</v>
       </c>
       <c r="C209" t="n">
-        <v>0.2043449166491769</v>
+        <v>0.118867048410788</v>
       </c>
       <c r="D209" t="n">
-        <v>69.2</v>
+        <v>223.02</v>
       </c>
       <c r="E209" t="n">
-        <v>7.335</v>
+        <v>10.489</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>6.369</v>
+        <v>10.033</v>
       </c>
       <c r="B210" t="n">
-        <v>53.6</v>
+        <v>150.8</v>
       </c>
       <c r="C210" t="n">
-        <v>0.2053733932904878</v>
+        <v>0.1223646513205948</v>
       </c>
       <c r="D210" t="n">
-        <v>72.77</v>
+        <v>218.23</v>
       </c>
       <c r="E210" t="n">
-        <v>6.647</v>
+        <v>10.475</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>6.497</v>
+        <v>9.231</v>
       </c>
       <c r="B211" t="n">
-        <v>53.9</v>
+        <v>160.6</v>
       </c>
       <c r="C211" t="n">
-        <v>0.2069401344465465</v>
-      </c>
-      <c r="D211" t="inlineStr"/>
+        <v>0.1259721095024162</v>
+      </c>
+      <c r="D211" t="n">
+        <v>166.26</v>
+      </c>
       <c r="E211" t="n">
-        <v>6.369</v>
+        <v>10.033</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>7.22</v>
+        <v>7.078</v>
       </c>
       <c r="B212" t="n">
-        <v>180.8</v>
+        <v>208.6</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1111344152464313</v>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
+        <v>0.1293093699005927</v>
+      </c>
+      <c r="D212" t="n">
+        <v>174.28</v>
+      </c>
+      <c r="E212" t="n">
+        <v>9.231</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>7.642</v>
+        <v>7.338</v>
       </c>
       <c r="B213" t="n">
-        <v>185.2</v>
+        <v>203.8</v>
       </c>
       <c r="C213" t="n">
-        <v>0.1110455795112062</v>
+        <v>0.1321373695963384</v>
       </c>
       <c r="D213" t="n">
-        <v>245.88</v>
+        <v>172.34</v>
       </c>
       <c r="E213" t="n">
-        <v>7.22</v>
+        <v>7.078</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>7.516</v>
+        <v>6.917</v>
       </c>
       <c r="B214" t="n">
-        <v>185.7</v>
+        <v>215.7</v>
       </c>
       <c r="C214" t="n">
-        <v>0.1096663241571843</v>
+        <v>0.1349824562938866</v>
       </c>
       <c r="D214" t="n">
-        <v>257.23</v>
+        <v>177.38</v>
       </c>
       <c r="E214" t="n">
-        <v>7.642</v>
+        <v>7.338</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>7.808</v>
+        <v>6.747</v>
       </c>
       <c r="B215" t="n">
-        <v>181.5</v>
+        <v>223.6</v>
       </c>
       <c r="C215" t="n">
-        <v>0.1080288600448191</v>
+        <v>0.1382262986865217</v>
       </c>
       <c r="D215" t="n">
-        <v>277.84</v>
+        <v>181.47</v>
       </c>
       <c r="E215" t="n">
-        <v>7.516</v>
+        <v>6.917</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>9.125999999999999</v>
+        <v>6.619</v>
       </c>
       <c r="B216" t="n">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="C216" t="n">
-        <v>0.1077643168717956</v>
+        <v>0.1408263568832003</v>
       </c>
       <c r="D216" t="n">
-        <v>292.41</v>
+        <v>181.64</v>
       </c>
       <c r="E216" t="n">
-        <v>7.808</v>
+        <v>6.747</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>10.523</v>
+        <v>6.973</v>
       </c>
       <c r="B217" t="n">
-        <v>154.2</v>
+        <v>248.5</v>
       </c>
       <c r="C217" t="n">
-        <v>0.109439893907136</v>
+        <v>0.1439165303435343</v>
       </c>
       <c r="D217" t="n">
-        <v>245.94</v>
+        <v>185.72</v>
       </c>
       <c r="E217" t="n">
-        <v>9.125999999999999</v>
+        <v>6.619</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>10.521</v>
+        <v>6.441</v>
       </c>
       <c r="B218" t="n">
-        <v>146.2</v>
+        <v>264.8</v>
       </c>
       <c r="C218" t="n">
-        <v>0.1121714641928612</v>
+        <v>0.146870478614804</v>
       </c>
       <c r="D218" t="n">
-        <v>252.51</v>
+        <v>229.78</v>
       </c>
       <c r="E218" t="n">
-        <v>10.523</v>
+        <v>6.973</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>10.489</v>
+        <v>6.021</v>
       </c>
       <c r="B219" t="n">
-        <v>146.1</v>
+        <v>277.1</v>
       </c>
       <c r="C219" t="n">
-        <v>0.1152655253987142</v>
+        <v>0.1500167724784679</v>
       </c>
       <c r="D219" t="n">
-        <v>230.07</v>
+        <v>172.5</v>
       </c>
       <c r="E219" t="n">
-        <v>10.521</v>
+        <v>6.441</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>10.475</v>
+        <v>6.575</v>
       </c>
       <c r="B220" t="n">
-        <v>147.9</v>
+        <v>258.2</v>
       </c>
       <c r="C220" t="n">
-        <v>0.118867048410788</v>
+        <v>0.1518601812233764</v>
       </c>
       <c r="D220" t="n">
-        <v>223.02</v>
+        <v>205.63</v>
       </c>
       <c r="E220" t="n">
-        <v>10.489</v>
+        <v>6.021</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>10.033</v>
+        <v>6.854</v>
       </c>
       <c r="B221" t="n">
-        <v>150.8</v>
+        <v>261.6</v>
       </c>
       <c r="C221" t="n">
-        <v>0.1223646513205948</v>
+        <v>0.1545886236492796</v>
       </c>
       <c r="D221" t="n">
-        <v>218.23</v>
+        <v>203.39</v>
       </c>
       <c r="E221" t="n">
-        <v>10.475</v>
+        <v>6.575</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>9.231</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="B222" t="n">
-        <v>160.6</v>
+        <v>116.6</v>
       </c>
       <c r="C222" t="n">
-        <v>0.1259721095024162</v>
+        <v>0.1949990048991489</v>
       </c>
       <c r="D222" t="n">
-        <v>166.26</v>
+        <v>86.53</v>
       </c>
       <c r="E222" t="n">
-        <v>10.033</v>
+        <v>8.137</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>7.078</v>
+        <v>8.398</v>
       </c>
       <c r="B223" t="n">
-        <v>208.6</v>
+        <v>114.5</v>
       </c>
       <c r="C223" t="n">
-        <v>0.1293093699005927</v>
+        <v>0.1982629963295302</v>
       </c>
       <c r="D223" t="n">
-        <v>174.28</v>
+        <v>86.41</v>
       </c>
       <c r="E223" t="n">
-        <v>9.231</v>
+        <v>8.308999999999999</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>7.338</v>
+        <v>8.102</v>
       </c>
       <c r="B224" t="n">
-        <v>203.8</v>
+        <v>111.8</v>
       </c>
       <c r="C224" t="n">
-        <v>0.1321373695963384</v>
+        <v>0.2005708867904132</v>
       </c>
       <c r="D224" t="n">
-        <v>172.34</v>
+        <v>88.06</v>
       </c>
       <c r="E224" t="n">
-        <v>7.078</v>
+        <v>8.398</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>6.917</v>
+        <v>8.502000000000001</v>
       </c>
       <c r="B225" t="n">
-        <v>215.7</v>
+        <v>109.3</v>
       </c>
       <c r="C225" t="n">
-        <v>0.1349824562938866</v>
+        <v>0.2015298727738146</v>
       </c>
       <c r="D225" t="n">
-        <v>177.38</v>
+        <v>88</v>
       </c>
       <c r="E225" t="n">
-        <v>7.338</v>
+        <v>8.102</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>6.747</v>
+        <v>8.913</v>
       </c>
       <c r="B226" t="n">
-        <v>223.6</v>
+        <v>109.8</v>
       </c>
       <c r="C226" t="n">
-        <v>0.1382262986865217</v>
+        <v>0.2024932198588664</v>
       </c>
       <c r="D226" t="n">
-        <v>181.47</v>
+        <v>88.03</v>
       </c>
       <c r="E226" t="n">
-        <v>6.917</v>
+        <v>8.502000000000001</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>6.619</v>
+        <v>8.879</v>
       </c>
       <c r="B227" t="n">
-        <v>231</v>
+        <v>107.8</v>
       </c>
       <c r="C227" t="n">
-        <v>0.1408263568832003</v>
+        <v>0.2036140669786369</v>
       </c>
       <c r="D227" t="n">
-        <v>181.64</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="E227" t="n">
-        <v>6.747</v>
+        <v>8.913</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>6.973</v>
+        <v>8.728999999999999</v>
       </c>
       <c r="B228" t="n">
-        <v>248.5</v>
+        <v>106.7</v>
       </c>
       <c r="C228" t="n">
-        <v>0.1439165303435343</v>
+        <v>0.2044174018241025</v>
       </c>
       <c r="D228" t="n">
-        <v>185.72</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="E228" t="n">
-        <v>6.619</v>
+        <v>8.879</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>6.441</v>
+        <v>8.798</v>
       </c>
       <c r="B229" t="n">
-        <v>264.8</v>
+        <v>104.4</v>
       </c>
       <c r="C229" t="n">
-        <v>0.146870478614804</v>
+        <v>0.2082882699720498</v>
       </c>
       <c r="D229" t="n">
-        <v>229.78</v>
+        <v>90.27</v>
       </c>
       <c r="E229" t="n">
-        <v>6.973</v>
+        <v>8.728999999999999</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>6.021</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="B230" t="n">
-        <v>277.1</v>
+        <v>102.4</v>
       </c>
       <c r="C230" t="n">
-        <v>0.1500167724784679</v>
+        <v>0.2113806208568468</v>
       </c>
       <c r="D230" t="n">
-        <v>172.5</v>
+        <v>89.48</v>
       </c>
       <c r="E230" t="n">
-        <v>6.441</v>
+        <v>8.798</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>6.575</v>
+        <v>8.859</v>
       </c>
       <c r="B231" t="n">
-        <v>258.2</v>
+        <v>101</v>
       </c>
       <c r="C231" t="n">
-        <v>0.1518601812233764</v>
+        <v>0.2150777823129277</v>
       </c>
       <c r="D231" t="n">
-        <v>205.63</v>
+        <v>89.38</v>
       </c>
       <c r="E231" t="n">
-        <v>6.021</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>6.854</v>
+        <v>8.846</v>
       </c>
       <c r="B232" t="n">
-        <v>261.6</v>
+        <v>99.3</v>
       </c>
       <c r="C232" t="n">
-        <v>0.1545886236492796</v>
+        <v>0.2186193274101381</v>
       </c>
       <c r="D232" t="n">
-        <v>203.39</v>
+        <v>89.62</v>
       </c>
       <c r="E232" t="n">
-        <v>6.575</v>
+        <v>8.859</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>8.137</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="B233" t="n">
-        <v>118.6</v>
+        <v>99.5</v>
       </c>
       <c r="C233" t="n">
-        <v>0.1919381712035984</v>
+        <v>0.2214155602633029</v>
       </c>
       <c r="D233" t="n">
-        <v>85.98999999999999</v>
-      </c>
-      <c r="E233" t="inlineStr"/>
+        <v>90.38</v>
+      </c>
+      <c r="E233" t="n">
+        <v>8.846</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>8.308999999999999</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="B234" t="n">
-        <v>116.6</v>
+        <v>98</v>
       </c>
       <c r="C234" t="n">
-        <v>0.1949990048991489</v>
+        <v>0.2241164801801943</v>
       </c>
       <c r="D234" t="n">
-        <v>86.53</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="E234" t="n">
-        <v>8.137</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>8.398</v>
+        <v>8.654999999999999</v>
       </c>
       <c r="B235" t="n">
-        <v>114.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C235" t="n">
-        <v>0.1982629963295302</v>
+        <v>0.2263205358878139</v>
       </c>
       <c r="D235" t="n">
-        <v>86.41</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="E235" t="n">
-        <v>8.308999999999999</v>
+        <v>8.691000000000001</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>8.102</v>
+        <v>8.615</v>
       </c>
       <c r="B236" t="n">
-        <v>111.8</v>
+        <v>95.3</v>
       </c>
       <c r="C236" t="n">
-        <v>0.2005708867904132</v>
+        <v>0.2289197027056319</v>
       </c>
       <c r="D236" t="n">
-        <v>88.06</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="E236" t="n">
-        <v>8.398</v>
+        <v>8.654999999999999</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>8.502000000000001</v>
+        <v>9.564</v>
       </c>
       <c r="B237" t="n">
-        <v>109.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C237" t="n">
-        <v>0.2015298727738146</v>
+        <v>0.2323733103372605</v>
       </c>
       <c r="D237" t="n">
-        <v>88</v>
+        <v>84.72</v>
       </c>
       <c r="E237" t="n">
-        <v>8.102</v>
+        <v>8.615</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>8.913</v>
+        <v>9.282</v>
       </c>
       <c r="B238" t="n">
-        <v>109.8</v>
+        <v>93.7</v>
       </c>
       <c r="C238" t="n">
-        <v>0.2024932198588664</v>
+        <v>0.235354866456436</v>
       </c>
       <c r="D238" t="n">
-        <v>88.03</v>
+        <v>109.39</v>
       </c>
       <c r="E238" t="n">
-        <v>8.502000000000001</v>
+        <v>9.564</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>8.879</v>
+        <v>8.85</v>
       </c>
       <c r="B239" t="n">
-        <v>107.8</v>
+        <v>93.7</v>
       </c>
       <c r="C239" t="n">
-        <v>0.2036140669786369</v>
+        <v>0.2380378170586199</v>
       </c>
       <c r="D239" t="n">
-        <v>88.51000000000001</v>
+        <v>104.89</v>
       </c>
       <c r="E239" t="n">
-        <v>8.913</v>
+        <v>9.282</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>8.728999999999999</v>
+        <v>8.406000000000001</v>
       </c>
       <c r="B240" t="n">
-        <v>106.7</v>
+        <v>94.7</v>
       </c>
       <c r="C240" t="n">
-        <v>0.2044174018241025</v>
+        <v>0.2403723695298697</v>
       </c>
       <c r="D240" t="n">
-        <v>90.04000000000001</v>
+        <v>100.42</v>
       </c>
       <c r="E240" t="n">
-        <v>8.879</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>8.798</v>
+        <v>8.444000000000001</v>
       </c>
       <c r="B241" t="n">
-        <v>104.4</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="C241" t="n">
-        <v>0.2082882699720498</v>
-      </c>
-      <c r="D241" t="n">
-        <v>90.27</v>
-      </c>
+        <v>0.2434532228681681</v>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="n">
-        <v>8.728999999999999</v>
+        <v>8.406000000000001</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>8.789999999999999</v>
+        <v>6.082</v>
       </c>
       <c r="B242" t="n">
-        <v>102.4</v>
+        <v>26.7</v>
       </c>
       <c r="C242" t="n">
-        <v>0.2113806208568468</v>
+        <v>0.1663932998003311</v>
       </c>
       <c r="D242" t="n">
-        <v>89.48</v>
+        <v>67.81</v>
       </c>
       <c r="E242" t="n">
-        <v>8.798</v>
+        <v>6.475</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>8.859</v>
+        <v>6.021</v>
       </c>
       <c r="B243" t="n">
-        <v>101</v>
+        <v>31.8</v>
       </c>
       <c r="C243" t="n">
-        <v>0.2150777823129277</v>
+        <v>0.1700006373789541</v>
       </c>
       <c r="D243" t="n">
-        <v>89.38</v>
+        <v>67.92</v>
       </c>
       <c r="E243" t="n">
-        <v>8.789999999999999</v>
+        <v>6.082</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>8.846</v>
+        <v>5.818</v>
       </c>
       <c r="B244" t="n">
-        <v>99.3</v>
+        <v>39.8</v>
       </c>
       <c r="C244" t="n">
-        <v>0.2186193274101381</v>
+        <v>0.1739456004056428</v>
       </c>
       <c r="D244" t="n">
-        <v>89.62</v>
+        <v>68.28</v>
       </c>
       <c r="E244" t="n">
-        <v>8.859</v>
+        <v>6.021</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>8.720000000000001</v>
+        <v>5.866</v>
       </c>
       <c r="B245" t="n">
-        <v>99.5</v>
+        <v>42.2</v>
       </c>
       <c r="C245" t="n">
-        <v>0.2214155602633029</v>
+        <v>0.1759618762575223</v>
       </c>
       <c r="D245" t="n">
-        <v>90.38</v>
+        <v>68.91</v>
       </c>
       <c r="E245" t="n">
-        <v>8.846</v>
+        <v>5.818</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>8.691000000000001</v>
+        <v>6.268</v>
       </c>
       <c r="B246" t="n">
-        <v>98</v>
+        <v>35.5</v>
       </c>
       <c r="C246" t="n">
-        <v>0.2241164801801943</v>
+        <v>0.1782249585497546</v>
       </c>
       <c r="D246" t="n">
-        <v>89.76000000000001</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="E246" t="n">
-        <v>8.720000000000001</v>
+        <v>5.866</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>8.654999999999999</v>
+        <v>6.224</v>
       </c>
       <c r="B247" t="n">
-        <v>96.90000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="C247" t="n">
-        <v>0.2263205358878139</v>
+        <v>0.1811724948408492</v>
       </c>
       <c r="D247" t="n">
-        <v>88.59999999999999</v>
+        <v>68.28</v>
       </c>
       <c r="E247" t="n">
-        <v>8.691000000000001</v>
+        <v>6.268</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>8.615</v>
+        <v>5.918</v>
       </c>
       <c r="B248" t="n">
-        <v>95.3</v>
+        <v>35.7</v>
       </c>
       <c r="C248" t="n">
-        <v>0.2289197027056319</v>
+        <v>0.1837169003256041</v>
       </c>
       <c r="D248" t="n">
-        <v>87.98999999999999</v>
+        <v>69.17</v>
       </c>
       <c r="E248" t="n">
-        <v>8.654999999999999</v>
+        <v>6.224</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>9.564</v>
+        <v>5.621</v>
       </c>
       <c r="B249" t="n">
-        <v>92.09999999999999</v>
+        <v>40.3</v>
       </c>
       <c r="C249" t="n">
-        <v>0.2323733103372605</v>
+        <v>0.1856140390343763</v>
       </c>
       <c r="D249" t="n">
-        <v>84.72</v>
+        <v>69.69</v>
       </c>
       <c r="E249" t="n">
-        <v>8.615</v>
+        <v>5.918</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>9.282</v>
+        <v>5.604</v>
       </c>
       <c r="B250" t="n">
-        <v>93.7</v>
+        <v>41.6</v>
       </c>
       <c r="C250" t="n">
-        <v>0.235354866456436</v>
+        <v>0.1876565414499771</v>
       </c>
       <c r="D250" t="n">
-        <v>109.39</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="E250" t="n">
-        <v>9.564</v>
+        <v>5.621</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>8.85</v>
+        <v>5.664</v>
       </c>
       <c r="B251" t="n">
-        <v>93.7</v>
+        <v>42.6</v>
       </c>
       <c r="C251" t="n">
-        <v>0.2380378170586199</v>
+        <v>0.1906675500182866</v>
       </c>
       <c r="D251" t="n">
-        <v>104.89</v>
+        <v>72.61</v>
       </c>
       <c r="E251" t="n">
-        <v>9.282</v>
+        <v>5.604</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>8.406000000000001</v>
+        <v>5.849</v>
       </c>
       <c r="B252" t="n">
-        <v>94.7</v>
+        <v>43.2</v>
       </c>
       <c r="C252" t="n">
-        <v>0.2403723695298697</v>
+        <v>0.1938858947402341</v>
       </c>
       <c r="D252" t="n">
-        <v>100.42</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="E252" t="n">
-        <v>8.85</v>
+        <v>5.664</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>8.444000000000001</v>
+        <v>6.352</v>
       </c>
       <c r="B253" t="n">
-        <v>93.40000000000001</v>
+        <v>43.9</v>
       </c>
       <c r="C253" t="n">
-        <v>0.2434532228681681</v>
-      </c>
-      <c r="D253" t="inlineStr"/>
+        <v>0.1963399911729916</v>
+      </c>
+      <c r="D253" t="n">
+        <v>73.54000000000001</v>
+      </c>
       <c r="E253" t="n">
-        <v>8.406000000000001</v>
+        <v>5.849</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>6.475</v>
+        <v>6.187</v>
       </c>
       <c r="B254" t="n">
-        <v>23.3</v>
+        <v>45.2</v>
       </c>
       <c r="C254" t="n">
-        <v>0.162418955247483</v>
-      </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
+        <v>0.1989158593642635</v>
+      </c>
+      <c r="D254" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="E254" t="n">
+        <v>6.352</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>6.082</v>
+        <v>6.409</v>
       </c>
       <c r="B255" t="n">
-        <v>26.7</v>
+        <v>47.7</v>
       </c>
       <c r="C255" t="n">
-        <v>0.1663932998003311</v>
+        <v>0.20102368770546</v>
       </c>
       <c r="D255" t="n">
-        <v>67.81</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="E255" t="n">
-        <v>6.475</v>
+        <v>6.187</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>6.021</v>
+        <v>6.863</v>
       </c>
       <c r="B256" t="n">
-        <v>31.8</v>
+        <v>48.8</v>
       </c>
       <c r="C256" t="n">
-        <v>0.1700006373789541</v>
+        <v>0.2025966057767629</v>
       </c>
       <c r="D256" t="n">
-        <v>67.92</v>
+        <v>71.53</v>
       </c>
       <c r="E256" t="n">
-        <v>6.082</v>
+        <v>6.409</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>5.818</v>
+        <v>7.506</v>
       </c>
       <c r="B257" t="n">
-        <v>39.8</v>
+        <v>50.4</v>
       </c>
       <c r="C257" t="n">
-        <v>0.1739456004056428</v>
+        <v>0.2051780308490702</v>
       </c>
       <c r="D257" t="n">
-        <v>68.28</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="E257" t="n">
-        <v>6.021</v>
+        <v>6.863</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>5.866</v>
+        <v>9.411</v>
       </c>
       <c r="B258" t="n">
-        <v>42.2</v>
+        <v>51.5</v>
       </c>
       <c r="C258" t="n">
-        <v>0.1759618762575223</v>
+        <v>0.2079512027901626</v>
       </c>
       <c r="D258" t="n">
-        <v>68.91</v>
+        <v>76.84</v>
       </c>
       <c r="E258" t="n">
-        <v>5.818</v>
+        <v>7.506</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>6.268</v>
+        <v>8.103999999999999</v>
       </c>
       <c r="B259" t="n">
-        <v>35.5</v>
+        <v>52.9</v>
       </c>
       <c r="C259" t="n">
-        <v>0.1782249585497546</v>
+        <v>0.2087813080265727</v>
       </c>
       <c r="D259" t="n">
-        <v>68.48999999999999</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="E259" t="n">
-        <v>5.866</v>
+        <v>9.411</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>6.224</v>
+        <v>7.278</v>
       </c>
       <c r="B260" t="n">
-        <v>33.4</v>
+        <v>54.8</v>
       </c>
       <c r="C260" t="n">
-        <v>0.1811724948408492</v>
+        <v>0.2097272024335531</v>
       </c>
       <c r="D260" t="n">
-        <v>68.28</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="E260" t="n">
-        <v>6.268</v>
+        <v>8.103999999999999</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>5.918</v>
+        <v>7.589</v>
       </c>
       <c r="B261" t="n">
-        <v>35.7</v>
+        <v>54.2</v>
       </c>
       <c r="C261" t="n">
-        <v>0.1837169003256041</v>
-      </c>
-      <c r="D261" t="n">
-        <v>69.17</v>
-      </c>
+        <v>0.2133953956499395</v>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="n">
-        <v>6.224</v>
+        <v>7.278</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>5.621</v>
+        <v>5.646</v>
       </c>
       <c r="B262" t="n">
-        <v>40.3</v>
+        <v>28.6</v>
       </c>
       <c r="C262" t="n">
-        <v>0.1856140390343763</v>
+        <v>0.1582972204505219</v>
       </c>
       <c r="D262" t="n">
-        <v>69.69</v>
+        <v>83.03</v>
       </c>
       <c r="E262" t="n">
-        <v>5.918</v>
+        <v>5.483</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>5.604</v>
+        <v>5.857</v>
       </c>
       <c r="B263" t="n">
-        <v>41.6</v>
+        <v>31.5</v>
       </c>
       <c r="C263" t="n">
-        <v>0.1876565414499771</v>
+        <v>0.1629075622333643</v>
       </c>
       <c r="D263" t="n">
-        <v>70.68000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="E263" t="n">
-        <v>5.621</v>
+        <v>5.646</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>5.664</v>
+        <v>5.76</v>
       </c>
       <c r="B264" t="n">
-        <v>42.6</v>
+        <v>36.4</v>
       </c>
       <c r="C264" t="n">
-        <v>0.1906675500182866</v>
+        <v>0.1664854862317741</v>
       </c>
       <c r="D264" t="n">
-        <v>72.61</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E264" t="n">
-        <v>5.604</v>
+        <v>5.857</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>5.849</v>
+        <v>6.29</v>
       </c>
       <c r="B265" t="n">
-        <v>43.2</v>
+        <v>40.2</v>
       </c>
       <c r="C265" t="n">
-        <v>0.1938858947402341</v>
+        <v>0.1699359242732922</v>
       </c>
       <c r="D265" t="n">
-        <v>71.81999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="E265" t="n">
-        <v>5.664</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>6.352</v>
+        <v>7.345</v>
       </c>
       <c r="B266" t="n">
-        <v>43.9</v>
+        <v>35.2</v>
       </c>
       <c r="C266" t="n">
-        <v>0.1963399911729916</v>
+        <v>0.1720395017865129</v>
       </c>
       <c r="D266" t="n">
-        <v>73.54000000000001</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="E266" t="n">
-        <v>5.849</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>6.187</v>
+        <v>6.906</v>
       </c>
       <c r="B267" t="n">
-        <v>45.2</v>
+        <v>35.6</v>
       </c>
       <c r="C267" t="n">
-        <v>0.1989158593642635</v>
+        <v>0.173424621957647</v>
       </c>
       <c r="D267" t="n">
-        <v>73.65000000000001</v>
+        <v>84.67</v>
       </c>
       <c r="E267" t="n">
-        <v>6.352</v>
+        <v>7.345</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>6.409</v>
+        <v>6.54</v>
       </c>
       <c r="B268" t="n">
-        <v>47.7</v>
+        <v>39.6</v>
       </c>
       <c r="C268" t="n">
-        <v>0.20102368770546</v>
+        <v>0.1786376019299034</v>
       </c>
       <c r="D268" t="n">
-        <v>73.48999999999999</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E268" t="n">
-        <v>6.187</v>
+        <v>6.906</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>6.863</v>
+        <v>6.308</v>
       </c>
       <c r="B269" t="n">
-        <v>48.8</v>
+        <v>42.8</v>
       </c>
       <c r="C269" t="n">
-        <v>0.2025966057767629</v>
+        <v>0.1808914580670593</v>
       </c>
       <c r="D269" t="n">
-        <v>71.53</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E269" t="n">
-        <v>6.409</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>7.506</v>
+        <v>6.155</v>
       </c>
       <c r="B270" t="n">
-        <v>50.4</v>
+        <v>44.9</v>
       </c>
       <c r="C270" t="n">
-        <v>0.2051780308490702</v>
+        <v>0.1821936592599366</v>
       </c>
       <c r="D270" t="n">
-        <v>74.51000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="E270" t="n">
-        <v>6.863</v>
+        <v>6.308</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>9.411</v>
+        <v>6.222</v>
       </c>
       <c r="B271" t="n">
-        <v>51.5</v>
+        <v>46.2</v>
       </c>
       <c r="C271" t="n">
-        <v>0.2079512027901626</v>
+        <v>0.1838905620412353</v>
       </c>
       <c r="D271" t="n">
-        <v>76.84</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="E271" t="n">
-        <v>7.506</v>
+        <v>6.155</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>8.103999999999999</v>
+        <v>6.474</v>
       </c>
       <c r="B272" t="n">
-        <v>52.9</v>
+        <v>46.3</v>
       </c>
       <c r="C272" t="n">
-        <v>0.2087813080265727</v>
+        <v>0.18664620637153</v>
       </c>
       <c r="D272" t="n">
-        <v>76.34999999999999</v>
+        <v>100.24</v>
       </c>
       <c r="E272" t="n">
-        <v>9.411</v>
+        <v>6.222</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>7.278</v>
+        <v>6.649</v>
       </c>
       <c r="B273" t="n">
-        <v>54.8</v>
+        <v>47.4</v>
       </c>
       <c r="C273" t="n">
-        <v>0.2097272024335531</v>
+        <v>0.1891787912098918</v>
       </c>
       <c r="D273" t="n">
-        <v>75.79000000000001</v>
+        <v>102.16</v>
       </c>
       <c r="E273" t="n">
-        <v>8.103999999999999</v>
+        <v>6.474</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>7.589</v>
+        <v>6.464</v>
       </c>
       <c r="B274" t="n">
-        <v>54.2</v>
+        <v>50.2</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2133953956499395</v>
-      </c>
-      <c r="D274" t="inlineStr"/>
+        <v>0.1921571192381318</v>
+      </c>
+      <c r="D274" t="n">
+        <v>105.65</v>
+      </c>
       <c r="E274" t="n">
-        <v>7.278</v>
+        <v>6.649</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>5.483</v>
+        <v>6.469</v>
       </c>
       <c r="B275" t="n">
-        <v>25.5</v>
+        <v>53.2</v>
       </c>
       <c r="C275" t="n">
-        <v>0.1542079872806993</v>
+        <v>0.1950753662161206</v>
       </c>
       <c r="D275" t="n">
-        <v>82.89</v>
-      </c>
-      <c r="E275" t="inlineStr"/>
+        <v>102.55</v>
+      </c>
+      <c r="E275" t="n">
+        <v>6.464</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>5.646</v>
+        <v>6.945</v>
       </c>
       <c r="B276" t="n">
-        <v>28.6</v>
+        <v>55.3</v>
       </c>
       <c r="C276" t="n">
-        <v>0.1582972204505219</v>
+        <v>0.196378280349904</v>
       </c>
       <c r="D276" t="n">
-        <v>83.03</v>
+        <v>102.56</v>
       </c>
       <c r="E276" t="n">
-        <v>5.483</v>
+        <v>6.469</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>5.857</v>
+        <v>7.416</v>
       </c>
       <c r="B277" t="n">
-        <v>31.5</v>
+        <v>58.6</v>
       </c>
       <c r="C277" t="n">
-        <v>0.1629075622333643</v>
+        <v>0.1980471726281034</v>
       </c>
       <c r="D277" t="n">
-        <v>85.8</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="E277" t="n">
-        <v>5.646</v>
+        <v>6.945</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>5.76</v>
+        <v>7.732</v>
       </c>
       <c r="B278" t="n">
-        <v>36.4</v>
+        <v>60.7</v>
       </c>
       <c r="C278" t="n">
-        <v>0.1664854862317741</v>
+        <v>0.1992129533603177</v>
       </c>
       <c r="D278" t="n">
-        <v>89.04000000000001</v>
+        <v>102.23</v>
       </c>
       <c r="E278" t="n">
-        <v>5.857</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>6.29</v>
+        <v>7.244</v>
       </c>
       <c r="B279" t="n">
-        <v>40.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="C279" t="n">
-        <v>0.1699359242732922</v>
+        <v>0.199796293511257</v>
       </c>
       <c r="D279" t="n">
-        <v>83.59999999999999</v>
+        <v>104.22</v>
       </c>
       <c r="E279" t="n">
-        <v>5.76</v>
+        <v>7.732</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>7.345</v>
+        <v>7.319</v>
       </c>
       <c r="B280" t="n">
-        <v>35.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C280" t="n">
-        <v>0.1720395017865129</v>
+        <v>0.2000735664945565</v>
       </c>
       <c r="D280" t="n">
-        <v>84.73999999999999</v>
+        <v>105.93</v>
       </c>
       <c r="E280" t="n">
-        <v>6.29</v>
+        <v>7.244</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>6.906</v>
+        <v>7.596</v>
       </c>
       <c r="B281" t="n">
-        <v>35.6</v>
+        <v>68.5</v>
       </c>
       <c r="C281" t="n">
-        <v>0.173424621957647</v>
-      </c>
-      <c r="D281" t="n">
-        <v>84.67</v>
-      </c>
+        <v>0.2033978414292154</v>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="n">
-        <v>7.345</v>
+        <v>7.319</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>6.54</v>
+        <v>7.125</v>
       </c>
       <c r="B282" t="n">
-        <v>39.6</v>
+        <v>294.1</v>
       </c>
       <c r="C282" t="n">
-        <v>0.1786376019299034</v>
+        <v>0.1408299546863821</v>
       </c>
       <c r="D282" t="n">
-        <v>95.26000000000001</v>
+        <v>59.29</v>
       </c>
       <c r="E282" t="n">
-        <v>6.906</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>6.308</v>
+        <v>6.638</v>
       </c>
       <c r="B283" t="n">
-        <v>42.8</v>
+        <v>309.8</v>
       </c>
       <c r="C283" t="n">
-        <v>0.1808914580670593</v>
+        <v>0.1406991468515368</v>
       </c>
       <c r="D283" t="n">
-        <v>95.90000000000001</v>
+        <v>59.46</v>
       </c>
       <c r="E283" t="n">
-        <v>6.54</v>
+        <v>7.125</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>6.155</v>
+        <v>6.158</v>
       </c>
       <c r="B284" t="n">
-        <v>44.9</v>
+        <v>317.3</v>
       </c>
       <c r="C284" t="n">
-        <v>0.1821936592599366</v>
+        <v>0.1403419244960488</v>
       </c>
       <c r="D284" t="n">
-        <v>96.33</v>
+        <v>63.85</v>
       </c>
       <c r="E284" t="n">
-        <v>6.308</v>
+        <v>6.638</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>6.222</v>
+        <v>6.231</v>
       </c>
       <c r="B285" t="n">
-        <v>46.2</v>
+        <v>322.1</v>
       </c>
       <c r="C285" t="n">
-        <v>0.1838905620412353</v>
+        <v>0.1399196773866833</v>
       </c>
       <c r="D285" t="n">
-        <v>98.45999999999999</v>
+        <v>64.67</v>
       </c>
       <c r="E285" t="n">
-        <v>6.155</v>
+        <v>6.158</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>6.474</v>
+        <v>6.95</v>
       </c>
       <c r="B286" t="n">
-        <v>46.3</v>
+        <v>323.5</v>
       </c>
       <c r="C286" t="n">
-        <v>0.18664620637153</v>
+        <v>0.1395987841945289</v>
       </c>
       <c r="D286" t="n">
-        <v>100.24</v>
+        <v>64.34</v>
       </c>
       <c r="E286" t="n">
-        <v>6.222</v>
+        <v>6.231</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>6.649</v>
+        <v>6.662</v>
       </c>
       <c r="B287" t="n">
-        <v>47.4</v>
+        <v>332.9</v>
       </c>
       <c r="C287" t="n">
-        <v>0.1891787912098918</v>
+        <v>0.1395155218636594</v>
       </c>
       <c r="D287" t="n">
-        <v>102.16</v>
+        <v>67.44</v>
       </c>
       <c r="E287" t="n">
-        <v>6.474</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>6.464</v>
+        <v>5.952</v>
       </c>
       <c r="B288" t="n">
-        <v>50.2</v>
+        <v>329.8</v>
       </c>
       <c r="C288" t="n">
-        <v>0.1921571192381318</v>
+        <v>0.138879337292904</v>
       </c>
       <c r="D288" t="n">
-        <v>105.65</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="E288" t="n">
-        <v>6.649</v>
+        <v>6.662</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>6.469</v>
+        <v>5.294</v>
       </c>
       <c r="B289" t="n">
-        <v>53.2</v>
+        <v>336.9</v>
       </c>
       <c r="C289" t="n">
-        <v>0.1950753662161206</v>
+        <v>0.1395838453814687</v>
       </c>
       <c r="D289" t="n">
-        <v>102.55</v>
+        <v>71.84</v>
       </c>
       <c r="E289" t="n">
-        <v>6.464</v>
+        <v>5.952</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>6.945</v>
+        <v>5.236</v>
       </c>
       <c r="B290" t="n">
-        <v>55.3</v>
+        <v>342.9</v>
       </c>
       <c r="C290" t="n">
-        <v>0.196378280349904</v>
+        <v>0.1397607994950087</v>
       </c>
       <c r="D290" t="n">
-        <v>102.56</v>
+        <v>84.05</v>
       </c>
       <c r="E290" t="n">
-        <v>6.469</v>
+        <v>5.294</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>7.416</v>
+        <v>5.23</v>
       </c>
       <c r="B291" t="n">
-        <v>58.6</v>
+        <v>345.5</v>
       </c>
       <c r="C291" t="n">
-        <v>0.1980471726281034</v>
+        <v>0.1407618978314656</v>
       </c>
       <c r="D291" t="n">
-        <v>97.06999999999999</v>
+        <v>88.61</v>
       </c>
       <c r="E291" t="n">
-        <v>6.945</v>
+        <v>5.236</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>7.732</v>
+        <v>5.081</v>
       </c>
       <c r="B292" t="n">
-        <v>60.7</v>
+        <v>342.1</v>
       </c>
       <c r="C292" t="n">
-        <v>0.1992129533603177</v>
+        <v>0.141822302907144</v>
       </c>
       <c r="D292" t="n">
-        <v>102.23</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="E292" t="n">
-        <v>7.416</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>7.244</v>
+        <v>5.071</v>
       </c>
       <c r="B293" t="n">
-        <v>65.59999999999999</v>
+        <v>337.7</v>
       </c>
       <c r="C293" t="n">
-        <v>0.199796293511257</v>
+        <v>0.142224975661563</v>
       </c>
       <c r="D293" t="n">
-        <v>104.22</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="E293" t="n">
-        <v>7.732</v>
+        <v>5.081</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>7.319</v>
+        <v>5.135</v>
       </c>
       <c r="B294" t="n">
-        <v>67.40000000000001</v>
+        <v>328.6</v>
       </c>
       <c r="C294" t="n">
-        <v>0.2000735664945565</v>
+        <v>0.1424338925316634</v>
       </c>
       <c r="D294" t="n">
-        <v>105.93</v>
+        <v>98.39</v>
       </c>
       <c r="E294" t="n">
-        <v>7.244</v>
+        <v>5.071</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>7.596</v>
+        <v>5.274</v>
       </c>
       <c r="B295" t="n">
-        <v>68.5</v>
+        <v>322.7</v>
       </c>
       <c r="C295" t="n">
-        <v>0.2033978414292154</v>
-      </c>
-      <c r="D295" t="inlineStr"/>
+        <v>0.143201468426342</v>
+      </c>
+      <c r="D295" t="n">
+        <v>101.81</v>
+      </c>
       <c r="E295" t="n">
-        <v>7.319</v>
+        <v>5.135</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>7.28</v>
+        <v>5.466</v>
       </c>
       <c r="B296" t="n">
-        <v>289.3</v>
+        <v>316.8</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1398760330578512</v>
+        <v>0.1438815170045643</v>
       </c>
       <c r="D296" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="E296" t="inlineStr"/>
+        <v>107.1</v>
+      </c>
+      <c r="E296" t="n">
+        <v>5.274</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>7.125</v>
+        <v>5.767</v>
       </c>
       <c r="B297" t="n">
-        <v>294.1</v>
+        <v>334.9</v>
       </c>
       <c r="C297" t="n">
-        <v>0.1408299546863821</v>
+        <v>0.1450021402058431</v>
       </c>
       <c r="D297" t="n">
-        <v>59.29</v>
+        <v>110.09</v>
       </c>
       <c r="E297" t="n">
-        <v>7.28</v>
+        <v>5.466</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>6.638</v>
+        <v>5.608</v>
       </c>
       <c r="B298" t="n">
-        <v>309.8</v>
+        <v>342.5</v>
       </c>
       <c r="C298" t="n">
-        <v>0.1406991468515368</v>
+        <v>0.1461046429190364</v>
       </c>
       <c r="D298" t="n">
-        <v>59.46</v>
+        <v>114.99</v>
       </c>
       <c r="E298" t="n">
-        <v>7.125</v>
+        <v>5.767</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>6.158</v>
+        <v>5.609</v>
       </c>
       <c r="B299" t="n">
-        <v>317.3</v>
+        <v>324</v>
       </c>
       <c r="C299" t="n">
-        <v>0.1403419244960488</v>
+        <v>0.1475045592092929</v>
       </c>
       <c r="D299" t="n">
-        <v>63.85</v>
+        <v>115.6</v>
       </c>
       <c r="E299" t="n">
-        <v>6.638</v>
+        <v>5.608</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>6.231</v>
+        <v>5.668</v>
       </c>
       <c r="B300" t="n">
-        <v>322.1</v>
+        <v>320.4</v>
       </c>
       <c r="C300" t="n">
-        <v>0.1399196773866833</v>
+        <v>0.1486359901272531</v>
       </c>
       <c r="D300" t="n">
-        <v>64.67</v>
+        <v>116.89</v>
       </c>
       <c r="E300" t="n">
-        <v>6.158</v>
+        <v>5.609</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>6.95</v>
+        <v>5.891</v>
       </c>
       <c r="B301" t="n">
-        <v>323.5</v>
+        <v>318</v>
       </c>
       <c r="C301" t="n">
-        <v>0.1395987841945289</v>
-      </c>
-      <c r="D301" t="n">
-        <v>64.34</v>
-      </c>
+        <v>0.1503310765568038</v>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="n">
-        <v>6.231</v>
+        <v>5.668</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>6.662</v>
+        <v>5.791</v>
       </c>
       <c r="B302" t="n">
-        <v>332.9</v>
+        <v>29.3</v>
       </c>
       <c r="C302" t="n">
-        <v>0.1395155218636594</v>
-      </c>
-      <c r="D302" t="n">
-        <v>67.44</v>
-      </c>
+        <v>0.1314584452937464</v>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="n">
-        <v>6.95</v>
+        <v>5.842</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>5.952</v>
+        <v>5.781</v>
       </c>
       <c r="B303" t="n">
-        <v>329.8</v>
+        <v>31</v>
       </c>
       <c r="C303" t="n">
-        <v>0.138879337292904</v>
-      </c>
-      <c r="D303" t="n">
-        <v>69.06999999999999</v>
-      </c>
+        <v>0.1330244957321785</v>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="n">
-        <v>6.662</v>
+        <v>5.791</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>5.294</v>
+        <v>5.864</v>
       </c>
       <c r="B304" t="n">
-        <v>336.9</v>
+        <v>33.4</v>
       </c>
       <c r="C304" t="n">
-        <v>0.1395838453814687</v>
-      </c>
-      <c r="D304" t="n">
-        <v>71.84</v>
-      </c>
+        <v>0.134201854880302</v>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="n">
-        <v>5.952</v>
+        <v>5.781</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>5.236</v>
+        <v>6.352</v>
       </c>
       <c r="B305" t="n">
-        <v>342.9</v>
+        <v>38</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1397607994950087</v>
+        <v>0.1346265172347489</v>
       </c>
       <c r="D305" t="n">
-        <v>84.05</v>
+        <v>45.01</v>
       </c>
       <c r="E305" t="n">
-        <v>5.294</v>
+        <v>5.864</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>5.23</v>
+        <v>6.57</v>
       </c>
       <c r="B306" t="n">
-        <v>345.5</v>
+        <v>34.4</v>
       </c>
       <c r="C306" t="n">
-        <v>0.1407618978314656</v>
+        <v>0.134946080693151</v>
       </c>
       <c r="D306" t="n">
-        <v>88.61</v>
+        <v>44.6</v>
       </c>
       <c r="E306" t="n">
-        <v>5.236</v>
+        <v>6.352</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>5.081</v>
+        <v>6.435</v>
       </c>
       <c r="B307" t="n">
-        <v>342.1</v>
+        <v>37.8</v>
       </c>
       <c r="C307" t="n">
-        <v>0.141822302907144</v>
+        <v>0.1357045676905654</v>
       </c>
       <c r="D307" t="n">
-        <v>90.56999999999999</v>
+        <v>46.04</v>
       </c>
       <c r="E307" t="n">
-        <v>5.23</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>5.071</v>
+        <v>6.245</v>
       </c>
       <c r="B308" t="n">
-        <v>337.7</v>
+        <v>38.5</v>
       </c>
       <c r="C308" t="n">
-        <v>0.142224975661563</v>
+        <v>0.1361312662958016</v>
       </c>
       <c r="D308" t="n">
-        <v>94.31999999999999</v>
+        <v>38.25</v>
       </c>
       <c r="E308" t="n">
-        <v>5.081</v>
+        <v>6.435</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>5.135</v>
+        <v>6.229</v>
       </c>
       <c r="B309" t="n">
-        <v>328.6</v>
+        <v>39.2</v>
       </c>
       <c r="C309" t="n">
-        <v>0.1424338925316634</v>
+        <v>0.1396397132476974</v>
       </c>
       <c r="D309" t="n">
-        <v>98.39</v>
+        <v>33.3</v>
       </c>
       <c r="E309" t="n">
-        <v>5.071</v>
+        <v>6.245</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>5.274</v>
+        <v>6.45</v>
       </c>
       <c r="B310" t="n">
-        <v>322.7</v>
+        <v>39.1</v>
       </c>
       <c r="C310" t="n">
-        <v>0.143201468426342</v>
+        <v>0.143884793800518</v>
       </c>
       <c r="D310" t="n">
-        <v>101.81</v>
+        <v>33.83</v>
       </c>
       <c r="E310" t="n">
-        <v>5.135</v>
+        <v>6.229</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>5.466</v>
+        <v>6.283</v>
       </c>
       <c r="B311" t="n">
-        <v>316.8</v>
+        <v>40.1</v>
       </c>
       <c r="C311" t="n">
-        <v>0.1438815170045643</v>
+        <v>0.1488784638460412</v>
       </c>
       <c r="D311" t="n">
-        <v>107.1</v>
+        <v>36.19</v>
       </c>
       <c r="E311" t="n">
-        <v>5.274</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>5.767</v>
+        <v>6.365</v>
       </c>
       <c r="B312" t="n">
-        <v>334.9</v>
+        <v>41</v>
       </c>
       <c r="C312" t="n">
-        <v>0.1450021402058431</v>
+        <v>0.1541800114056834</v>
       </c>
       <c r="D312" t="n">
-        <v>110.09</v>
+        <v>38.5</v>
       </c>
       <c r="E312" t="n">
-        <v>5.466</v>
+        <v>6.283</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>5.608</v>
+        <v>6.526</v>
       </c>
       <c r="B313" t="n">
-        <v>342.5</v>
+        <v>39.5</v>
       </c>
       <c r="C313" t="n">
-        <v>0.1461046429190364</v>
+        <v>0.1595976412171882</v>
       </c>
       <c r="D313" t="n">
-        <v>114.99</v>
+        <v>42.27</v>
       </c>
       <c r="E313" t="n">
-        <v>5.767</v>
+        <v>6.365</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>5.609</v>
+        <v>6.537</v>
       </c>
       <c r="B314" t="n">
-        <v>324</v>
+        <v>41.7</v>
       </c>
       <c r="C314" t="n">
-        <v>0.1475045592092929</v>
+        <v>0.1654769693511415</v>
       </c>
       <c r="D314" t="n">
-        <v>115.6</v>
+        <v>41.89</v>
       </c>
       <c r="E314" t="n">
-        <v>5.608</v>
+        <v>6.526</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>5.668</v>
+        <v>6.251</v>
       </c>
       <c r="B315" t="n">
-        <v>320.4</v>
+        <v>43.3</v>
       </c>
       <c r="C315" t="n">
-        <v>0.1486359901272531</v>
+        <v>0.171088120456637</v>
       </c>
       <c r="D315" t="n">
-        <v>116.89</v>
+        <v>52.17</v>
       </c>
       <c r="E315" t="n">
-        <v>5.609</v>
+        <v>6.537</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>5.891</v>
+        <v>6.389</v>
       </c>
       <c r="B316" t="n">
-        <v>318</v>
+        <v>44.8</v>
       </c>
       <c r="C316" t="n">
-        <v>0.1503310765568038</v>
-      </c>
-      <c r="D316" t="inlineStr"/>
+        <v>0.1766011956133246</v>
+      </c>
+      <c r="D316" t="n">
+        <v>87.55</v>
+      </c>
       <c r="E316" t="n">
-        <v>5.668</v>
+        <v>6.251</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>5.842</v>
+        <v>6.427</v>
       </c>
       <c r="B317" t="n">
-        <v>25.5</v>
+        <v>46.9</v>
       </c>
       <c r="C317" t="n">
-        <v>0.1296475562787584</v>
-      </c>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
+        <v>0.1822203712942927</v>
+      </c>
+      <c r="D317" t="n">
+        <v>87.04000000000001</v>
+      </c>
+      <c r="E317" t="n">
+        <v>6.389</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>5.791</v>
+        <v>6.365</v>
       </c>
       <c r="B318" t="n">
-        <v>29.3</v>
+        <v>47.4</v>
       </c>
       <c r="C318" t="n">
-        <v>0.1314584452937464</v>
-      </c>
-      <c r="D318" t="inlineStr"/>
+        <v>0.1894025674556528</v>
+      </c>
+      <c r="D318" t="n">
+        <v>90.34</v>
+      </c>
       <c r="E318" t="n">
-        <v>5.842</v>
+        <v>6.427</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>5.781</v>
+        <v>6.466</v>
       </c>
       <c r="B319" t="n">
-        <v>31</v>
+        <v>48.5</v>
       </c>
       <c r="C319" t="n">
-        <v>0.1330244957321785</v>
-      </c>
-      <c r="D319" t="inlineStr"/>
+        <v>0.1935243494800631</v>
+      </c>
+      <c r="D319" t="n">
+        <v>86.65000000000001</v>
+      </c>
       <c r="E319" t="n">
-        <v>5.791</v>
+        <v>6.365</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>5.864</v>
+        <v>7.138</v>
       </c>
       <c r="B320" t="n">
-        <v>33.4</v>
+        <v>52.1</v>
       </c>
       <c r="C320" t="n">
-        <v>0.134201854880302</v>
-      </c>
-      <c r="D320" t="inlineStr"/>
+        <v>0.198915451751626</v>
+      </c>
+      <c r="D320" t="n">
+        <v>104.95</v>
+      </c>
       <c r="E320" t="n">
-        <v>5.781</v>
+        <v>6.466</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>6.352</v>
+        <v>8.064</v>
       </c>
       <c r="B321" t="n">
-        <v>38</v>
+        <v>56.6</v>
       </c>
       <c r="C321" t="n">
-        <v>0.1346265172347489</v>
-      </c>
-      <c r="D321" t="n">
-        <v>45.01</v>
-      </c>
+        <v>0.2047916535252889</v>
+      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="n">
-        <v>5.864</v>
+        <v>7.138</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>6.57</v>
+        <v>9.653</v>
       </c>
       <c r="B322" t="n">
-        <v>34.4</v>
+        <v>68.3</v>
       </c>
       <c r="C322" t="n">
-        <v>0.134946080693151</v>
+        <v>0.1718432934349926</v>
       </c>
       <c r="D322" t="n">
-        <v>44.6</v>
+        <v>171.41</v>
       </c>
       <c r="E322" t="n">
-        <v>6.352</v>
+        <v>9.532999999999999</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>6.435</v>
+        <v>9.353999999999999</v>
       </c>
       <c r="B323" t="n">
-        <v>37.8</v>
+        <v>67.7</v>
       </c>
       <c r="C323" t="n">
-        <v>0.1357045676905654</v>
+        <v>0.1735766821651623</v>
       </c>
       <c r="D323" t="n">
-        <v>46.04</v>
+        <v>175.59</v>
       </c>
       <c r="E323" t="n">
-        <v>6.57</v>
+        <v>9.653</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>6.245</v>
+        <v>9.252000000000001</v>
       </c>
       <c r="B324" t="n">
-        <v>38.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C324" t="n">
-        <v>0.1361312662958016</v>
+        <v>0.1754249762736376</v>
       </c>
       <c r="D324" t="n">
-        <v>38.25</v>
+        <v>181.95</v>
       </c>
       <c r="E324" t="n">
-        <v>6.435</v>
+        <v>9.353999999999999</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>6.229</v>
+        <v>9.583</v>
       </c>
       <c r="B325" t="n">
-        <v>39.2</v>
+        <v>66.8</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1396397132476974</v>
+        <v>0.177229216269846</v>
       </c>
       <c r="D325" t="n">
-        <v>33.3</v>
+        <v>189.07</v>
       </c>
       <c r="E325" t="n">
-        <v>6.245</v>
+        <v>9.252000000000001</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>6.45</v>
+        <v>10.131</v>
       </c>
       <c r="B326" t="n">
-        <v>39.1</v>
+        <v>68.5</v>
       </c>
       <c r="C326" t="n">
-        <v>0.143884793800518</v>
+        <v>0.1797122487956562</v>
       </c>
       <c r="D326" t="n">
-        <v>33.83</v>
+        <v>195.68</v>
       </c>
       <c r="E326" t="n">
-        <v>6.229</v>
+        <v>9.583</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>6.283</v>
+        <v>10.019</v>
       </c>
       <c r="B327" t="n">
-        <v>40.1</v>
+        <v>67.8</v>
       </c>
       <c r="C327" t="n">
-        <v>0.1488784638460412</v>
+        <v>0.1825696159230089</v>
       </c>
       <c r="D327" t="n">
-        <v>36.19</v>
+        <v>204.87</v>
       </c>
       <c r="E327" t="n">
-        <v>6.45</v>
+        <v>10.131</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>6.365</v>
+        <v>9.718</v>
       </c>
       <c r="B328" t="n">
-        <v>41</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C328" t="n">
-        <v>0.1541800114056834</v>
+        <v>0.1869359836507556</v>
       </c>
       <c r="D328" t="n">
-        <v>38.5</v>
+        <v>212.1</v>
       </c>
       <c r="E328" t="n">
-        <v>6.283</v>
+        <v>10.019</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>6.526</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="B329" t="n">
-        <v>39.5</v>
+        <v>61.6</v>
       </c>
       <c r="C329" t="n">
-        <v>0.1595976412171882</v>
+        <v>0.1917366783629054</v>
       </c>
       <c r="D329" t="n">
-        <v>42.27</v>
+        <v>214.11</v>
       </c>
       <c r="E329" t="n">
-        <v>6.365</v>
+        <v>9.718</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>6.537</v>
+        <v>9.395</v>
       </c>
       <c r="B330" t="n">
-        <v>41.7</v>
+        <v>62.1</v>
       </c>
       <c r="C330" t="n">
-        <v>0.1654769693511415</v>
+        <v>0.1950937409944069</v>
       </c>
       <c r="D330" t="n">
-        <v>41.89</v>
+        <v>220.1</v>
       </c>
       <c r="E330" t="n">
-        <v>6.526</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>6.251</v>
+        <v>9.336</v>
       </c>
       <c r="B331" t="n">
-        <v>43.3</v>
+        <v>61.9</v>
       </c>
       <c r="C331" t="n">
-        <v>0.171088120456637</v>
+        <v>0.1998930112833169</v>
       </c>
       <c r="D331" t="n">
-        <v>52.17</v>
+        <v>229.82</v>
       </c>
       <c r="E331" t="n">
-        <v>6.537</v>
+        <v>9.395</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>6.389</v>
+        <v>9.333</v>
       </c>
       <c r="B332" t="n">
-        <v>44.8</v>
+        <v>62.2</v>
       </c>
       <c r="C332" t="n">
-        <v>0.1766011956133246</v>
+        <v>0.2044670764294134</v>
       </c>
       <c r="D332" t="n">
-        <v>87.55</v>
+        <v>241.35</v>
       </c>
       <c r="E332" t="n">
-        <v>6.251</v>
+        <v>9.336</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>6.427</v>
+        <v>9.4</v>
       </c>
       <c r="B333" t="n">
-        <v>46.9</v>
+        <v>63.2</v>
       </c>
       <c r="C333" t="n">
-        <v>0.1822203712942927</v>
+        <v>0.2088054901387407</v>
       </c>
       <c r="D333" t="n">
-        <v>87.04000000000001</v>
+        <v>252.58</v>
       </c>
       <c r="E333" t="n">
-        <v>6.389</v>
+        <v>9.333</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>6.365</v>
+        <v>9.327</v>
       </c>
       <c r="B334" t="n">
-        <v>47.4</v>
+        <v>63.8</v>
       </c>
       <c r="C334" t="n">
-        <v>0.1894025674556528</v>
+        <v>0.2132975680358158</v>
       </c>
       <c r="D334" t="n">
-        <v>90.34</v>
+        <v>262.02</v>
       </c>
       <c r="E334" t="n">
-        <v>6.427</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>6.466</v>
+        <v>9.420999999999999</v>
       </c>
       <c r="B335" t="n">
-        <v>48.5</v>
+        <v>64.7</v>
       </c>
       <c r="C335" t="n">
-        <v>0.1935243494800631</v>
+        <v>0.217890103978707</v>
       </c>
       <c r="D335" t="n">
-        <v>86.65000000000001</v>
+        <v>267.71</v>
       </c>
       <c r="E335" t="n">
-        <v>6.365</v>
+        <v>9.327</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>7.138</v>
+        <v>9.509</v>
       </c>
       <c r="B336" t="n">
-        <v>52.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C336" t="n">
-        <v>0.198915451751626</v>
+        <v>0.2221724380596847</v>
       </c>
       <c r="D336" t="n">
-        <v>104.95</v>
+        <v>280.84</v>
       </c>
       <c r="E336" t="n">
-        <v>6.466</v>
+        <v>9.420999999999999</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>8.064</v>
+        <v>10.521</v>
       </c>
       <c r="B337" t="n">
-        <v>56.6</v>
+        <v>63.4</v>
       </c>
       <c r="C337" t="n">
-        <v>0.2047916535252889</v>
-      </c>
-      <c r="D337" t="inlineStr"/>
+        <v>0.2273149118660061</v>
+      </c>
+      <c r="D337" t="n">
+        <v>289.83</v>
+      </c>
       <c r="E337" t="n">
-        <v>7.138</v>
+        <v>9.509</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>9.532999999999999</v>
+        <v>11.22</v>
       </c>
       <c r="B338" t="n">
-        <v>68.3</v>
+        <v>62.5</v>
       </c>
       <c r="C338" t="n">
-        <v>0.1693808393925361</v>
+        <v>0.2320746655593928</v>
       </c>
       <c r="D338" t="n">
-        <v>166.08</v>
-      </c>
-      <c r="E338" t="inlineStr"/>
+        <v>295.82</v>
+      </c>
+      <c r="E338" t="n">
+        <v>10.521</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>9.653</v>
+        <v>10.549</v>
       </c>
       <c r="B339" t="n">
-        <v>68.3</v>
+        <v>64.5</v>
       </c>
       <c r="C339" t="n">
-        <v>0.1718432934349926</v>
+        <v>0.2362169045794227</v>
       </c>
       <c r="D339" t="n">
-        <v>171.41</v>
+        <v>302.54</v>
       </c>
       <c r="E339" t="n">
-        <v>9.532999999999999</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>9.353999999999999</v>
+        <v>10.028</v>
       </c>
       <c r="B340" t="n">
-        <v>67.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C340" t="n">
-        <v>0.1735766821651623</v>
+        <v>0.2387557752627959</v>
       </c>
       <c r="D340" t="n">
-        <v>175.59</v>
+        <v>307.85</v>
       </c>
       <c r="E340" t="n">
-        <v>9.653</v>
+        <v>10.549</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>9.252000000000001</v>
+        <v>10.241</v>
       </c>
       <c r="B341" t="n">
-        <v>67.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1754249762736376</v>
-      </c>
-      <c r="D341" t="n">
-        <v>181.95</v>
-      </c>
+        <v>0.2410376921360569</v>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="n">
-        <v>9.353999999999999</v>
+        <v>10.028</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>9.583</v>
+        <v>6.616</v>
       </c>
       <c r="B342" t="n">
-        <v>66.8</v>
+        <v>32.9</v>
       </c>
       <c r="C342" t="n">
-        <v>0.177229216269846</v>
-      </c>
-      <c r="D342" t="n">
-        <v>189.07</v>
-      </c>
+        <v>0.1168060290152875</v>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="n">
-        <v>9.252000000000001</v>
+        <v>6.495</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>10.131</v>
+        <v>6.852</v>
       </c>
       <c r="B343" t="n">
-        <v>68.5</v>
+        <v>36.3</v>
       </c>
       <c r="C343" t="n">
-        <v>0.1797122487956562</v>
-      </c>
-      <c r="D343" t="n">
-        <v>195.68</v>
-      </c>
+        <v>0.1181823020892891</v>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="n">
-        <v>9.583</v>
+        <v>6.616</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>10.019</v>
+        <v>7.175</v>
       </c>
       <c r="B344" t="n">
-        <v>67.8</v>
+        <v>42.3</v>
       </c>
       <c r="C344" t="n">
-        <v>0.1825696159230089</v>
-      </c>
-      <c r="D344" t="n">
-        <v>204.87</v>
-      </c>
+        <v>0.1196412552715524</v>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="n">
-        <v>10.131</v>
+        <v>6.852</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>9.718</v>
+        <v>6.96</v>
       </c>
       <c r="B345" t="n">
-        <v>64.40000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="C345" t="n">
-        <v>0.1869359836507556</v>
-      </c>
-      <c r="D345" t="n">
-        <v>212.1</v>
-      </c>
+        <v>0.1210273910429638</v>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="n">
-        <v>10.019</v>
+        <v>7.175</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>9.640000000000001</v>
+        <v>7.953</v>
       </c>
       <c r="B346" t="n">
-        <v>61.6</v>
+        <v>48.8</v>
       </c>
       <c r="C346" t="n">
-        <v>0.1917366783629054</v>
-      </c>
-      <c r="D346" t="n">
-        <v>214.11</v>
-      </c>
+        <v>0.1224416389637264</v>
+      </c>
+      <c r="D346" t="inlineStr"/>
       <c r="E346" t="n">
-        <v>9.718</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>9.395</v>
+        <v>7.671</v>
       </c>
       <c r="B347" t="n">
-        <v>62.1</v>
+        <v>50.4</v>
       </c>
       <c r="C347" t="n">
-        <v>0.1950937409944069</v>
-      </c>
-      <c r="D347" t="n">
-        <v>220.1</v>
-      </c>
+        <v>0.1243766244126143</v>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="n">
-        <v>9.640000000000001</v>
+        <v>7.953</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>9.336</v>
+        <v>7.315</v>
       </c>
       <c r="B348" t="n">
-        <v>61.9</v>
+        <v>51.3</v>
       </c>
       <c r="C348" t="n">
-        <v>0.1998930112833169</v>
-      </c>
-      <c r="D348" t="n">
-        <v>229.82</v>
-      </c>
+        <v>0.1258145190512802</v>
+      </c>
+      <c r="D348" t="inlineStr"/>
       <c r="E348" t="n">
-        <v>9.395</v>
+        <v>7.671</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>9.333</v>
+        <v>7.528</v>
       </c>
       <c r="B349" t="n">
-        <v>62.2</v>
+        <v>52.5</v>
       </c>
       <c r="C349" t="n">
-        <v>0.2044670764294134</v>
-      </c>
-      <c r="D349" t="n">
-        <v>241.35</v>
-      </c>
+        <v>0.1277980845700904</v>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="n">
-        <v>9.336</v>
+        <v>7.315</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>9.4</v>
+        <v>7.48</v>
       </c>
       <c r="B350" t="n">
-        <v>63.2</v>
+        <v>52.5</v>
       </c>
       <c r="C350" t="n">
-        <v>0.2088054901387407</v>
-      </c>
-      <c r="D350" t="n">
-        <v>252.58</v>
-      </c>
+        <v>0.131259199132999</v>
+      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" t="n">
-        <v>9.333</v>
+        <v>7.528</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>9.327</v>
+        <v>6.865</v>
       </c>
       <c r="B351" t="n">
-        <v>63.8</v>
+        <v>52.6</v>
       </c>
       <c r="C351" t="n">
-        <v>0.2132975680358158</v>
-      </c>
-      <c r="D351" t="n">
-        <v>262.02</v>
-      </c>
+        <v>0.1353661195849518</v>
+      </c>
+      <c r="D351" t="inlineStr"/>
       <c r="E351" t="n">
-        <v>9.4</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>9.420999999999999</v>
+        <v>6.741</v>
       </c>
       <c r="B352" t="n">
-        <v>64.7</v>
+        <v>53.3</v>
       </c>
       <c r="C352" t="n">
-        <v>0.217890103978707</v>
-      </c>
-      <c r="D352" t="n">
-        <v>267.71</v>
-      </c>
+        <v>0.1396108238004969</v>
+      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="n">
-        <v>9.327</v>
+        <v>6.865</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>9.509</v>
+        <v>6.942</v>
       </c>
       <c r="B353" t="n">
-        <v>65.40000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="C353" t="n">
-        <v>0.2221724380596847</v>
-      </c>
-      <c r="D353" t="n">
-        <v>280.84</v>
-      </c>
+        <v>0.14447099028943</v>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="n">
-        <v>9.420999999999999</v>
+        <v>6.741</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>10.521</v>
+        <v>6.734</v>
       </c>
       <c r="B354" t="n">
-        <v>63.4</v>
+        <v>52.7</v>
       </c>
       <c r="C354" t="n">
-        <v>0.2273149118660061</v>
-      </c>
-      <c r="D354" t="n">
-        <v>289.83</v>
-      </c>
+        <v>0.1498818013876953</v>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="n">
-        <v>9.509</v>
+        <v>6.942</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>11.22</v>
+        <v>6.637</v>
       </c>
       <c r="B355" t="n">
-        <v>62.5</v>
+        <v>54.1</v>
       </c>
       <c r="C355" t="n">
-        <v>0.2320746655593928</v>
-      </c>
-      <c r="D355" t="n">
-        <v>295.82</v>
-      </c>
+        <v>0.1552152074545481</v>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="n">
-        <v>10.521</v>
+        <v>6.734</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>10.549</v>
+        <v>6.911</v>
       </c>
       <c r="B356" t="n">
-        <v>64.5</v>
+        <v>54.7</v>
       </c>
       <c r="C356" t="n">
-        <v>0.2362169045794227</v>
-      </c>
-      <c r="D356" t="n">
-        <v>302.54</v>
-      </c>
+        <v>0.1604131130420934</v>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="n">
-        <v>11.22</v>
+        <v>6.637</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>10.028</v>
+        <v>7.06</v>
       </c>
       <c r="B357" t="n">
-        <v>66.59999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="C357" t="n">
-        <v>0.2387557752627959</v>
-      </c>
-      <c r="D357" t="n">
-        <v>307.85</v>
-      </c>
+        <v>0.1658475746870622</v>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="n">
-        <v>10.549</v>
+        <v>6.911</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>10.241</v>
+        <v>7.629</v>
       </c>
       <c r="B358" t="n">
-        <v>67.7</v>
+        <v>56.3</v>
       </c>
       <c r="C358" t="n">
-        <v>0.2410376921360569</v>
+        <v>0.1707072133479346</v>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="n">
-        <v>10.028</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>6.495</v>
+        <v>7.702</v>
       </c>
       <c r="B359" t="n">
-        <v>30.3</v>
+        <v>55.8</v>
       </c>
       <c r="C359" t="n">
-        <v>0.1156529144851658</v>
+        <v>0.1738745309779065</v>
       </c>
       <c r="D359" t="inlineStr"/>
-      <c r="E359" t="inlineStr"/>
+      <c r="E359" t="n">
+        <v>7.629</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>6.616</v>
+        <v>7.353</v>
       </c>
       <c r="B360" t="n">
-        <v>32.9</v>
+        <v>59</v>
       </c>
       <c r="C360" t="n">
-        <v>0.1168060290152875</v>
+        <v>0.1785052733646822</v>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="n">
-        <v>6.495</v>
+        <v>7.702</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>6.852</v>
+        <v>8.364000000000001</v>
       </c>
       <c r="B361" t="n">
-        <v>36.3</v>
+        <v>59.7</v>
       </c>
       <c r="C361" t="n">
-        <v>0.1181823020892891</v>
+        <v>0.1835001724523461</v>
       </c>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="n">
-        <v>6.616</v>
+        <v>7.353</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>7.175</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="B362" t="n">
-        <v>42.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C362" t="n">
-        <v>0.1196412552715524</v>
-      </c>
-      <c r="D362" t="inlineStr"/>
+        <v>0.1534268793896645</v>
+      </c>
+      <c r="D362" t="n">
+        <v>46.52</v>
+      </c>
       <c r="E362" t="n">
-        <v>6.852</v>
+        <v>8</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>6.96</v>
+        <v>7.867</v>
       </c>
       <c r="B363" t="n">
-        <v>48.1</v>
+        <v>66.8</v>
       </c>
       <c r="C363" t="n">
-        <v>0.1210273910429638</v>
-      </c>
-      <c r="D363" t="inlineStr"/>
+        <v>0.1561747825401152</v>
+      </c>
+      <c r="D363" t="n">
+        <v>46.52</v>
+      </c>
       <c r="E363" t="n">
-        <v>7.175</v>
+        <v>8.053000000000001</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>7.953</v>
+        <v>7.541</v>
       </c>
       <c r="B364" t="n">
-        <v>48.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C364" t="n">
-        <v>0.1224416389637264</v>
-      </c>
-      <c r="D364" t="inlineStr"/>
+        <v>0.158990577389216</v>
+      </c>
+      <c r="D364" t="n">
+        <v>48.01</v>
+      </c>
       <c r="E364" t="n">
-        <v>6.96</v>
+        <v>7.867</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>7.671</v>
+        <v>7.893</v>
       </c>
       <c r="B365" t="n">
-        <v>50.4</v>
+        <v>73.5</v>
       </c>
       <c r="C365" t="n">
-        <v>0.1243766244126143</v>
-      </c>
-      <c r="D365" t="inlineStr"/>
+        <v>0.162639925303529</v>
+      </c>
+      <c r="D365" t="n">
+        <v>47.96</v>
+      </c>
       <c r="E365" t="n">
-        <v>7.953</v>
+        <v>7.541</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>7.315</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="B366" t="n">
-        <v>51.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C366" t="n">
-        <v>0.1258145190512802</v>
-      </c>
-      <c r="D366" t="inlineStr"/>
+        <v>0.1643550706025796</v>
+      </c>
+      <c r="D366" t="n">
+        <v>48.87</v>
+      </c>
       <c r="E366" t="n">
-        <v>7.671</v>
+        <v>7.893</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>7.528</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="B367" t="n">
-        <v>52.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C367" t="n">
-        <v>0.1277980845700904</v>
-      </c>
-      <c r="D367" t="inlineStr"/>
+        <v>0.1652510825725363</v>
+      </c>
+      <c r="D367" t="n">
+        <v>50.17</v>
+      </c>
       <c r="E367" t="n">
-        <v>7.315</v>
+        <v>8.641999999999999</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>7.48</v>
+        <v>8.601000000000001</v>
       </c>
       <c r="B368" t="n">
-        <v>52.5</v>
+        <v>69.2</v>
       </c>
       <c r="C368" t="n">
-        <v>0.131259199132999</v>
-      </c>
-      <c r="D368" t="inlineStr"/>
+        <v>0.1653232945840603</v>
+      </c>
+      <c r="D368" t="n">
+        <v>52.14</v>
+      </c>
       <c r="E368" t="n">
-        <v>7.528</v>
+        <v>8.638999999999999</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>6.865</v>
+        <v>8.792999999999999</v>
       </c>
       <c r="B369" t="n">
-        <v>52.6</v>
+        <v>67.2</v>
       </c>
       <c r="C369" t="n">
-        <v>0.1353661195849518</v>
-      </c>
-      <c r="D369" t="inlineStr"/>
+        <v>0.1678427007398701</v>
+      </c>
+      <c r="D369" t="n">
+        <v>54.16</v>
+      </c>
       <c r="E369" t="n">
-        <v>7.48</v>
+        <v>8.601000000000001</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>6.741</v>
+        <v>8.84</v>
       </c>
       <c r="B370" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="C370" t="n">
-        <v>0.1396108238004969</v>
-      </c>
-      <c r="D370" t="inlineStr"/>
+        <v>0.1710420672802541</v>
+      </c>
+      <c r="D370" t="n">
+        <v>57.86</v>
+      </c>
       <c r="E370" t="n">
-        <v>6.865</v>
+        <v>8.792999999999999</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>6.942</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="B371" t="n">
-        <v>52.8</v>
+        <v>67.3</v>
       </c>
       <c r="C371" t="n">
-        <v>0.14447099028943</v>
-      </c>
-      <c r="D371" t="inlineStr"/>
+        <v>0.174716714740052</v>
+      </c>
+      <c r="D371" t="n">
+        <v>61.7</v>
+      </c>
       <c r="E371" t="n">
-        <v>6.741</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>6.734</v>
+        <v>8.597</v>
       </c>
       <c r="B372" t="n">
-        <v>52.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="C372" t="n">
-        <v>0.1498818013876953</v>
-      </c>
-      <c r="D372" t="inlineStr"/>
+        <v>0.1790637721935513</v>
+      </c>
+      <c r="D372" t="n">
+        <v>65.55</v>
+      </c>
       <c r="E372" t="n">
-        <v>6.942</v>
+        <v>8.585000000000001</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>6.637</v>
+        <v>8.569000000000001</v>
       </c>
       <c r="B373" t="n">
-        <v>54.1</v>
+        <v>68</v>
       </c>
       <c r="C373" t="n">
-        <v>0.1552152074545481</v>
-      </c>
-      <c r="D373" t="inlineStr"/>
+        <v>0.1841411731877135</v>
+      </c>
+      <c r="D373" t="n">
+        <v>67.52</v>
+      </c>
       <c r="E373" t="n">
-        <v>6.734</v>
+        <v>8.597</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>6.911</v>
+        <v>8.259</v>
       </c>
       <c r="B374" t="n">
-        <v>54.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="C374" t="n">
-        <v>0.1604131130420934</v>
-      </c>
-      <c r="D374" t="inlineStr"/>
+        <v>0.1889863715242062</v>
+      </c>
+      <c r="D374" t="n">
+        <v>67.28</v>
+      </c>
       <c r="E374" t="n">
-        <v>6.637</v>
+        <v>8.569000000000001</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>7.06</v>
+        <v>8.352</v>
       </c>
       <c r="B375" t="n">
-        <v>56.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C375" t="n">
-        <v>0.1658475746870622</v>
-      </c>
-      <c r="D375" t="inlineStr"/>
+        <v>0.1941389921040409</v>
+      </c>
+      <c r="D375" t="n">
+        <v>67.52</v>
+      </c>
       <c r="E375" t="n">
-        <v>6.911</v>
+        <v>8.259</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>7.629</v>
+        <v>8.566000000000001</v>
       </c>
       <c r="B376" t="n">
-        <v>56.3</v>
+        <v>72.7</v>
       </c>
       <c r="C376" t="n">
-        <v>0.1707072133479346</v>
-      </c>
-      <c r="D376" t="inlineStr"/>
+        <v>0.1984970022701628</v>
+      </c>
+      <c r="D376" t="n">
+        <v>67.70999999999999</v>
+      </c>
       <c r="E376" t="n">
-        <v>7.06</v>
+        <v>8.352</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>7.702</v>
+        <v>9.49</v>
       </c>
       <c r="B377" t="n">
-        <v>55.8</v>
+        <v>72.8</v>
       </c>
       <c r="C377" t="n">
-        <v>0.1738745309779065</v>
-      </c>
-      <c r="D377" t="inlineStr"/>
+        <v>0.2023054009784046</v>
+      </c>
+      <c r="D377" t="n">
+        <v>68.97</v>
+      </c>
       <c r="E377" t="n">
-        <v>7.629</v>
+        <v>8.566000000000001</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>7.353</v>
+        <v>9.526999999999999</v>
       </c>
       <c r="B378" t="n">
-        <v>59</v>
+        <v>74.2</v>
       </c>
       <c r="C378" t="n">
-        <v>0.1785052733646822</v>
-      </c>
-      <c r="D378" t="inlineStr"/>
+        <v>0.2066001668107333</v>
+      </c>
+      <c r="D378" t="n">
+        <v>69.26000000000001</v>
+      </c>
       <c r="E378" t="n">
-        <v>7.702</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>8.364000000000001</v>
+        <v>9.627000000000001</v>
       </c>
       <c r="B379" t="n">
-        <v>59.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C379" t="n">
-        <v>0.1835001724523461</v>
-      </c>
-      <c r="D379" t="inlineStr"/>
+        <v>0.2110607541833161</v>
+      </c>
+      <c r="D379" t="n">
+        <v>68.61</v>
+      </c>
       <c r="E379" t="n">
-        <v>7.353</v>
+        <v>9.526999999999999</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="B380" t="n">
-        <v>64.7</v>
+        <v>78.7</v>
       </c>
       <c r="C380" t="n">
-        <v>0.1503456414515288</v>
-      </c>
-      <c r="D380" t="inlineStr"/>
-      <c r="E380" t="inlineStr"/>
+        <v>0.2143193202366399</v>
+      </c>
+      <c r="D380" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="E380" t="n">
+        <v>9.627000000000001</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>8.053000000000001</v>
+        <v>9.875999999999999</v>
       </c>
       <c r="B381" t="n">
-        <v>65.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C381" t="n">
-        <v>0.1534268793896645</v>
-      </c>
-      <c r="D381" t="n">
-        <v>46.52</v>
-      </c>
+        <v>0.2177604076180737</v>
+      </c>
+      <c r="D381" t="inlineStr"/>
       <c r="E381" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>7.867</v>
+        <v>6.335</v>
       </c>
       <c r="B382" t="n">
-        <v>66.8</v>
+        <v>48.8</v>
       </c>
       <c r="C382" t="n">
-        <v>0.1561747825401152</v>
+        <v>0.1406167653133611</v>
       </c>
       <c r="D382" t="n">
-        <v>46.52</v>
+        <v>69.7</v>
       </c>
       <c r="E382" t="n">
-        <v>8.053000000000001</v>
+        <v>6.333</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>7.541</v>
+        <v>6.165</v>
       </c>
       <c r="B383" t="n">
-        <v>70.09999999999999</v>
+        <v>52</v>
       </c>
       <c r="C383" t="n">
-        <v>0.158990577389216</v>
+        <v>0.1424070068626666</v>
       </c>
       <c r="D383" t="n">
-        <v>48.01</v>
+        <v>69.52</v>
       </c>
       <c r="E383" t="n">
-        <v>7.867</v>
+        <v>6.335</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>7.893</v>
+        <v>5.99</v>
       </c>
       <c r="B384" t="n">
-        <v>73.5</v>
+        <v>54.5</v>
       </c>
       <c r="C384" t="n">
-        <v>0.162639925303529</v>
+        <v>0.1445307513492233</v>
       </c>
       <c r="D384" t="n">
-        <v>47.96</v>
+        <v>68.73</v>
       </c>
       <c r="E384" t="n">
-        <v>7.541</v>
+        <v>6.165</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>8.641999999999999</v>
+        <v>6.339</v>
       </c>
       <c r="B385" t="n">
-        <v>72.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="C385" t="n">
-        <v>0.1643550706025796</v>
+        <v>0.146240093462299</v>
       </c>
       <c r="D385" t="n">
-        <v>48.87</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="E385" t="n">
-        <v>7.893</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>8.638999999999999</v>
+        <v>7.265</v>
       </c>
       <c r="B386" t="n">
-        <v>70.09999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="C386" t="n">
-        <v>0.1652510825725363</v>
+        <v>0.1492788599187226</v>
       </c>
       <c r="D386" t="n">
-        <v>50.17</v>
+        <v>69.17</v>
       </c>
       <c r="E386" t="n">
-        <v>8.641999999999999</v>
+        <v>6.339</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>8.601000000000001</v>
+        <v>7.478</v>
       </c>
       <c r="B387" t="n">
-        <v>69.2</v>
+        <v>60.4</v>
       </c>
       <c r="C387" t="n">
-        <v>0.1653232945840603</v>
+        <v>0.1528872630396533</v>
       </c>
       <c r="D387" t="n">
-        <v>52.14</v>
+        <v>69.19</v>
       </c>
       <c r="E387" t="n">
-        <v>8.638999999999999</v>
+        <v>7.265</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>8.792999999999999</v>
+        <v>7.473</v>
       </c>
       <c r="B388" t="n">
-        <v>67.2</v>
+        <v>61.3</v>
       </c>
       <c r="C388" t="n">
-        <v>0.1678427007398701</v>
+        <v>0.1560990741538045</v>
       </c>
       <c r="D388" t="n">
-        <v>54.16</v>
+        <v>69.19</v>
       </c>
       <c r="E388" t="n">
-        <v>8.601000000000001</v>
+        <v>7.478</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>8.84</v>
+        <v>7.54</v>
       </c>
       <c r="B389" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="C389" t="n">
-        <v>0.1710420672802541</v>
+        <v>0.16195753725806</v>
       </c>
       <c r="D389" t="n">
-        <v>57.86</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="E389" t="n">
-        <v>8.792999999999999</v>
+        <v>7.473</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>8.585000000000001</v>
+        <v>7.448</v>
       </c>
       <c r="B390" t="n">
-        <v>67.3</v>
+        <v>58.2</v>
       </c>
       <c r="C390" t="n">
-        <v>0.174716714740052</v>
+        <v>0.1680864386834504</v>
       </c>
       <c r="D390" t="n">
-        <v>61.7</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="E390" t="n">
-        <v>8.84</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>8.597</v>
+        <v>7.539</v>
       </c>
       <c r="B391" t="n">
-        <v>67.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="C391" t="n">
-        <v>0.1790637721935513</v>
-      </c>
-      <c r="D391" t="n">
-        <v>65.55</v>
-      </c>
+        <v>0.1736559397033166</v>
+      </c>
+      <c r="D391" t="inlineStr"/>
       <c r="E391" t="n">
-        <v>8.585000000000001</v>
+        <v>7.448</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>8.569000000000001</v>
+        <v>7.293</v>
       </c>
       <c r="B392" t="n">
-        <v>68</v>
+        <v>58.4</v>
       </c>
       <c r="C392" t="n">
-        <v>0.1841411731877135</v>
-      </c>
-      <c r="D392" t="n">
-        <v>67.52</v>
-      </c>
+        <v>0.178435844576081</v>
+      </c>
+      <c r="D392" t="inlineStr"/>
       <c r="E392" t="n">
-        <v>8.597</v>
+        <v>7.539</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>8.259</v>
+        <v>7.323</v>
       </c>
       <c r="B393" t="n">
-        <v>69.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="C393" t="n">
-        <v>0.1889863715242062</v>
-      </c>
-      <c r="D393" t="n">
-        <v>67.28</v>
-      </c>
+        <v>0.1831003171072376</v>
+      </c>
+      <c r="D393" t="inlineStr"/>
       <c r="E393" t="n">
-        <v>8.569000000000001</v>
+        <v>7.293</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>8.352</v>
+        <v>7.242</v>
       </c>
       <c r="B394" t="n">
-        <v>71.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="C394" t="n">
-        <v>0.1941389921040409</v>
-      </c>
-      <c r="D394" t="n">
-        <v>67.52</v>
-      </c>
+        <v>0.1880098158395738</v>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="n">
-        <v>8.259</v>
+        <v>7.323</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>8.566000000000001</v>
+        <v>7.372</v>
       </c>
       <c r="B395" t="n">
-        <v>72.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="C395" t="n">
-        <v>0.1984970022701628</v>
-      </c>
-      <c r="D395" t="n">
-        <v>67.70999999999999</v>
-      </c>
+        <v>0.1922876931363692</v>
+      </c>
+      <c r="D395" t="inlineStr"/>
       <c r="E395" t="n">
-        <v>8.352</v>
+        <v>7.242</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>9.49</v>
+        <v>7.488</v>
       </c>
       <c r="B396" t="n">
-        <v>72.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="C396" t="n">
-        <v>0.2023054009784046</v>
+        <v>0.1959301583128322</v>
       </c>
       <c r="D396" t="n">
-        <v>68.97</v>
+        <v>68.69</v>
       </c>
       <c r="E396" t="n">
-        <v>8.566000000000001</v>
+        <v>7.372</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>9.526999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="B397" t="n">
-        <v>74.2</v>
+        <v>68.8</v>
       </c>
       <c r="C397" t="n">
-        <v>0.2066001668107333</v>
+        <v>0.1993306675865647</v>
       </c>
       <c r="D397" t="n">
-        <v>69.26000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="E397" t="n">
-        <v>9.49</v>
+        <v>7.488</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>9.627000000000001</v>
+        <v>9.154</v>
       </c>
       <c r="B398" t="n">
-        <v>74.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C398" t="n">
-        <v>0.2110607541833161</v>
+        <v>0.2050374107799302</v>
       </c>
       <c r="D398" t="n">
-        <v>68.61</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="E398" t="n">
-        <v>9.526999999999999</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>9.300000000000001</v>
+        <v>8.471</v>
       </c>
       <c r="B399" t="n">
-        <v>78.7</v>
+        <v>73.8</v>
       </c>
       <c r="C399" t="n">
-        <v>0.2143193202366399</v>
+        <v>0.2062536305328274</v>
       </c>
       <c r="D399" t="n">
-        <v>71.26000000000001</v>
+        <v>77.19</v>
       </c>
       <c r="E399" t="n">
-        <v>9.627000000000001</v>
+        <v>9.154</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>9.875999999999999</v>
+        <v>8.427</v>
       </c>
       <c r="B400" t="n">
-        <v>79.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C400" t="n">
-        <v>0.2177604076180737</v>
-      </c>
-      <c r="D400" t="inlineStr"/>
+        <v>0.2039106983689446</v>
+      </c>
+      <c r="D400" t="n">
+        <v>76.37</v>
+      </c>
       <c r="E400" t="n">
-        <v>9.300000000000001</v>
+        <v>8.471</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>6.333</v>
+        <v>8.507</v>
       </c>
       <c r="B401" t="n">
-        <v>44.6</v>
+        <v>73.7</v>
       </c>
       <c r="C401" t="n">
-        <v>0.1395509147457168</v>
+        <v>0.2052484483588221</v>
       </c>
       <c r="D401" t="inlineStr"/>
-      <c r="E401" t="inlineStr"/>
-    </row>
-    <row r="402">
-      <c r="A402" t="n">
-        <v>6.335</v>
-      </c>
-      <c r="B402" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="C402" t="n">
-        <v>0.1406167653133611</v>
-      </c>
-      <c r="D402" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="E402" t="n">
-        <v>6.333</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="n">
-        <v>6.165</v>
-      </c>
-      <c r="B403" t="n">
-        <v>52</v>
-      </c>
-      <c r="C403" t="n">
-        <v>0.1424070068626666</v>
-      </c>
-      <c r="D403" t="n">
-        <v>69.52</v>
-      </c>
-      <c r="E403" t="n">
-        <v>6.335</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="B404" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="C404" t="n">
-        <v>0.1445307513492233</v>
-      </c>
-      <c r="D404" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="E404" t="n">
-        <v>6.165</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="n">
-        <v>6.339</v>
-      </c>
-      <c r="B405" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="C405" t="n">
-        <v>0.146240093462299</v>
-      </c>
-      <c r="D405" t="n">
-        <v>68.84999999999999</v>
-      </c>
-      <c r="E405" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="n">
-        <v>7.265</v>
-      </c>
-      <c r="B406" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="C406" t="n">
-        <v>0.1492788599187226</v>
-      </c>
-      <c r="D406" t="n">
-        <v>69.17</v>
-      </c>
-      <c r="E406" t="n">
-        <v>6.339</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="n">
-        <v>7.478</v>
-      </c>
-      <c r="B407" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="C407" t="n">
-        <v>0.1528872630396533</v>
-      </c>
-      <c r="D407" t="n">
-        <v>69.19</v>
-      </c>
-      <c r="E407" t="n">
-        <v>7.265</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="n">
-        <v>7.473</v>
-      </c>
-      <c r="B408" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="C408" t="n">
-        <v>0.1560990741538045</v>
-      </c>
-      <c r="D408" t="n">
-        <v>69.19</v>
-      </c>
-      <c r="E408" t="n">
-        <v>7.478</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="B409" t="n">
-        <v>60</v>
-      </c>
-      <c r="C409" t="n">
-        <v>0.16195753725806</v>
-      </c>
-      <c r="D409" t="n">
-        <v>69.34999999999999</v>
-      </c>
-      <c r="E409" t="n">
-        <v>7.473</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="n">
-        <v>7.448</v>
-      </c>
-      <c r="B410" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="C410" t="n">
-        <v>0.1680864386834504</v>
-      </c>
-      <c r="D410" t="n">
-        <v>69.20999999999999</v>
-      </c>
-      <c r="E410" t="n">
-        <v>7.54</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="n">
-        <v>7.539</v>
-      </c>
-      <c r="B411" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="C411" t="n">
-        <v>0.1736559397033166</v>
-      </c>
-      <c r="D411" t="inlineStr"/>
-      <c r="E411" t="n">
-        <v>7.448</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="n">
-        <v>7.293</v>
-      </c>
-      <c r="B412" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="C412" t="n">
-        <v>0.178435844576081</v>
-      </c>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="n">
-        <v>7.539</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="n">
-        <v>7.323</v>
-      </c>
-      <c r="B413" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="C413" t="n">
-        <v>0.1831003171072376</v>
-      </c>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="n">
-        <v>7.293</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="n">
-        <v>7.242</v>
-      </c>
-      <c r="B414" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="C414" t="n">
-        <v>0.1880098158395738</v>
-      </c>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="n">
-        <v>7.323</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="n">
-        <v>7.372</v>
-      </c>
-      <c r="B415" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="C415" t="n">
-        <v>0.1922876931363692</v>
-      </c>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="n">
-        <v>7.242</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="n">
-        <v>7.488</v>
-      </c>
-      <c r="B416" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="C416" t="n">
-        <v>0.1959301583128322</v>
-      </c>
-      <c r="D416" t="n">
-        <v>68.69</v>
-      </c>
-      <c r="E416" t="n">
-        <v>7.372</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="B417" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="C417" t="n">
-        <v>0.1993306675865647</v>
-      </c>
-      <c r="D417" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="E417" t="n">
-        <v>7.488</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="n">
-        <v>9.154</v>
-      </c>
-      <c r="B418" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="C418" t="n">
-        <v>0.2050374107799302</v>
-      </c>
-      <c r="D418" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="E418" t="n">
-        <v>8.970000000000001</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="n">
-        <v>8.471</v>
-      </c>
-      <c r="B419" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="C419" t="n">
-        <v>0.2062536305328274</v>
-      </c>
-      <c r="D419" t="n">
-        <v>77.19</v>
-      </c>
-      <c r="E419" t="n">
-        <v>9.154</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="n">
-        <v>8.427</v>
-      </c>
-      <c r="B420" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="C420" t="n">
-        <v>0.2039106983689446</v>
-      </c>
-      <c r="D420" t="n">
-        <v>76.37</v>
-      </c>
-      <c r="E420" t="n">
-        <v>8.471</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="n">
-        <v>8.507</v>
-      </c>
-      <c r="B421" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="C421" t="n">
-        <v>0.2052484483588221</v>
-      </c>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="n">
+      <c r="E401" t="n">
         <v>8.427</v>
       </c>
     </row>

--- a/panel.xlsx
+++ b/panel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:F381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,10 +434,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Densité médicale</t>
+          <t>Practiciens pour 1000 habitants</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
+        <is>
+          <t>Lits d hôpitaux pour 1000 habitants</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Depenses t-1</t>
         </is>
@@ -454,9 +459,12 @@
         <v>0.1862702164434696</v>
       </c>
       <c r="D2" t="n">
-        <v>84.36</v>
+        <v>3.4</v>
       </c>
       <c r="E2" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="F2" t="n">
         <v>9.975</v>
       </c>
     </row>
@@ -471,9 +479,12 @@
         <v>0.1925092185951393</v>
       </c>
       <c r="D3" t="n">
-        <v>82.54000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="E3" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F3" t="n">
         <v>10.107</v>
       </c>
     </row>
@@ -488,9 +499,12 @@
         <v>0.1980113905493617</v>
       </c>
       <c r="D4" t="n">
-        <v>81.94</v>
+        <v>3.49</v>
       </c>
       <c r="E4" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="F4" t="n">
         <v>9.962</v>
       </c>
     </row>
@@ -505,9 +519,12 @@
         <v>0.2009143587662127</v>
       </c>
       <c r="D5" t="n">
-        <v>83.48</v>
+        <v>3.54</v>
       </c>
       <c r="E5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F5" t="n">
         <v>9.835000000000001</v>
       </c>
     </row>
@@ -522,9 +539,12 @@
         <v>0.2040064922037118</v>
       </c>
       <c r="D6" t="n">
-        <v>85.78</v>
+        <v>3.62</v>
       </c>
       <c r="E6" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="F6" t="n">
         <v>10.032</v>
       </c>
     </row>
@@ -539,9 +559,12 @@
         <v>0.2066170619228758</v>
       </c>
       <c r="D7" t="n">
-        <v>89.27</v>
+        <v>3.75</v>
       </c>
       <c r="E7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F7" t="n">
         <v>10.97</v>
       </c>
     </row>
@@ -556,9 +579,12 @@
         <v>0.206631704132772</v>
       </c>
       <c r="D8" t="n">
-        <v>90.64</v>
+        <v>3.88</v>
       </c>
       <c r="E8" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F8" t="n">
         <v>10.831</v>
       </c>
     </row>
@@ -573,9 +599,12 @@
         <v>0.2066957059751344</v>
       </c>
       <c r="D9" t="n">
-        <v>90.81</v>
+        <v>3.95</v>
       </c>
       <c r="E9" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="F9" t="n">
         <v>10.521</v>
       </c>
     </row>
@@ -590,9 +619,12 @@
         <v>0.2075804446554188</v>
       </c>
       <c r="D10" t="n">
-        <v>94.69</v>
+        <v>4.04</v>
       </c>
       <c r="E10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F10" t="n">
         <v>10.594</v>
       </c>
     </row>
@@ -607,9 +639,12 @@
         <v>0.208658404932194</v>
       </c>
       <c r="D11" t="n">
-        <v>96.62</v>
+        <v>4.11</v>
       </c>
       <c r="E11" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="F11" t="n">
         <v>10.743</v>
       </c>
     </row>
@@ -624,9 +659,12 @@
         <v>0.2104584896460591</v>
       </c>
       <c r="D12" t="n">
-        <v>94.2</v>
+        <v>4.14</v>
       </c>
       <c r="E12" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="F12" t="n">
         <v>10.768</v>
       </c>
     </row>
@@ -641,9 +679,12 @@
         <v>0.2105267295371706</v>
       </c>
       <c r="D13" t="n">
-        <v>95.16</v>
+        <v>4.19</v>
       </c>
       <c r="E13" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F13" t="n">
         <v>10.923</v>
       </c>
     </row>
@@ -658,9 +699,12 @@
         <v>0.2121831587644033</v>
       </c>
       <c r="D14" t="n">
-        <v>96.42</v>
+        <v>4.25</v>
       </c>
       <c r="E14" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="F14" t="n">
         <v>10.971</v>
       </c>
     </row>
@@ -675,9 +719,12 @@
         <v>0.2139051589439706</v>
       </c>
       <c r="D15" t="n">
-        <v>97.37</v>
+        <v>4.31</v>
       </c>
       <c r="E15" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="F15" t="n">
         <v>11.051</v>
       </c>
     </row>
@@ -692,9 +739,12 @@
         <v>0.2154143764287431</v>
       </c>
       <c r="D16" t="n">
-        <v>98.98999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
         <v>11.184</v>
       </c>
     </row>
@@ -709,9 +759,12 @@
         <v>0.2175231145067165</v>
       </c>
       <c r="D17" t="n">
-        <v>100.87</v>
+        <v>4.47</v>
       </c>
       <c r="E17" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="F17" t="n">
         <v>11.428</v>
       </c>
     </row>
@@ -726,9 +779,12 @@
         <v>0.2197297719725461</v>
       </c>
       <c r="D18" t="n">
-        <v>101.77</v>
+        <v>4.53</v>
       </c>
       <c r="E18" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="F18" t="n">
         <v>12.468</v>
       </c>
     </row>
@@ -743,9 +799,12 @@
         <v>0.2214937051405092</v>
       </c>
       <c r="D19" t="n">
-        <v>103.02</v>
+        <v>4.58</v>
       </c>
       <c r="E19" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="F19" t="n">
         <v>12.724</v>
       </c>
     </row>
@@ -759,196 +818,230 @@
       <c r="C20" t="n">
         <v>0.2224559367354327</v>
       </c>
-      <c r="D20" t="n">
-        <v>106.07</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
         <v>12.447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>12.267</v>
+        <v>9.718</v>
       </c>
       <c r="B21" t="n">
-        <v>129.8</v>
+        <v>138.8</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2241730602019303</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>0.1594790570684688</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.32</v>
+      </c>
       <c r="E21" t="n">
-        <v>11.744</v>
+        <v>7.69</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.815</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>9.641</v>
+      </c>
+      <c r="B22" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1644703159493394</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="F22" t="n">
         <v>9.718</v>
-      </c>
-      <c r="B22" t="n">
-        <v>138.8</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.1594790570684688</v>
-      </c>
-      <c r="D22" t="n">
-        <v>136.19</v>
-      </c>
-      <c r="E22" t="n">
-        <v>9.815</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9.641</v>
+        <v>9.605</v>
       </c>
       <c r="B23" t="n">
         <v>137.9</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1644703159493394</v>
+        <v>0.168852070703022</v>
       </c>
       <c r="D23" t="n">
-        <v>140.97</v>
+        <v>4.52</v>
       </c>
       <c r="E23" t="n">
-        <v>9.718</v>
+        <v>7.75</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.641</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>9.834</v>
+      </c>
+      <c r="B24" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1714044156774883</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="F24" t="n">
         <v>9.605</v>
-      </c>
-      <c r="B24" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.168852070703022</v>
-      </c>
-      <c r="D24" t="n">
-        <v>143.64</v>
-      </c>
-      <c r="E24" t="n">
-        <v>9.641</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>10.312</v>
+      </c>
+      <c r="B25" t="n">
+        <v>141.7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1738544065311074</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="F25" t="n">
         <v>9.834</v>
-      </c>
-      <c r="B25" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.1714044156774883</v>
-      </c>
-      <c r="D25" t="n">
-        <v>143.76</v>
-      </c>
-      <c r="E25" t="n">
-        <v>9.605</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>10.316</v>
+      </c>
+      <c r="B26" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1764185801524323</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="E26" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="F26" t="n">
         <v>10.312</v>
-      </c>
-      <c r="B26" t="n">
-        <v>141.7</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.1738544065311074</v>
-      </c>
-      <c r="D26" t="n">
-        <v>146.51</v>
-      </c>
-      <c r="E26" t="n">
-        <v>9.834</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>10.137</v>
+      </c>
+      <c r="B27" t="n">
+        <v>142</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1764262765481369</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="F27" t="n">
         <v>10.316</v>
-      </c>
-      <c r="B27" t="n">
-        <v>140.1</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.1764185801524323</v>
-      </c>
-      <c r="D27" t="n">
-        <v>149.22</v>
-      </c>
-      <c r="E27" t="n">
-        <v>10.312</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>10.302</v>
+      </c>
+      <c r="B28" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1779656834148795</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="F28" t="n">
         <v>10.137</v>
-      </c>
-      <c r="B28" t="n">
-        <v>142</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.1764262765481369</v>
-      </c>
-      <c r="D28" t="n">
-        <v>151.3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>10.316</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>10.406</v>
+      </c>
+      <c r="B29" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1807006978345595</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="F29" t="n">
         <v>10.302</v>
-      </c>
-      <c r="B29" t="n">
-        <v>144.6</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.1779656834148795</v>
-      </c>
-      <c r="D29" t="n">
-        <v>154.16</v>
-      </c>
-      <c r="E29" t="n">
-        <v>10.137</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>10.512</v>
+      </c>
+      <c r="B30" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1829686360235201</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="F30" t="n">
         <v>10.406</v>
-      </c>
-      <c r="B30" t="n">
-        <v>144.3</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.1807006978345595</v>
-      </c>
-      <c r="D30" t="n">
-        <v>157.18</v>
-      </c>
-      <c r="E30" t="n">
-        <v>10.302</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>10.517</v>
+      </c>
+      <c r="B31" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1845010661711004</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="F31" t="n">
         <v>10.512</v>
-      </c>
-      <c r="B31" t="n">
-        <v>143.9</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.1829686360235201</v>
-      </c>
-      <c r="D31" t="n">
-        <v>159.5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10.406</v>
       </c>
     </row>
     <row r="32">
@@ -956,6173 +1049,6931 @@
         <v>10.517</v>
       </c>
       <c r="B32" t="n">
-        <v>142.6</v>
+        <v>142.8</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1845010661711004</v>
+        <v>0.1844689787483919</v>
       </c>
       <c r="D32" t="n">
-        <v>161.14</v>
+        <v>5.11</v>
       </c>
       <c r="E32" t="n">
-        <v>10.512</v>
+        <v>7.42</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.517</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10.517</v>
+        <v>10.571</v>
       </c>
       <c r="B33" t="n">
-        <v>142.8</v>
+        <v>140.8</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1844689787483919</v>
+        <v>0.1852891843200596</v>
       </c>
       <c r="D33" t="n">
-        <v>156.16</v>
+        <v>5.16</v>
       </c>
       <c r="E33" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="F33" t="n">
         <v>10.517</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>10.516</v>
+      </c>
+      <c r="B34" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1866858030934679</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="F34" t="n">
         <v>10.571</v>
-      </c>
-      <c r="B34" t="n">
-        <v>140.8</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.1852891843200596</v>
-      </c>
-      <c r="D34" t="n">
-        <v>155.16</v>
-      </c>
-      <c r="E34" t="n">
-        <v>10.517</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>10.625</v>
+      </c>
+      <c r="B35" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1883509853224627</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="F35" t="n">
         <v>10.516</v>
-      </c>
-      <c r="B35" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.1866858030934679</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="n">
-        <v>10.571</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>11.413</v>
+      </c>
+      <c r="B36" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1902724213644571</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F36" t="n">
         <v>10.625</v>
-      </c>
-      <c r="B36" t="n">
-        <v>140.6</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.1883509853224627</v>
-      </c>
-      <c r="D36" t="n">
-        <v>152.94</v>
-      </c>
-      <c r="E36" t="n">
-        <v>10.516</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>12.185</v>
+      </c>
+      <c r="B37" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1921360749715874</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="F37" t="n">
         <v>11.413</v>
-      </c>
-      <c r="B37" t="n">
-        <v>139.8</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.1902724213644571</v>
-      </c>
-      <c r="D37" t="n">
-        <v>148.93</v>
-      </c>
-      <c r="E37" t="n">
-        <v>10.625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>11.225</v>
+      </c>
+      <c r="B38" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1944207377071363</v>
+      </c>
+      <c r="D38" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="F38" t="n">
         <v>12.185</v>
-      </c>
-      <c r="B38" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.1921360749715874</v>
-      </c>
-      <c r="D38" t="n">
-        <v>148.25</v>
-      </c>
-      <c r="E38" t="n">
-        <v>11.413</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>11.153</v>
+      </c>
+      <c r="B39" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1955790875378318</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
         <v>11.225</v>
-      </c>
-      <c r="B39" t="n">
-        <v>137.4</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.1944207377071363</v>
-      </c>
-      <c r="D39" t="n">
-        <v>146.14</v>
-      </c>
-      <c r="E39" t="n">
-        <v>12.185</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11.153</v>
+        <v>9.25</v>
       </c>
       <c r="B40" t="n">
-        <v>136.4</v>
+        <v>133.8</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1955790875378318</v>
+        <v>0.1722693371493297</v>
       </c>
       <c r="D40" t="n">
-        <v>142.64</v>
+        <v>2.87</v>
       </c>
       <c r="E40" t="n">
-        <v>11.225</v>
+        <v>6.02</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9.355</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11.777</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="B41" t="n">
-        <v>134.8</v>
+        <v>132.2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.198405677630681</v>
+        <v>0.1721007760920495</v>
       </c>
       <c r="D41" t="n">
-        <v>141.94</v>
+        <v>2.89</v>
       </c>
       <c r="E41" t="n">
-        <v>11.153</v>
+        <v>5.98</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9.25</v>
+        <v>9.138999999999999</v>
       </c>
       <c r="B42" t="n">
-        <v>133.8</v>
+        <v>131</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1722693371493297</v>
+        <v>0.1710100794234304</v>
       </c>
       <c r="D42" t="n">
-        <v>108.29</v>
+        <v>2.91</v>
       </c>
       <c r="E42" t="n">
-        <v>9.355</v>
+        <v>5.93</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9.132999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9.132999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="B43" t="n">
-        <v>132.2</v>
+        <v>129.3</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1721007760920495</v>
+        <v>0.1705961244849237</v>
       </c>
       <c r="D43" t="n">
-        <v>108.38</v>
+        <v>2.92</v>
       </c>
       <c r="E43" t="n">
-        <v>9.25</v>
+        <v>5.89</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9.138999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>9.138999999999999</v>
+        <v>10.544</v>
       </c>
       <c r="B44" t="n">
-        <v>131</v>
+        <v>132.9</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1710100794234304</v>
+        <v>0.1708141295331198</v>
       </c>
       <c r="D44" t="n">
-        <v>107.69</v>
+        <v>2.92</v>
       </c>
       <c r="E44" t="n">
-        <v>9.132999999999999</v>
+        <v>5.83</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>9.6</v>
+        <v>10.413</v>
       </c>
       <c r="B45" t="n">
-        <v>129.3</v>
+        <v>132.8</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1705961244849237</v>
+        <v>0.1716028876636834</v>
       </c>
       <c r="D45" t="n">
-        <v>107.14</v>
+        <v>2.91</v>
       </c>
       <c r="E45" t="n">
-        <v>9.138999999999999</v>
+        <v>5.75</v>
+      </c>
+      <c r="F45" t="n">
+        <v>10.544</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>10.544</v>
+        <v>10.413</v>
       </c>
       <c r="B46" t="n">
-        <v>132.9</v>
+        <v>132.6</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1708141295331198</v>
+        <v>0.1711884347071506</v>
       </c>
       <c r="D46" t="n">
-        <v>107.25</v>
+        <v>2.92</v>
       </c>
       <c r="E46" t="n">
-        <v>9.6</v>
+        <v>5.69</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10.413</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>10.587</v>
+      </c>
+      <c r="B47" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.1737773825649571</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="F47" t="n">
         <v>10.413</v>
-      </c>
-      <c r="B47" t="n">
-        <v>132.8</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.1716028876636834</v>
-      </c>
-      <c r="D47" t="n">
-        <v>106.74</v>
-      </c>
-      <c r="E47" t="n">
-        <v>10.544</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10.413</v>
+        <v>10.638</v>
       </c>
       <c r="B48" t="n">
-        <v>132.6</v>
+        <v>134.7</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1711884347071506</v>
+        <v>0.17592589101034</v>
       </c>
       <c r="D48" t="n">
-        <v>107.28</v>
+        <v>2.96</v>
       </c>
       <c r="E48" t="n">
-        <v>10.413</v>
+        <v>5.61</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10.587</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10.587</v>
+        <v>10.62</v>
       </c>
       <c r="B49" t="n">
-        <v>134.4</v>
+        <v>134.6</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1737773825649571</v>
+        <v>0.1783564562233249</v>
       </c>
       <c r="D49" t="n">
-        <v>107.92</v>
+        <v>2.98</v>
       </c>
       <c r="E49" t="n">
-        <v>10.413</v>
+        <v>5.63</v>
+      </c>
+      <c r="F49" t="n">
+        <v>10.638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10.638</v>
+        <v>10.884</v>
       </c>
       <c r="B50" t="n">
-        <v>134.7</v>
+        <v>132.6</v>
       </c>
       <c r="C50" t="n">
-        <v>0.17592589101034</v>
+        <v>0.1807328004994806</v>
       </c>
       <c r="D50" t="n">
-        <v>108.97</v>
+        <v>3.02</v>
       </c>
       <c r="E50" t="n">
-        <v>10.587</v>
+        <v>5.69</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10.62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10.62</v>
+        <v>10.898</v>
       </c>
       <c r="B51" t="n">
-        <v>134.6</v>
+        <v>132.7</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1783564562233249</v>
+        <v>0.182378274400309</v>
       </c>
       <c r="D51" t="n">
-        <v>109.64</v>
+        <v>3.07</v>
       </c>
       <c r="E51" t="n">
-        <v>10.638</v>
+        <v>5.64</v>
+      </c>
+      <c r="F51" t="n">
+        <v>10.884</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10.884</v>
+        <v>10.94</v>
       </c>
       <c r="B52" t="n">
-        <v>132.6</v>
+        <v>131.5</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1807328004994806</v>
+        <v>0.1845748228441364</v>
       </c>
       <c r="D52" t="n">
-        <v>110.8</v>
+        <v>3.08</v>
       </c>
       <c r="E52" t="n">
-        <v>10.62</v>
+        <v>5.55</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10.898</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10.898</v>
+        <v>10.994</v>
       </c>
       <c r="B53" t="n">
-        <v>132.7</v>
+        <v>131.2</v>
       </c>
       <c r="C53" t="n">
-        <v>0.182378274400309</v>
+        <v>0.1869226971864676</v>
       </c>
       <c r="D53" t="n">
-        <v>112.86</v>
+        <v>3.13</v>
       </c>
       <c r="E53" t="n">
-        <v>10.884</v>
+        <v>5.52</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10.94</v>
+        <v>10.858</v>
       </c>
       <c r="B54" t="n">
-        <v>131.5</v>
+        <v>131.7</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1845748228441364</v>
+        <v>0.1890319417217151</v>
       </c>
       <c r="D54" t="n">
-        <v>113.41</v>
+        <v>3.16</v>
       </c>
       <c r="E54" t="n">
-        <v>10.898</v>
+        <v>5.47</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10.994</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10.994</v>
+        <v>11.463</v>
       </c>
       <c r="B55" t="n">
-        <v>131.2</v>
+        <v>131.7</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1869226971864676</v>
+        <v>0.191334647869722</v>
       </c>
       <c r="D55" t="n">
-        <v>115.04</v>
+        <v>3.21</v>
       </c>
       <c r="E55" t="n">
-        <v>10.94</v>
+        <v>5.44</v>
+      </c>
+      <c r="F55" t="n">
+        <v>10.858</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10.858</v>
+        <v>11.288</v>
       </c>
       <c r="B56" t="n">
-        <v>131.7</v>
+        <v>131.3</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1890319417217151</v>
+        <v>0.1929401086149119</v>
       </c>
       <c r="D56" t="n">
-        <v>116.85</v>
+        <v>3.25</v>
       </c>
       <c r="E56" t="n">
-        <v>10.994</v>
+        <v>5.41</v>
+      </c>
+      <c r="F56" t="n">
+        <v>11.463</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>11.463</v>
+        <v>10.74</v>
       </c>
       <c r="B57" t="n">
-        <v>131.7</v>
+        <v>133</v>
       </c>
       <c r="C57" t="n">
-        <v>0.191334647869722</v>
+        <v>0.1953482222654324</v>
       </c>
       <c r="D57" t="n">
-        <v>118.71</v>
+        <v>3.26</v>
       </c>
       <c r="E57" t="n">
-        <v>10.858</v>
+        <v>5.35</v>
+      </c>
+      <c r="F57" t="n">
+        <v>11.288</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>11.288</v>
+        <v>10.804</v>
       </c>
       <c r="B58" t="n">
-        <v>131.3</v>
+        <v>133.2</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1929401086149119</v>
+        <v>0.1967919735640473</v>
       </c>
       <c r="D58" t="n">
-        <v>120.42</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>11.463</v>
+        <v>5.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10.74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10.74</v>
+        <v>9.067</v>
       </c>
       <c r="B59" t="n">
-        <v>133</v>
+        <v>178.1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1953482222654324</v>
+        <v>0.1501464037528147</v>
       </c>
       <c r="D59" t="n">
-        <v>120.21</v>
+        <v>3.33</v>
       </c>
       <c r="E59" t="n">
-        <v>11.288</v>
+        <v>3.86</v>
+      </c>
+      <c r="F59" t="n">
+        <v>8.986000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10.804</v>
+        <v>9.153</v>
       </c>
       <c r="B60" t="n">
-        <v>133.2</v>
+        <v>178.2</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1967919735640473</v>
+        <v>0.1516413113392473</v>
       </c>
       <c r="D60" t="n">
-        <v>123.56</v>
+        <v>3.42</v>
       </c>
       <c r="E60" t="n">
-        <v>10.74</v>
+        <v>3.79</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9.067</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10.969</v>
+        <v>9.302</v>
       </c>
       <c r="B61" t="n">
-        <v>131</v>
+        <v>173.6</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1994595795786037</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+        <v>0.1532462139375857</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3.46</v>
+      </c>
       <c r="E61" t="n">
-        <v>10.804</v>
+        <v>3.69</v>
+      </c>
+      <c r="F61" t="n">
+        <v>9.153</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>9.067</v>
+        <v>9.468</v>
       </c>
       <c r="B62" t="n">
-        <v>178.1</v>
+        <v>174</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1501464037528147</v>
+        <v>0.155784068456959</v>
       </c>
       <c r="D62" t="n">
-        <v>71.79000000000001</v>
+        <v>3.58</v>
       </c>
       <c r="E62" t="n">
-        <v>8.986000000000001</v>
+        <v>3.57</v>
+      </c>
+      <c r="F62" t="n">
+        <v>9.302</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>9.153</v>
+        <v>10.629</v>
       </c>
       <c r="B63" t="n">
-        <v>178.2</v>
+        <v>173.6</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1516413113392473</v>
+        <v>0.1588503644503054</v>
       </c>
       <c r="D63" t="n">
-        <v>72.11</v>
+        <v>3.65</v>
       </c>
       <c r="E63" t="n">
-        <v>9.067</v>
+        <v>3.49</v>
+      </c>
+      <c r="F63" t="n">
+        <v>9.468</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>9.302</v>
+        <v>10.579</v>
       </c>
       <c r="B64" t="n">
-        <v>173.6</v>
+        <v>174.9</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1532462139375857</v>
+        <v>0.1631258787678839</v>
       </c>
       <c r="D64" t="n">
-        <v>72.11</v>
+        <v>3.73</v>
       </c>
       <c r="E64" t="n">
-        <v>9.153</v>
+        <v>3.5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>10.629</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>9.468</v>
+        <v>10.378</v>
       </c>
       <c r="B65" t="n">
-        <v>174</v>
+        <v>172.1</v>
       </c>
       <c r="C65" t="n">
-        <v>0.155784068456959</v>
+        <v>0.1679272556984571</v>
       </c>
       <c r="D65" t="n">
-        <v>74.81999999999999</v>
+        <v>3.79</v>
       </c>
       <c r="E65" t="n">
-        <v>9.302</v>
+        <v>3.13</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10.579</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>10.629</v>
+        <v>10.517</v>
       </c>
       <c r="B66" t="n">
-        <v>173.6</v>
+        <v>175.1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1588503644503054</v>
+        <v>0.1734757144321421</v>
       </c>
       <c r="D66" t="n">
-        <v>74.92</v>
-      </c>
-      <c r="E66" t="n">
-        <v>9.468</v>
+        <v>3.84</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>10.378</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10.579</v>
+        <v>10.279</v>
       </c>
       <c r="B67" t="n">
-        <v>174.9</v>
+        <v>176.1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1631258787678839</v>
+        <v>0.1784521478134904</v>
       </c>
       <c r="D67" t="n">
-        <v>75.73</v>
+        <v>3.85</v>
       </c>
       <c r="E67" t="n">
-        <v>10.629</v>
+        <v>3.07</v>
+      </c>
+      <c r="F67" t="n">
+        <v>10.517</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>10.378</v>
+        <v>10.297</v>
       </c>
       <c r="B68" t="n">
-        <v>172.1</v>
+        <v>175.3</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1679272556984571</v>
+        <v>0.1824579922466362</v>
       </c>
       <c r="D68" t="n">
-        <v>76.16</v>
+        <v>3.88</v>
       </c>
       <c r="E68" t="n">
-        <v>10.579</v>
+        <v>2.69</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10.279</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>10.517</v>
+        <v>10.359</v>
       </c>
       <c r="B69" t="n">
-        <v>175.1</v>
+        <v>172.3</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1734757144321421</v>
+        <v>0.1857211891411493</v>
       </c>
       <c r="D69" t="n">
-        <v>77.18000000000001</v>
+        <v>3.93</v>
       </c>
       <c r="E69" t="n">
-        <v>10.378</v>
+        <v>2.53</v>
+      </c>
+      <c r="F69" t="n">
+        <v>10.297</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>10.279</v>
+        <v>10.268</v>
       </c>
       <c r="B70" t="n">
-        <v>176.1</v>
+        <v>172.9</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1784521478134904</v>
+        <v>0.1882556067711057</v>
       </c>
       <c r="D70" t="n">
-        <v>76.8</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>10.517</v>
+        <v>2.6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>10.359</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>10.297</v>
+        <v>10.114</v>
       </c>
       <c r="B71" t="n">
-        <v>175.3</v>
+        <v>172.2</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1824579922466362</v>
+        <v>0.1905054803906715</v>
       </c>
       <c r="D71" t="n">
-        <v>77.48999999999999</v>
+        <v>4.11</v>
       </c>
       <c r="E71" t="n">
-        <v>10.279</v>
+        <v>2.61</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10.268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>10.359</v>
+        <v>10.142</v>
       </c>
       <c r="B72" t="n">
-        <v>172.3</v>
+        <v>169.6</v>
       </c>
       <c r="C72" t="n">
-        <v>0.1857211891411493</v>
+        <v>0.1930507386887475</v>
       </c>
       <c r="D72" t="n">
-        <v>78.8</v>
+        <v>4.2</v>
       </c>
       <c r="E72" t="n">
-        <v>10.297</v>
+        <v>2.61</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10.114</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>10.268</v>
+        <v>10.185</v>
       </c>
       <c r="B73" t="n">
-        <v>172.9</v>
+        <v>167.3</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1882556067711057</v>
+        <v>0.195667783484247</v>
       </c>
       <c r="D73" t="n">
-        <v>78.97</v>
+        <v>4.25</v>
       </c>
       <c r="E73" t="n">
-        <v>10.359</v>
+        <v>2.59</v>
+      </c>
+      <c r="F73" t="n">
+        <v>10.142</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>10.114</v>
+        <v>10.692</v>
       </c>
       <c r="B74" t="n">
-        <v>172.2</v>
+        <v>175.5</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1905054803906715</v>
+        <v>0.1985296327533853</v>
       </c>
       <c r="D74" t="n">
-        <v>79.52</v>
+        <v>4.38</v>
       </c>
       <c r="E74" t="n">
-        <v>10.268</v>
+        <v>2.59</v>
+      </c>
+      <c r="F74" t="n">
+        <v>10.185</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>10.142</v>
+        <v>10.656</v>
       </c>
       <c r="B75" t="n">
-        <v>169.6</v>
+        <v>176.3</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1930507386887475</v>
+        <v>0.2014148863578962</v>
       </c>
       <c r="D75" t="n">
-        <v>80.06999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="E75" t="n">
-        <v>10.114</v>
+        <v>2.51</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.692</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>10.185</v>
+        <v>9.474</v>
       </c>
       <c r="B76" t="n">
-        <v>167.3</v>
+        <v>178.3</v>
       </c>
       <c r="C76" t="n">
-        <v>0.195667783484247</v>
-      </c>
-      <c r="D76" t="n">
-        <v>79.81999999999999</v>
-      </c>
-      <c r="E76" t="n">
-        <v>10.142</v>
+        <v>0.2034957486438906</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>10.656</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10.692</v>
+        <v>9.513</v>
       </c>
       <c r="B77" t="n">
-        <v>175.5</v>
+        <v>163.9</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1985296327533853</v>
-      </c>
-      <c r="D77" t="n">
-        <v>79.53</v>
-      </c>
-      <c r="E77" t="n">
-        <v>10.185</v>
+        <v>0.2045170677406773</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>9.474</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>10.656</v>
+        <v>7.778</v>
       </c>
       <c r="B78" t="n">
-        <v>176.3</v>
+        <v>96.2</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2014148863578962</v>
+        <v>0.165600240833301</v>
       </c>
       <c r="D78" t="n">
-        <v>80.15000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="E78" t="n">
-        <v>10.692</v>
+        <v>3.34</v>
+      </c>
+      <c r="F78" t="n">
+        <v>7.684</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>9.474</v>
+        <v>7.871</v>
       </c>
       <c r="B79" t="n">
-        <v>178.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2034957486438906</v>
+        <v>0.166420196005128</v>
       </c>
       <c r="D79" t="n">
-        <v>71.81</v>
+        <v>3.62</v>
       </c>
       <c r="E79" t="n">
-        <v>10.656</v>
+        <v>3.29</v>
+      </c>
+      <c r="F79" t="n">
+        <v>7.778</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9.513</v>
+        <v>7.962</v>
       </c>
       <c r="B80" t="n">
-        <v>163.9</v>
+        <v>96.5</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2045170677406773</v>
+        <v>0.1653950260564632</v>
       </c>
       <c r="D80" t="n">
-        <v>68.93000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="E80" t="n">
-        <v>9.474</v>
+        <v>3.25</v>
+      </c>
+      <c r="F80" t="n">
+        <v>7.871</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>9.388</v>
+        <v>8.429</v>
       </c>
       <c r="B81" t="n">
-        <v>164.4</v>
+        <v>95.3</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2065765077083678</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
+        <v>0.1643632228898508</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3.54</v>
+      </c>
       <c r="E81" t="n">
-        <v>9.513</v>
+        <v>3.2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>7.962</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7.778</v>
+        <v>9.153</v>
       </c>
       <c r="B82" t="n">
-        <v>96.2</v>
+        <v>95.5</v>
       </c>
       <c r="C82" t="n">
-        <v>0.165600240833301</v>
+        <v>0.1656160986787141</v>
       </c>
       <c r="D82" t="n">
-        <v>66.52</v>
+        <v>3.6</v>
       </c>
       <c r="E82" t="n">
-        <v>7.684</v>
+        <v>3.16</v>
+      </c>
+      <c r="F82" t="n">
+        <v>8.429</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7.871</v>
+        <v>9.17</v>
       </c>
       <c r="B83" t="n">
-        <v>97.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="C83" t="n">
-        <v>0.166420196005128</v>
+        <v>0.1680139396672406</v>
       </c>
       <c r="D83" t="n">
-        <v>68.2</v>
+        <v>3.76</v>
       </c>
       <c r="E83" t="n">
-        <v>7.778</v>
+        <v>3.12</v>
+      </c>
+      <c r="F83" t="n">
+        <v>9.153</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>7.962</v>
+        <v>9.217000000000001</v>
       </c>
       <c r="B84" t="n">
-        <v>96.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1653950260564632</v>
+        <v>0.1710623188796476</v>
       </c>
       <c r="D84" t="n">
-        <v>67.33</v>
+        <v>3.84</v>
       </c>
       <c r="E84" t="n">
-        <v>7.871</v>
+        <v>3.05</v>
+      </c>
+      <c r="F84" t="n">
+        <v>9.17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>8.429</v>
+        <v>9.218999999999999</v>
       </c>
       <c r="B85" t="n">
-        <v>95.3</v>
+        <v>85.3</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1643632228898508</v>
+        <v>0.1736085048429544</v>
       </c>
       <c r="D85" t="n">
-        <v>71.08</v>
+        <v>3.82</v>
       </c>
       <c r="E85" t="n">
-        <v>7.962</v>
+        <v>2.99</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9.217000000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>9.153</v>
+        <v>9.137</v>
       </c>
       <c r="B86" t="n">
-        <v>95.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1656160986787141</v>
+        <v>0.1766742413457597</v>
       </c>
       <c r="D86" t="n">
-        <v>72.38</v>
+        <v>3.81</v>
       </c>
       <c r="E86" t="n">
-        <v>8.429</v>
+        <v>2.96</v>
+      </c>
+      <c r="F86" t="n">
+        <v>9.218999999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>9.17</v>
+        <v>9.151</v>
       </c>
       <c r="B87" t="n">
-        <v>92.2</v>
+        <v>83.3</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1680139396672406</v>
+        <v>0.1811493972437563</v>
       </c>
       <c r="D87" t="n">
-        <v>73.79000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="E87" t="n">
-        <v>9.153</v>
+        <v>2.97</v>
+      </c>
+      <c r="F87" t="n">
+        <v>9.137</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>9.217000000000001</v>
+        <v>9.176</v>
       </c>
       <c r="B88" t="n">
-        <v>88.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1710623188796476</v>
+        <v>0.1844799311898693</v>
       </c>
       <c r="D88" t="n">
-        <v>74</v>
+        <v>3.85</v>
       </c>
       <c r="E88" t="n">
-        <v>9.17</v>
+        <v>2.97</v>
+      </c>
+      <c r="F88" t="n">
+        <v>9.151</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>9.218999999999999</v>
+        <v>9.013</v>
       </c>
       <c r="B89" t="n">
-        <v>85.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="C89" t="n">
-        <v>0.1736085048429544</v>
+        <v>0.1866525485619172</v>
       </c>
       <c r="D89" t="n">
-        <v>74.73</v>
+        <v>3.83</v>
       </c>
       <c r="E89" t="n">
-        <v>9.217000000000001</v>
+        <v>2.97</v>
+      </c>
+      <c r="F89" t="n">
+        <v>9.176</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>9.137</v>
+        <v>9.022</v>
       </c>
       <c r="B90" t="n">
-        <v>83.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="C90" t="n">
-        <v>0.1766742413457597</v>
+        <v>0.1889202476362492</v>
       </c>
       <c r="D90" t="n">
-        <v>74.63</v>
+        <v>3.88</v>
       </c>
       <c r="E90" t="n">
-        <v>9.218999999999999</v>
+        <v>2.98</v>
+      </c>
+      <c r="F90" t="n">
+        <v>9.013</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>9.151</v>
+        <v>9.071</v>
       </c>
       <c r="B91" t="n">
-        <v>83.3</v>
+        <v>84.7</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1811493972437563</v>
+        <v>0.1911982123727116</v>
       </c>
       <c r="D91" t="n">
-        <v>74.34</v>
+        <v>4.02</v>
       </c>
       <c r="E91" t="n">
-        <v>9.137</v>
+        <v>2.97</v>
+      </c>
+      <c r="F91" t="n">
+        <v>9.022</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>9.176</v>
+        <v>9.215</v>
       </c>
       <c r="B92" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1844799311898693</v>
+        <v>0.1930333651321403</v>
       </c>
       <c r="D92" t="n">
-        <v>74.03</v>
+        <v>4.41</v>
       </c>
       <c r="E92" t="n">
-        <v>9.151</v>
+        <v>2.95</v>
+      </c>
+      <c r="F92" t="n">
+        <v>9.071</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>9.013</v>
+        <v>10.795</v>
       </c>
       <c r="B93" t="n">
-        <v>84.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1866525485619172</v>
+        <v>0.1946707017723681</v>
       </c>
       <c r="D93" t="n">
-        <v>74.16</v>
+        <v>4.58</v>
       </c>
       <c r="E93" t="n">
-        <v>9.176</v>
+        <v>2.95</v>
+      </c>
+      <c r="F93" t="n">
+        <v>9.215</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>9.022</v>
+        <v>10.344</v>
       </c>
       <c r="B94" t="n">
-        <v>84.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1889202476362492</v>
+        <v>0.1964415029468491</v>
       </c>
       <c r="D94" t="n">
-        <v>75.40000000000001</v>
+        <v>4.48</v>
       </c>
       <c r="E94" t="n">
-        <v>9.013</v>
+        <v>2.96</v>
+      </c>
+      <c r="F94" t="n">
+        <v>10.795</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9.071</v>
+        <v>9.68</v>
       </c>
       <c r="B95" t="n">
-        <v>84.7</v>
+        <v>79.7</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1911982123727116</v>
+        <v>0.1996723176564928</v>
       </c>
       <c r="D95" t="n">
-        <v>88.93000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="E95" t="n">
-        <v>9.022</v>
+        <v>2.94</v>
+      </c>
+      <c r="F95" t="n">
+        <v>10.344</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>9.215</v>
+        <v>9.221</v>
       </c>
       <c r="B96" t="n">
-        <v>84</v>
+        <v>80.7</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1930333651321403</v>
+        <v>0.2014703809751995</v>
       </c>
       <c r="D96" t="n">
-        <v>91.54000000000001</v>
+        <v>4.39</v>
       </c>
       <c r="E96" t="n">
-        <v>9.071</v>
+        <v>2.88</v>
+      </c>
+      <c r="F96" t="n">
+        <v>9.68</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>10.795</v>
+        <v>5.294</v>
       </c>
       <c r="B97" t="n">
-        <v>78.2</v>
+        <v>37.8</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1946707017723681</v>
+        <v>0.1656842182728042</v>
       </c>
       <c r="D97" t="n">
-        <v>91.43000000000001</v>
+        <v>3.14</v>
       </c>
       <c r="E97" t="n">
-        <v>9.215</v>
+        <v>5.38</v>
+      </c>
+      <c r="F97" t="n">
+        <v>5.336</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>10.344</v>
+        <v>4.973</v>
       </c>
       <c r="B98" t="n">
-        <v>78.40000000000001</v>
+        <v>43.1</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1964415029468491</v>
+        <v>0.1687051158658473</v>
       </c>
       <c r="D98" t="n">
-        <v>94.34999999999999</v>
+        <v>3.18</v>
       </c>
       <c r="E98" t="n">
-        <v>10.795</v>
+        <v>5.55</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5.294</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>9.68</v>
+        <v>5.184</v>
       </c>
       <c r="B99" t="n">
-        <v>79.7</v>
+        <v>49.5</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1996723176564928</v>
+        <v>0.1728397819676526</v>
       </c>
       <c r="D99" t="n">
-        <v>95.13</v>
+        <v>3.26</v>
       </c>
       <c r="E99" t="n">
-        <v>10.344</v>
+        <v>5.48</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4.973</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>9.221</v>
+        <v>5.957</v>
       </c>
       <c r="B100" t="n">
-        <v>80.7</v>
+        <v>48.9</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2014703809751995</v>
+        <v>0.1745763724933505</v>
       </c>
       <c r="D100" t="n">
-        <v>94.76000000000001</v>
+        <v>3.34</v>
       </c>
       <c r="E100" t="n">
-        <v>9.68</v>
+        <v>5.63</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5.184</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>9.173</v>
+        <v>6.844</v>
       </c>
       <c r="B101" t="n">
-        <v>81.7</v>
+        <v>43.7</v>
       </c>
       <c r="C101" t="n">
-        <v>0.204204654101594</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>0.1742929013131298</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3.28</v>
+      </c>
       <c r="E101" t="n">
-        <v>9.221</v>
+        <v>5.37</v>
+      </c>
+      <c r="F101" t="n">
+        <v>5.957</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>5.294</v>
+        <v>6.594</v>
       </c>
       <c r="B102" t="n">
-        <v>37.8</v>
+        <v>44.1</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1656842182728042</v>
+        <v>0.1743431661529</v>
       </c>
       <c r="D102" t="n">
-        <v>74.12</v>
+        <v>3.24</v>
       </c>
       <c r="E102" t="n">
-        <v>5.336</v>
+        <v>5.27</v>
+      </c>
+      <c r="F102" t="n">
+        <v>6.844</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4.973</v>
+        <v>6.055</v>
       </c>
       <c r="B103" t="n">
-        <v>43.1</v>
+        <v>48.7</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1687051158658473</v>
+        <v>0.1744957357519968</v>
       </c>
       <c r="D103" t="n">
-        <v>74.5</v>
+        <v>3.29</v>
       </c>
       <c r="E103" t="n">
-        <v>5.294</v>
+        <v>5.36</v>
+      </c>
+      <c r="F103" t="n">
+        <v>6.594</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>5.184</v>
+        <v>6.038</v>
       </c>
       <c r="B104" t="n">
-        <v>49.5</v>
+        <v>52.5</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1728397819676526</v>
+        <v>0.1770419486016253</v>
       </c>
       <c r="D104" t="n">
-        <v>76.77</v>
+        <v>3.28</v>
       </c>
       <c r="E104" t="n">
-        <v>4.973</v>
+        <v>5.53</v>
+      </c>
+      <c r="F104" t="n">
+        <v>6.055</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>5.957</v>
+        <v>6.198</v>
       </c>
       <c r="B105" t="n">
-        <v>48.9</v>
+        <v>55.3</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1745763724933505</v>
+        <v>0.1803194124410873</v>
       </c>
       <c r="D105" t="n">
-        <v>76.98999999999999</v>
+        <v>3.33</v>
       </c>
       <c r="E105" t="n">
-        <v>5.184</v>
+        <v>5.01</v>
+      </c>
+      <c r="F105" t="n">
+        <v>6.038</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>6.844</v>
+        <v>6.263</v>
       </c>
       <c r="B106" t="n">
-        <v>43.7</v>
+        <v>57.7</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1742929013131298</v>
+        <v>0.1837509566285332</v>
       </c>
       <c r="D106" t="n">
-        <v>73.90000000000001</v>
+        <v>3.36</v>
       </c>
       <c r="E106" t="n">
-        <v>5.957</v>
+        <v>5.01</v>
+      </c>
+      <c r="F106" t="n">
+        <v>6.198</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>6.594</v>
+        <v>6.521</v>
       </c>
       <c r="B107" t="n">
-        <v>44.1</v>
+        <v>57.6</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1743431661529</v>
+        <v>0.1875843239255592</v>
       </c>
       <c r="D107" t="n">
-        <v>73.90000000000001</v>
+        <v>3.41</v>
       </c>
       <c r="E107" t="n">
-        <v>6.844</v>
+        <v>4.96</v>
+      </c>
+      <c r="F107" t="n">
+        <v>6.263</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6.055</v>
+        <v>6.569</v>
       </c>
       <c r="B108" t="n">
-        <v>48.7</v>
+        <v>59.2</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1744957357519968</v>
+        <v>0.1902246600159277</v>
       </c>
       <c r="D108" t="n">
-        <v>75.56</v>
+        <v>3.46</v>
       </c>
       <c r="E108" t="n">
-        <v>6.594</v>
+        <v>4.76</v>
+      </c>
+      <c r="F108" t="n">
+        <v>6.521</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>6.038</v>
+        <v>6.466</v>
       </c>
       <c r="B109" t="n">
-        <v>52.5</v>
+        <v>62.3</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1770419486016253</v>
+        <v>0.1934229478540781</v>
       </c>
       <c r="D109" t="n">
-        <v>72.39</v>
+        <v>3.47</v>
       </c>
       <c r="E109" t="n">
-        <v>6.055</v>
+        <v>4.69</v>
+      </c>
+      <c r="F109" t="n">
+        <v>6.569</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>6.198</v>
+        <v>6.563</v>
       </c>
       <c r="B110" t="n">
-        <v>55.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>0.1803194124410873</v>
+        <v>0.1958725920737333</v>
       </c>
       <c r="D110" t="n">
-        <v>79.41</v>
+        <v>3.48</v>
       </c>
       <c r="E110" t="n">
-        <v>6.038</v>
+        <v>4.57</v>
+      </c>
+      <c r="F110" t="n">
+        <v>6.466</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>6.263</v>
+        <v>6.648</v>
       </c>
       <c r="B111" t="n">
-        <v>57.7</v>
+        <v>67.8</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1837509566285332</v>
+        <v>0.197647982367416</v>
       </c>
       <c r="D111" t="n">
-        <v>79.78</v>
+        <v>3.47</v>
       </c>
       <c r="E111" t="n">
-        <v>6.198</v>
+        <v>4.63</v>
+      </c>
+      <c r="F111" t="n">
+        <v>6.563</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>6.521</v>
+        <v>7.472</v>
       </c>
       <c r="B112" t="n">
-        <v>57.6</v>
+        <v>68.7</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1875843239255592</v>
+        <v>0.2003708118130049</v>
       </c>
       <c r="D112" t="n">
-        <v>79.41</v>
+        <v>3.48</v>
       </c>
       <c r="E112" t="n">
-        <v>6.263</v>
+        <v>4.57</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.648</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>6.569</v>
+        <v>7.476</v>
       </c>
       <c r="B113" t="n">
-        <v>59.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1902246600159277</v>
+        <v>0.2034790702430252</v>
       </c>
       <c r="D113" t="n">
-        <v>80.09</v>
+        <v>3.43</v>
       </c>
       <c r="E113" t="n">
-        <v>6.521</v>
+        <v>4.48</v>
+      </c>
+      <c r="F113" t="n">
+        <v>7.472</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6.466</v>
+        <v>6.936</v>
       </c>
       <c r="B114" t="n">
-        <v>62.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1934229478540781</v>
+        <v>0.2043451099117282</v>
       </c>
       <c r="D114" t="n">
-        <v>79.94</v>
+        <v>3.47</v>
       </c>
       <c r="E114" t="n">
-        <v>6.569</v>
+        <v>4.39</v>
+      </c>
+      <c r="F114" t="n">
+        <v>7.476</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6.563</v>
+        <v>7.471</v>
       </c>
       <c r="B115" t="n">
-        <v>65.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1958725920737333</v>
+        <v>0.202398593145538</v>
       </c>
       <c r="D115" t="n">
-        <v>82.8</v>
+        <v>3.48</v>
       </c>
       <c r="E115" t="n">
-        <v>6.466</v>
+        <v>4.17</v>
+      </c>
+      <c r="F115" t="n">
+        <v>6.936</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6.648</v>
+        <v>8.289</v>
       </c>
       <c r="B116" t="n">
-        <v>67.8</v>
+        <v>142</v>
       </c>
       <c r="C116" t="n">
-        <v>0.197647982367416</v>
+        <v>0.1586789624052656</v>
       </c>
       <c r="D116" t="n">
-        <v>83.05</v>
+        <v>2.85</v>
       </c>
       <c r="E116" t="n">
-        <v>6.563</v>
+        <v>7.05</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8.06</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>7.472</v>
+        <v>8.286</v>
       </c>
       <c r="B117" t="n">
-        <v>68.7</v>
+        <v>140.7</v>
       </c>
       <c r="C117" t="n">
-        <v>0.2003708118130049</v>
+        <v>0.1600517925709437</v>
       </c>
       <c r="D117" t="n">
-        <v>81.53</v>
+        <v>2.87</v>
       </c>
       <c r="E117" t="n">
-        <v>6.648</v>
+        <v>6.99</v>
+      </c>
+      <c r="F117" t="n">
+        <v>8.289</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>7.476</v>
+        <v>8.084</v>
       </c>
       <c r="B118" t="n">
-        <v>71.09999999999999</v>
+        <v>143.3</v>
       </c>
       <c r="C118" t="n">
-        <v>0.2034790702430252</v>
+        <v>0.1646246746466475</v>
       </c>
       <c r="D118" t="n">
-        <v>86.86</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
-        <v>7.472</v>
+        <v>6.73</v>
+      </c>
+      <c r="F118" t="n">
+        <v>8.286</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>6.936</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="B119" t="n">
-        <v>75.40000000000001</v>
+        <v>144</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2043451099117282</v>
+        <v>0.1651228453854403</v>
       </c>
       <c r="D119" t="n">
-        <v>87.63</v>
+        <v>3.07</v>
       </c>
       <c r="E119" t="n">
-        <v>7.476</v>
+        <v>6.57</v>
+      </c>
+      <c r="F119" t="n">
+        <v>8.084</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>7.471</v>
+        <v>9.162000000000001</v>
       </c>
       <c r="B120" t="n">
-        <v>73.2</v>
+        <v>140.5</v>
       </c>
       <c r="C120" t="n">
-        <v>0.202398593145538</v>
+        <v>0.1674831787986964</v>
       </c>
       <c r="D120" t="n">
-        <v>88.23</v>
+        <v>3.13</v>
       </c>
       <c r="E120" t="n">
-        <v>6.936</v>
+        <v>6.25</v>
+      </c>
+      <c r="F120" t="n">
+        <v>8.343999999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>7.836</v>
+        <v>9.141999999999999</v>
       </c>
       <c r="B121" t="n">
-        <v>72.59999999999999</v>
+        <v>139.8</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2047455166157824</v>
-      </c>
-      <c r="D121" t="inlineStr"/>
+        <v>0.1701305091146716</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3.18</v>
+      </c>
       <c r="E121" t="n">
-        <v>7.471</v>
+        <v>5.85</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9.162000000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>8.289</v>
+        <v>9.239000000000001</v>
       </c>
       <c r="B122" t="n">
-        <v>142</v>
+        <v>141.8</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1586789624052656</v>
+        <v>0.1750684057897678</v>
       </c>
       <c r="D122" t="n">
-        <v>130.38</v>
+        <v>3.26</v>
       </c>
       <c r="E122" t="n">
-        <v>8.06</v>
+        <v>5.52</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.141999999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>8.286</v>
+        <v>9.617000000000001</v>
       </c>
       <c r="B123" t="n">
-        <v>140.7</v>
+        <v>142.5</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1600517925709437</v>
+        <v>0.1813722595087412</v>
       </c>
       <c r="D123" t="n">
-        <v>132.39</v>
+        <v>3.26</v>
       </c>
       <c r="E123" t="n">
-        <v>8.289</v>
+        <v>5.3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9.239000000000001</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>8.084</v>
+        <v>9.845000000000001</v>
       </c>
       <c r="B124" t="n">
-        <v>143.3</v>
+        <v>142.5</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1646246746466475</v>
+        <v>0.1876274491520957</v>
       </c>
       <c r="D124" t="n">
-        <v>133.17</v>
+        <v>3.33</v>
       </c>
       <c r="E124" t="n">
-        <v>8.286</v>
+        <v>4.87</v>
+      </c>
+      <c r="F124" t="n">
+        <v>9.617000000000001</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>8.343999999999999</v>
+        <v>9.831</v>
       </c>
       <c r="B125" t="n">
-        <v>144</v>
+        <v>140.4</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1651228453854403</v>
+        <v>0.1938166702438147</v>
       </c>
       <c r="D125" t="n">
-        <v>121.06</v>
+        <v>3.38</v>
       </c>
       <c r="E125" t="n">
-        <v>8.084</v>
+        <v>4.53</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9.845000000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>9.162000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="B126" t="n">
-        <v>140.5</v>
+        <v>138</v>
       </c>
       <c r="C126" t="n">
-        <v>0.1674831787986964</v>
+        <v>0.1994585647415006</v>
       </c>
       <c r="D126" t="n">
-        <v>115.86</v>
+        <v>3.41</v>
       </c>
       <c r="E126" t="n">
-        <v>8.343999999999999</v>
+        <v>4.35</v>
+      </c>
+      <c r="F126" t="n">
+        <v>9.831</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>9.141999999999999</v>
+        <v>9.456</v>
       </c>
       <c r="B127" t="n">
-        <v>139.8</v>
+        <v>137.8</v>
       </c>
       <c r="C127" t="n">
-        <v>0.1701305091146716</v>
+        <v>0.2046728559796534</v>
       </c>
       <c r="D127" t="n">
-        <v>111.13</v>
+        <v>3.42</v>
       </c>
       <c r="E127" t="n">
-        <v>9.162000000000001</v>
+        <v>3.97</v>
+      </c>
+      <c r="F127" t="n">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>9.239000000000001</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="B128" t="n">
-        <v>141.8</v>
+        <v>137.6</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1750684057897678</v>
+        <v>0.2089611009545732</v>
       </c>
       <c r="D128" t="n">
-        <v>113.19</v>
+        <v>3.47</v>
       </c>
       <c r="E128" t="n">
-        <v>9.141999999999999</v>
+        <v>3.28</v>
+      </c>
+      <c r="F128" t="n">
+        <v>9.456</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>9.617000000000001</v>
+        <v>9.103</v>
       </c>
       <c r="B129" t="n">
-        <v>142.5</v>
+        <v>137.2</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1813722595087412</v>
+        <v>0.2139107911476784</v>
       </c>
       <c r="D129" t="n">
-        <v>119.54</v>
+        <v>3.49</v>
       </c>
       <c r="E129" t="n">
-        <v>9.239000000000001</v>
+        <v>3.21</v>
+      </c>
+      <c r="F129" t="n">
+        <v>9.191000000000001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>9.845000000000001</v>
+        <v>9.223000000000001</v>
       </c>
       <c r="B130" t="n">
-        <v>142.5</v>
+        <v>136.3</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1876274491520957</v>
+        <v>0.2183498887895962</v>
       </c>
       <c r="D130" t="n">
-        <v>121.55</v>
+        <v>3.57</v>
       </c>
       <c r="E130" t="n">
-        <v>9.617000000000001</v>
+        <v>3.3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>9.103</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>9.831</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="B131" t="n">
-        <v>140.4</v>
+        <v>140.1</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1938166702438147</v>
+        <v>0.2228432452076741</v>
       </c>
       <c r="D131" t="n">
-        <v>124.67</v>
+        <v>3.61</v>
       </c>
       <c r="E131" t="n">
-        <v>9.845000000000001</v>
+        <v>2.83</v>
+      </c>
+      <c r="F131" t="n">
+        <v>9.223000000000001</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="B132" t="n">
+        <v>135</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.2269578930762318</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F132" t="n">
         <v>9.699999999999999</v>
-      </c>
-      <c r="B132" t="n">
-        <v>138</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0.1994585647415006</v>
-      </c>
-      <c r="D132" t="n">
-        <v>119.88</v>
-      </c>
-      <c r="E132" t="n">
-        <v>9.831</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>9.456</v>
+        <v>9.742000000000001</v>
       </c>
       <c r="B133" t="n">
-        <v>137.8</v>
+        <v>132.5</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2046728559796534</v>
-      </c>
-      <c r="D133" t="n">
-        <v>121.24</v>
-      </c>
-      <c r="E133" t="n">
-        <v>9.699999999999999</v>
+        <v>0.2305300004091387</v>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>9.91</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>9.191000000000001</v>
+        <v>10.474</v>
       </c>
       <c r="B134" t="n">
-        <v>137.6</v>
+        <v>127.5</v>
       </c>
       <c r="C134" t="n">
-        <v>0.2089611009545732</v>
-      </c>
-      <c r="D134" t="n">
-        <v>118.99</v>
-      </c>
-      <c r="E134" t="n">
-        <v>9.456</v>
+        <v>0.2326595937792619</v>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>9.742000000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>9.103</v>
+        <v>10.237</v>
       </c>
       <c r="B135" t="n">
-        <v>137.2</v>
+        <v>126.6</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2139107911476784</v>
+        <v>0.1630931802226025</v>
       </c>
       <c r="D135" t="n">
-        <v>121.46</v>
+        <v>3.34</v>
       </c>
       <c r="E135" t="n">
-        <v>9.191000000000001</v>
+        <v>7.22</v>
+      </c>
+      <c r="F135" t="n">
+        <v>10.212</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>9.223000000000001</v>
+        <v>10.398</v>
       </c>
       <c r="B136" t="n">
-        <v>136.3</v>
+        <v>124.8</v>
       </c>
       <c r="C136" t="n">
-        <v>0.2183498887895962</v>
+        <v>0.1635523912165553</v>
       </c>
       <c r="D136" t="n">
-        <v>120.8</v>
+        <v>3.33</v>
       </c>
       <c r="E136" t="n">
-        <v>9.103</v>
+        <v>7.11</v>
+      </c>
+      <c r="F136" t="n">
+        <v>10.237</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>9.699999999999999</v>
+        <v>10.334</v>
       </c>
       <c r="B137" t="n">
-        <v>140.1</v>
+        <v>123.1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.2228432452076741</v>
+        <v>0.163243073127508</v>
       </c>
       <c r="D137" t="n">
-        <v>118.96</v>
+        <v>3.31</v>
       </c>
       <c r="E137" t="n">
-        <v>9.223000000000001</v>
+        <v>7.06</v>
+      </c>
+      <c r="F137" t="n">
+        <v>10.398</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>9.91</v>
+        <v>10.513</v>
       </c>
       <c r="B138" t="n">
-        <v>135</v>
+        <v>122.2</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2269578930762318</v>
+        <v>0.1638660048722962</v>
       </c>
       <c r="D138" t="n">
-        <v>123.84</v>
+        <v>3.31</v>
       </c>
       <c r="E138" t="n">
-        <v>9.699999999999999</v>
+        <v>6.9</v>
+      </c>
+      <c r="F138" t="n">
+        <v>10.334</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>9.742000000000001</v>
+        <v>11.291</v>
       </c>
       <c r="B139" t="n">
-        <v>132.5</v>
+        <v>124</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2305300004091387</v>
+        <v>0.1649578977391626</v>
       </c>
       <c r="D139" t="n">
-        <v>123.95</v>
+        <v>3.27</v>
       </c>
       <c r="E139" t="n">
-        <v>9.91</v>
+        <v>6.66</v>
+      </c>
+      <c r="F139" t="n">
+        <v>10.513</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>10.474</v>
+        <v>11.224</v>
       </c>
       <c r="B140" t="n">
-        <v>127.5</v>
+        <v>122.8</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2326595937792619</v>
+        <v>0.1660920972681608</v>
       </c>
       <c r="D140" t="n">
-        <v>125.99</v>
+        <v>3.27</v>
       </c>
       <c r="E140" t="n">
-        <v>9.742000000000001</v>
+        <v>6.43</v>
+      </c>
+      <c r="F140" t="n">
+        <v>11.291</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>10.603</v>
+        <v>11.176</v>
       </c>
       <c r="B141" t="n">
-        <v>122.9</v>
+        <v>122.5</v>
       </c>
       <c r="C141" t="n">
-        <v>0.2336564623149331</v>
-      </c>
-      <c r="D141" t="inlineStr"/>
+        <v>0.1673862894285038</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3.06</v>
+      </c>
       <c r="E141" t="n">
-        <v>10.474</v>
+        <v>6.36</v>
+      </c>
+      <c r="F141" t="n">
+        <v>11.224</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>10.237</v>
+        <v>11.337</v>
       </c>
       <c r="B142" t="n">
-        <v>126.6</v>
+        <v>123</v>
       </c>
       <c r="C142" t="n">
-        <v>0.1630931802226025</v>
+        <v>0.1713932918744115</v>
       </c>
       <c r="D142" t="n">
-        <v>154.06</v>
+        <v>3.07</v>
       </c>
       <c r="E142" t="n">
-        <v>10.212</v>
+        <v>6.34</v>
+      </c>
+      <c r="F142" t="n">
+        <v>11.176</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>10.398</v>
+        <v>11.478</v>
       </c>
       <c r="B143" t="n">
-        <v>124.8</v>
+        <v>123</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1635523912165553</v>
+        <v>0.1756759681922429</v>
       </c>
       <c r="D143" t="n">
-        <v>154.56</v>
+        <v>3.08</v>
       </c>
       <c r="E143" t="n">
-        <v>10.237</v>
+        <v>6.27</v>
+      </c>
+      <c r="F143" t="n">
+        <v>11.337</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>10.334</v>
+        <v>11.579</v>
       </c>
       <c r="B144" t="n">
-        <v>123.1</v>
+        <v>121.5</v>
       </c>
       <c r="C144" t="n">
-        <v>0.163243073127508</v>
+        <v>0.1796300606444581</v>
       </c>
       <c r="D144" t="n">
-        <v>154.43</v>
+        <v>3.09</v>
       </c>
       <c r="E144" t="n">
-        <v>10.398</v>
+        <v>6.2</v>
+      </c>
+      <c r="F144" t="n">
+        <v>11.478</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>10.513</v>
+        <v>11.5</v>
       </c>
       <c r="B145" t="n">
-        <v>122.2</v>
+        <v>119.4</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1638660048722962</v>
+        <v>0.184089633065788</v>
       </c>
       <c r="D145" t="n">
-        <v>154.89</v>
+        <v>3.11</v>
       </c>
       <c r="E145" t="n">
-        <v>10.334</v>
+        <v>6.13</v>
+      </c>
+      <c r="F145" t="n">
+        <v>11.579</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>11.291</v>
+        <v>11.57</v>
       </c>
       <c r="B146" t="n">
-        <v>124</v>
+        <v>117.7</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1649578977391626</v>
+        <v>0.1885813089334645</v>
       </c>
       <c r="D146" t="n">
-        <v>153.59</v>
+        <v>3.12</v>
       </c>
       <c r="E146" t="n">
-        <v>10.513</v>
+        <v>6.06</v>
+      </c>
+      <c r="F146" t="n">
+        <v>11.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>11.224</v>
+        <v>11.449</v>
       </c>
       <c r="B147" t="n">
-        <v>122.8</v>
+        <v>115.6</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1660920972681608</v>
+        <v>0.1929025968279871</v>
       </c>
       <c r="D147" t="n">
-        <v>153.46</v>
+        <v>3.14</v>
       </c>
       <c r="E147" t="n">
-        <v>11.291</v>
+        <v>5.98</v>
+      </c>
+      <c r="F147" t="n">
+        <v>11.57</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>11.176</v>
+        <v>11.308</v>
       </c>
       <c r="B148" t="n">
-        <v>122.5</v>
+        <v>114.5</v>
       </c>
       <c r="C148" t="n">
-        <v>0.1673862894285038</v>
+        <v>0.1965427591445402</v>
       </c>
       <c r="D148" t="n">
-        <v>137.74</v>
+        <v>3.14</v>
       </c>
       <c r="E148" t="n">
-        <v>11.224</v>
+        <v>5.89</v>
+      </c>
+      <c r="F148" t="n">
+        <v>11.449</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>11.337</v>
+        <v>11.171</v>
       </c>
       <c r="B149" t="n">
-        <v>123</v>
+        <v>113.9</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1713932918744115</v>
+        <v>0.2000985399552338</v>
       </c>
       <c r="D149" t="n">
-        <v>138.01</v>
+        <v>3.16</v>
       </c>
       <c r="E149" t="n">
-        <v>11.176</v>
+        <v>5.83</v>
+      </c>
+      <c r="F149" t="n">
+        <v>11.308</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>11.478</v>
+        <v>12.129</v>
       </c>
       <c r="B150" t="n">
-        <v>123</v>
+        <v>112.3</v>
       </c>
       <c r="C150" t="n">
-        <v>0.1756759681922429</v>
+        <v>0.2037363592493313</v>
       </c>
       <c r="D150" t="n">
-        <v>138.99</v>
+        <v>3.17</v>
       </c>
       <c r="E150" t="n">
-        <v>11.337</v>
+        <v>5.72</v>
+      </c>
+      <c r="F150" t="n">
+        <v>11.171</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>11.579</v>
+        <v>12.249</v>
       </c>
       <c r="B151" t="n">
-        <v>121.5</v>
+        <v>111</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1796300606444581</v>
+        <v>0.2062662981446766</v>
       </c>
       <c r="D151" t="n">
-        <v>139.35</v>
-      </c>
-      <c r="E151" t="n">
-        <v>11.478</v>
+        <v>3.18</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="n">
+        <v>12.129</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>11.5</v>
+        <v>11.835</v>
       </c>
       <c r="B152" t="n">
-        <v>119.4</v>
+        <v>107.7</v>
       </c>
       <c r="C152" t="n">
-        <v>0.184089633065788</v>
+        <v>0.2086942516329779</v>
       </c>
       <c r="D152" t="n">
-        <v>139.35</v>
-      </c>
-      <c r="E152" t="n">
-        <v>11.579</v>
+        <v>3.19</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="n">
+        <v>12.249</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>11.57</v>
+        <v>11.503</v>
       </c>
       <c r="B153" t="n">
-        <v>117.7</v>
+        <v>107.7</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1885813089334645</v>
-      </c>
-      <c r="D153" t="n">
-        <v>139.46</v>
-      </c>
-      <c r="E153" t="n">
-        <v>11.5</v>
+        <v>0.2112970198987334</v>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="n">
+        <v>11.835</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>11.449</v>
+        <v>8.760999999999999</v>
       </c>
       <c r="B154" t="n">
-        <v>115.6</v>
+        <v>80.2</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1929025968279871</v>
+        <v>0.1828291785749968</v>
       </c>
       <c r="D154" t="n">
-        <v>140.25</v>
+        <v>5.06</v>
       </c>
       <c r="E154" t="n">
-        <v>11.57</v>
+        <v>4.78</v>
+      </c>
+      <c r="F154" t="n">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>11.308</v>
+        <v>8.396000000000001</v>
       </c>
       <c r="B155" t="n">
-        <v>114.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1965427591445402</v>
+        <v>0.184548787992348</v>
       </c>
       <c r="D155" t="n">
-        <v>139.9</v>
+        <v>5.41</v>
       </c>
       <c r="E155" t="n">
-        <v>11.449</v>
+        <v>4.87</v>
+      </c>
+      <c r="F155" t="n">
+        <v>8.760999999999999</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>11.171</v>
+        <v>8.523</v>
       </c>
       <c r="B156" t="n">
-        <v>113.9</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C156" t="n">
-        <v>0.2000985399552338</v>
+        <v>0.1858613186942235</v>
       </c>
       <c r="D156" t="n">
-        <v>140.15</v>
+        <v>5.63</v>
       </c>
       <c r="E156" t="n">
-        <v>11.308</v>
+        <v>4.88</v>
+      </c>
+      <c r="F156" t="n">
+        <v>8.396000000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>12.129</v>
+        <v>8.948</v>
       </c>
       <c r="B157" t="n">
-        <v>112.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="C157" t="n">
-        <v>0.2037363592493313</v>
+        <v>0.1866335555477804</v>
       </c>
       <c r="D157" t="n">
-        <v>139.05</v>
+        <v>5.71</v>
       </c>
       <c r="E157" t="n">
-        <v>11.171</v>
+        <v>4.84</v>
+      </c>
+      <c r="F157" t="n">
+        <v>8.523</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>12.249</v>
+        <v>9.536</v>
       </c>
       <c r="B158" t="n">
-        <v>111</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="C158" t="n">
-        <v>0.2062662981446766</v>
+        <v>0.1877314890968652</v>
       </c>
       <c r="D158" t="n">
-        <v>138.02</v>
+        <v>5.79</v>
       </c>
       <c r="E158" t="n">
-        <v>12.129</v>
+        <v>4.93</v>
+      </c>
+      <c r="F158" t="n">
+        <v>8.948</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>11.835</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="B159" t="n">
-        <v>107.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>0.2086942516329779</v>
+        <v>0.189768968141758</v>
       </c>
       <c r="D159" t="n">
-        <v>137.23</v>
+        <v>5.76</v>
       </c>
       <c r="E159" t="n">
-        <v>12.249</v>
+        <v>4.48</v>
+      </c>
+      <c r="F159" t="n">
+        <v>9.536</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>11.503</v>
+        <v>9.186</v>
       </c>
       <c r="B160" t="n">
-        <v>107.7</v>
+        <v>70.8</v>
       </c>
       <c r="C160" t="n">
-        <v>0.2112970198987334</v>
+        <v>0.1929009604264598</v>
       </c>
       <c r="D160" t="n">
-        <v>139.08</v>
+        <v>5.78</v>
       </c>
       <c r="E160" t="n">
-        <v>11.835</v>
+        <v>4.47</v>
+      </c>
+      <c r="F160" t="n">
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>11.541</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="B161" t="n">
-        <v>106.6</v>
+        <v>64.8</v>
       </c>
       <c r="C161" t="n">
-        <v>0.2151933157090585</v>
-      </c>
-      <c r="D161" t="inlineStr"/>
+        <v>0.1966787974389536</v>
+      </c>
+      <c r="D161" t="n">
+        <v>5.78</v>
+      </c>
       <c r="E161" t="n">
-        <v>11.503</v>
+        <v>4.45</v>
+      </c>
+      <c r="F161" t="n">
+        <v>9.186</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>8.760999999999999</v>
+        <v>8.522</v>
       </c>
       <c r="B162" t="n">
-        <v>80.2</v>
+        <v>61.9</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1828291785749968</v>
+        <v>0.2006391535872529</v>
       </c>
       <c r="D162" t="n">
-        <v>27.14</v>
+        <v>5.81</v>
       </c>
       <c r="E162" t="n">
-        <v>8.300000000000001</v>
+        <v>4.24</v>
+      </c>
+      <c r="F162" t="n">
+        <v>9.042999999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>8.396000000000001</v>
+        <v>7.944</v>
       </c>
       <c r="B163" t="n">
-        <v>83.40000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="C163" t="n">
-        <v>0.184548787992348</v>
+        <v>0.2048656117015703</v>
       </c>
       <c r="D163" t="n">
-        <v>25.85</v>
+        <v>5.87</v>
       </c>
       <c r="E163" t="n">
-        <v>8.760999999999999</v>
+        <v>4.24</v>
+      </c>
+      <c r="F163" t="n">
+        <v>8.522</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>8.523</v>
+        <v>8.266999999999999</v>
       </c>
       <c r="B164" t="n">
-        <v>84.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1858613186942235</v>
+        <v>0.2089767211658702</v>
       </c>
       <c r="D164" t="n">
-        <v>32.63</v>
+        <v>5.9</v>
       </c>
       <c r="E164" t="n">
-        <v>8.396000000000001</v>
+        <v>4.25</v>
+      </c>
+      <c r="F164" t="n">
+        <v>7.944</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>8.948</v>
+        <v>8.451000000000001</v>
       </c>
       <c r="B165" t="n">
-        <v>84.90000000000001</v>
+        <v>56.8</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1866335555477804</v>
+        <v>0.2126211591739718</v>
       </c>
       <c r="D165" t="n">
-        <v>28.5</v>
+        <v>6.12</v>
       </c>
       <c r="E165" t="n">
-        <v>8.523</v>
+        <v>4.2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>8.266999999999999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>9.536</v>
+        <v>8.113</v>
       </c>
       <c r="B166" t="n">
-        <v>87.09999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="C166" t="n">
-        <v>0.1877314890968652</v>
+        <v>0.2154252807318739</v>
       </c>
       <c r="D166" t="n">
-        <v>29.13</v>
+        <v>6.07</v>
       </c>
       <c r="E166" t="n">
-        <v>8.948</v>
+        <v>4.21</v>
+      </c>
+      <c r="F166" t="n">
+        <v>8.451000000000001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>9.619999999999999</v>
+        <v>8.073</v>
       </c>
       <c r="B167" t="n">
-        <v>80.09999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="C167" t="n">
-        <v>0.189768968141758</v>
+        <v>0.2178685459165742</v>
       </c>
       <c r="D167" t="n">
-        <v>31.62</v>
+        <v>6.1</v>
       </c>
       <c r="E167" t="n">
-        <v>9.536</v>
+        <v>4.2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>8.113</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>9.186</v>
+        <v>8.117000000000001</v>
       </c>
       <c r="B168" t="n">
-        <v>70.8</v>
+        <v>54.5</v>
       </c>
       <c r="C168" t="n">
-        <v>0.1929009604264598</v>
+        <v>0.2203600339742307</v>
       </c>
       <c r="D168" t="n">
-        <v>31.41</v>
+        <v>6.16</v>
       </c>
       <c r="E168" t="n">
-        <v>9.619999999999999</v>
+        <v>4.18</v>
+      </c>
+      <c r="F168" t="n">
+        <v>8.073</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>9.042999999999999</v>
+        <v>9.381</v>
       </c>
       <c r="B169" t="n">
-        <v>64.8</v>
+        <v>51.3</v>
       </c>
       <c r="C169" t="n">
-        <v>0.1966787974389536</v>
+        <v>0.2226230843401145</v>
       </c>
       <c r="D169" t="n">
-        <v>32.22</v>
+        <v>6.19</v>
       </c>
       <c r="E169" t="n">
-        <v>9.186</v>
+        <v>4.23</v>
+      </c>
+      <c r="F169" t="n">
+        <v>8.117000000000001</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>8.522</v>
+        <v>9.032</v>
       </c>
       <c r="B170" t="n">
-        <v>61.9</v>
+        <v>52.2</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2006391535872529</v>
+        <v>0.2254835638122936</v>
       </c>
       <c r="D170" t="n">
-        <v>32.58</v>
+        <v>6.37</v>
       </c>
       <c r="E170" t="n">
-        <v>9.042999999999999</v>
+        <v>4.27</v>
+      </c>
+      <c r="F170" t="n">
+        <v>9.381</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>7.944</v>
+        <v>8.449</v>
       </c>
       <c r="B171" t="n">
-        <v>60.2</v>
+        <v>54.1</v>
       </c>
       <c r="C171" t="n">
-        <v>0.2048656117015703</v>
+        <v>0.227671087871896</v>
       </c>
       <c r="D171" t="n">
-        <v>40.16</v>
+        <v>6.56</v>
       </c>
       <c r="E171" t="n">
-        <v>8.522</v>
+        <v>4.26</v>
+      </c>
+      <c r="F171" t="n">
+        <v>9.032</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>8.266999999999999</v>
+        <v>8.394</v>
       </c>
       <c r="B172" t="n">
-        <v>58.3</v>
+        <v>55.5</v>
       </c>
       <c r="C172" t="n">
-        <v>0.2089767211658702</v>
+        <v>0.2301800598464641</v>
       </c>
       <c r="D172" t="n">
-        <v>40.99</v>
+        <v>6.61</v>
       </c>
       <c r="E172" t="n">
-        <v>7.944</v>
+        <v>4.24</v>
+      </c>
+      <c r="F172" t="n">
+        <v>8.449</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>8.451000000000001</v>
+        <v>7.992</v>
       </c>
       <c r="B173" t="n">
-        <v>56.8</v>
+        <v>40.8</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2126211591739718</v>
+        <v>0.156235835052645</v>
       </c>
       <c r="D173" t="n">
-        <v>42.16</v>
+        <v>2.78</v>
       </c>
       <c r="E173" t="n">
-        <v>8.266999999999999</v>
+        <v>7.89</v>
+      </c>
+      <c r="F173" t="n">
+        <v>7.766</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>8.113</v>
+        <v>7.786</v>
       </c>
       <c r="B174" t="n">
-        <v>55.6</v>
+        <v>39.2</v>
       </c>
       <c r="C174" t="n">
-        <v>0.2154252807318739</v>
+        <v>0.1578622749124926</v>
       </c>
       <c r="D174" t="n">
-        <v>43.37</v>
+        <v>3.04</v>
       </c>
       <c r="E174" t="n">
-        <v>8.451000000000001</v>
+        <v>7.93</v>
+      </c>
+      <c r="F174" t="n">
+        <v>7.992</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>8.073</v>
+        <v>7.207</v>
       </c>
       <c r="B175" t="n">
-        <v>54.9</v>
+        <v>41.2</v>
       </c>
       <c r="C175" t="n">
-        <v>0.2178685459165742</v>
+        <v>0.1594568652707418</v>
       </c>
       <c r="D175" t="n">
-        <v>40.93</v>
+        <v>2.8</v>
       </c>
       <c r="E175" t="n">
-        <v>8.113</v>
+        <v>7.15</v>
+      </c>
+      <c r="F175" t="n">
+        <v>7.786</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>8.117000000000001</v>
+        <v>7.093</v>
       </c>
       <c r="B176" t="n">
-        <v>54.5</v>
+        <v>42.5</v>
       </c>
       <c r="C176" t="n">
-        <v>0.2203600339742307</v>
+        <v>0.1616555675577311</v>
       </c>
       <c r="D176" t="n">
-        <v>44.14</v>
+        <v>3.09</v>
       </c>
       <c r="E176" t="n">
-        <v>8.073</v>
+        <v>7.07</v>
+      </c>
+      <c r="F176" t="n">
+        <v>7.207</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>9.381</v>
+        <v>7.237</v>
       </c>
       <c r="B177" t="n">
-        <v>51.3</v>
+        <v>38.9</v>
       </c>
       <c r="C177" t="n">
-        <v>0.2226230843401145</v>
+        <v>0.1635212927955657</v>
       </c>
       <c r="D177" t="n">
-        <v>44.58</v>
+        <v>3.02</v>
       </c>
       <c r="E177" t="n">
-        <v>8.117000000000001</v>
+        <v>7.09</v>
+      </c>
+      <c r="F177" t="n">
+        <v>7.093</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>9.032</v>
+        <v>7.464</v>
       </c>
       <c r="B178" t="n">
-        <v>52.2</v>
+        <v>39.7</v>
       </c>
       <c r="C178" t="n">
-        <v>0.2254835638122936</v>
+        <v>0.1661103635153007</v>
       </c>
       <c r="D178" t="n">
-        <v>46.81</v>
+        <v>2.87</v>
       </c>
       <c r="E178" t="n">
-        <v>9.381</v>
+        <v>7.12</v>
+      </c>
+      <c r="F178" t="n">
+        <v>7.237</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>8.449</v>
+        <v>7.493</v>
       </c>
       <c r="B179" t="n">
-        <v>54.1</v>
+        <v>39.5</v>
       </c>
       <c r="C179" t="n">
-        <v>0.227671087871896</v>
+        <v>0.1673524458221449</v>
       </c>
       <c r="D179" t="n">
-        <v>45.79</v>
+        <v>2.96</v>
       </c>
       <c r="E179" t="n">
-        <v>9.032</v>
+        <v>7.15</v>
+      </c>
+      <c r="F179" t="n">
+        <v>7.464</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>8.394</v>
+        <v>7.43</v>
       </c>
       <c r="B180" t="n">
-        <v>55.5</v>
+        <v>38.8</v>
       </c>
       <c r="C180" t="n">
-        <v>0.2301800598464641</v>
+        <v>0.1687400982186233</v>
       </c>
       <c r="D180" t="n">
-        <v>46.97</v>
+        <v>3.09</v>
       </c>
       <c r="E180" t="n">
-        <v>8.449</v>
+        <v>6.94</v>
+      </c>
+      <c r="F180" t="n">
+        <v>7.493</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>8.112</v>
+        <v>7.236</v>
       </c>
       <c r="B181" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
+        <v>39.4</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.1715394760112175</v>
+      </c>
+      <c r="D181" t="n">
+        <v>3.22</v>
+      </c>
       <c r="E181" t="n">
-        <v>8.394</v>
+        <v>7.01</v>
+      </c>
+      <c r="F181" t="n">
+        <v>7.43</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>7.992</v>
+        <v>7.042</v>
       </c>
       <c r="B182" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="C182" t="n">
-        <v>0.156235835052645</v>
-      </c>
-      <c r="D182" t="inlineStr"/>
+        <v>0.1749531000179996</v>
+      </c>
+      <c r="D182" t="n">
+        <v>3.33</v>
+      </c>
       <c r="E182" t="n">
-        <v>7.766</v>
+        <v>6.99</v>
+      </c>
+      <c r="F182" t="n">
+        <v>7.236</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>7.786</v>
+        <v>6.85</v>
       </c>
       <c r="B183" t="n">
-        <v>39.2</v>
+        <v>41.4</v>
       </c>
       <c r="C183" t="n">
-        <v>0.1578622749124926</v>
-      </c>
-      <c r="D183" t="inlineStr"/>
+        <v>0.178425462145031</v>
+      </c>
+      <c r="D183" t="n">
+        <v>3.11</v>
+      </c>
       <c r="E183" t="n">
-        <v>7.992</v>
+        <v>7</v>
+      </c>
+      <c r="F183" t="n">
+        <v>7.042</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>7.207</v>
+        <v>6.968</v>
       </c>
       <c r="B184" t="n">
-        <v>41.2</v>
+        <v>41.9</v>
       </c>
       <c r="C184" t="n">
-        <v>0.1594568652707418</v>
-      </c>
-      <c r="D184" t="inlineStr"/>
+        <v>0.1819223219803731</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3.23</v>
+      </c>
       <c r="E184" t="n">
-        <v>7.786</v>
+        <v>7</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6.85</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>7.093</v>
+        <v>6.733</v>
       </c>
       <c r="B185" t="n">
-        <v>42.5</v>
+        <v>44.1</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1616555675577311</v>
-      </c>
-      <c r="D185" t="inlineStr"/>
+        <v>0.1856813708866568</v>
+      </c>
+      <c r="D185" t="n">
+        <v>3.35</v>
+      </c>
       <c r="E185" t="n">
-        <v>7.207</v>
+        <v>7.02</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6.968</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>7.237</v>
+        <v>6.555</v>
       </c>
       <c r="B186" t="n">
-        <v>38.9</v>
+        <v>45.9</v>
       </c>
       <c r="C186" t="n">
-        <v>0.1635212927955657</v>
-      </c>
-      <c r="D186" t="inlineStr"/>
+        <v>0.1883700831458395</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3.41</v>
+      </c>
       <c r="E186" t="n">
-        <v>7.093</v>
+        <v>7.02</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6.733</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>7.464</v>
+        <v>6.247</v>
       </c>
       <c r="B187" t="n">
-        <v>39.7</v>
+        <v>48</v>
       </c>
       <c r="C187" t="n">
-        <v>0.1661103635153007</v>
-      </c>
-      <c r="D187" t="inlineStr"/>
+        <v>0.192310483664788</v>
+      </c>
+      <c r="D187" t="n">
+        <v>3.52</v>
+      </c>
       <c r="E187" t="n">
-        <v>7.237</v>
+        <v>6.99</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6.555</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>7.493</v>
+        <v>7.231</v>
       </c>
       <c r="B188" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1673524458221449</v>
-      </c>
-      <c r="D188" t="inlineStr"/>
+        <v>0.197682699071643</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3.17</v>
+      </c>
       <c r="E188" t="n">
-        <v>7.464</v>
+        <v>6.98</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6.247</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>7.43</v>
+        <v>7.335</v>
       </c>
       <c r="B189" t="n">
-        <v>38.8</v>
+        <v>48.4</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1687400982186233</v>
-      </c>
-      <c r="D189" t="inlineStr"/>
+        <v>0.202040292138154</v>
+      </c>
+      <c r="D189" t="n">
+        <v>3.33</v>
+      </c>
       <c r="E189" t="n">
-        <v>7.493</v>
+        <v>6.92</v>
+      </c>
+      <c r="F189" t="n">
+        <v>7.231</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>7.236</v>
+        <v>6.647</v>
       </c>
       <c r="B190" t="n">
-        <v>39.4</v>
+        <v>48.6</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1715394760112175</v>
-      </c>
-      <c r="D190" t="inlineStr"/>
+        <v>0.2043449166491769</v>
+      </c>
+      <c r="D190" t="n">
+        <v>3.48</v>
+      </c>
       <c r="E190" t="n">
-        <v>7.43</v>
+        <v>6.82</v>
+      </c>
+      <c r="F190" t="n">
+        <v>7.335</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>7.042</v>
+        <v>6.369</v>
       </c>
       <c r="B191" t="n">
-        <v>40.3</v>
+        <v>53.6</v>
       </c>
       <c r="C191" t="n">
-        <v>0.1749531000179996</v>
-      </c>
-      <c r="D191" t="inlineStr"/>
+        <v>0.2053733932904878</v>
+      </c>
+      <c r="D191" t="n">
+        <v>4.37</v>
+      </c>
       <c r="E191" t="n">
-        <v>7.236</v>
+        <v>6.62</v>
+      </c>
+      <c r="F191" t="n">
+        <v>6.647</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>6.85</v>
+        <v>7.642</v>
       </c>
       <c r="B192" t="n">
-        <v>41.4</v>
+        <v>185.2</v>
       </c>
       <c r="C192" t="n">
-        <v>0.178425462145031</v>
+        <v>0.1110455795112062</v>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
-        <v>7.042</v>
+        <v>5.52</v>
+      </c>
+      <c r="F192" t="n">
+        <v>7.22</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>6.968</v>
+        <v>7.516</v>
       </c>
       <c r="B193" t="n">
-        <v>41.9</v>
+        <v>185.7</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1819223219803731</v>
+        <v>0.1096663241571843</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="n">
-        <v>6.85</v>
+        <v>5.34</v>
+      </c>
+      <c r="F193" t="n">
+        <v>7.642</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>6.733</v>
+        <v>7.808</v>
       </c>
       <c r="B194" t="n">
-        <v>44.1</v>
+        <v>181.5</v>
       </c>
       <c r="C194" t="n">
-        <v>0.1856813708866568</v>
-      </c>
-      <c r="D194" t="n">
-        <v>70.67</v>
-      </c>
+        <v>0.1080288600448191</v>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="n">
-        <v>6.968</v>
+        <v>5.17</v>
+      </c>
+      <c r="F194" t="n">
+        <v>7.516</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>6.555</v>
+        <v>9.125999999999999</v>
       </c>
       <c r="B195" t="n">
-        <v>45.9</v>
+        <v>164</v>
       </c>
       <c r="C195" t="n">
-        <v>0.1883700831458395</v>
-      </c>
-      <c r="D195" t="n">
-        <v>73.15000000000001</v>
-      </c>
+        <v>0.1077643168717956</v>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
-        <v>6.733</v>
+        <v>4.89</v>
+      </c>
+      <c r="F195" t="n">
+        <v>7.808</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>6.247</v>
+        <v>10.523</v>
       </c>
       <c r="B196" t="n">
-        <v>48</v>
+        <v>154.2</v>
       </c>
       <c r="C196" t="n">
-        <v>0.192310483664788</v>
-      </c>
-      <c r="D196" t="n">
-        <v>75.31999999999999</v>
-      </c>
+        <v>0.109439893907136</v>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="n">
-        <v>6.555</v>
+        <v>2.83</v>
+      </c>
+      <c r="F196" t="n">
+        <v>9.125999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>7.231</v>
+        <v>10.521</v>
       </c>
       <c r="B197" t="n">
-        <v>47.1</v>
+        <v>146.2</v>
       </c>
       <c r="C197" t="n">
-        <v>0.197682699071643</v>
-      </c>
-      <c r="D197" t="n">
-        <v>66.56999999999999</v>
-      </c>
+        <v>0.1121714641928612</v>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
-        <v>6.247</v>
+        <v>2.73</v>
+      </c>
+      <c r="F197" t="n">
+        <v>10.523</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>7.335</v>
+        <v>10.489</v>
       </c>
       <c r="B198" t="n">
-        <v>48.4</v>
+        <v>146.1</v>
       </c>
       <c r="C198" t="n">
-        <v>0.202040292138154</v>
+        <v>0.1152655253987142</v>
       </c>
       <c r="D198" t="n">
-        <v>67.37</v>
+        <v>2.67</v>
       </c>
       <c r="E198" t="n">
-        <v>7.231</v>
+        <v>2.63</v>
+      </c>
+      <c r="F198" t="n">
+        <v>10.521</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>6.647</v>
+        <v>10.475</v>
       </c>
       <c r="B199" t="n">
-        <v>48.6</v>
+        <v>147.9</v>
       </c>
       <c r="C199" t="n">
-        <v>0.2043449166491769</v>
+        <v>0.118867048410788</v>
       </c>
       <c r="D199" t="n">
-        <v>69.2</v>
+        <v>2.71</v>
       </c>
       <c r="E199" t="n">
-        <v>7.335</v>
+        <v>2.55</v>
+      </c>
+      <c r="F199" t="n">
+        <v>10.489</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>6.369</v>
+        <v>10.033</v>
       </c>
       <c r="B200" t="n">
-        <v>53.6</v>
+        <v>150.8</v>
       </c>
       <c r="C200" t="n">
-        <v>0.2053733932904878</v>
+        <v>0.1223646513205948</v>
       </c>
       <c r="D200" t="n">
-        <v>72.77</v>
+        <v>2.68</v>
       </c>
       <c r="E200" t="n">
-        <v>6.647</v>
+        <v>2.57</v>
+      </c>
+      <c r="F200" t="n">
+        <v>10.475</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>6.497</v>
+        <v>9.231</v>
       </c>
       <c r="B201" t="n">
-        <v>53.9</v>
+        <v>160.6</v>
       </c>
       <c r="C201" t="n">
-        <v>0.2069401344465465</v>
-      </c>
-      <c r="D201" t="inlineStr"/>
+        <v>0.1259721095024162</v>
+      </c>
+      <c r="D201" t="n">
+        <v>3.02</v>
+      </c>
       <c r="E201" t="n">
-        <v>6.369</v>
+        <v>2.59</v>
+      </c>
+      <c r="F201" t="n">
+        <v>10.033</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>7.642</v>
+        <v>7.078</v>
       </c>
       <c r="B202" t="n">
-        <v>185.2</v>
+        <v>208.6</v>
       </c>
       <c r="C202" t="n">
-        <v>0.1110455795112062</v>
+        <v>0.1293093699005927</v>
       </c>
       <c r="D202" t="n">
-        <v>245.88</v>
+        <v>3.14</v>
       </c>
       <c r="E202" t="n">
-        <v>7.22</v>
+        <v>2.94</v>
+      </c>
+      <c r="F202" t="n">
+        <v>9.231</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>7.516</v>
+        <v>7.338</v>
       </c>
       <c r="B203" t="n">
-        <v>185.7</v>
+        <v>203.8</v>
       </c>
       <c r="C203" t="n">
-        <v>0.1096663241571843</v>
+        <v>0.1321373695963384</v>
       </c>
       <c r="D203" t="n">
-        <v>257.23</v>
+        <v>3.21</v>
       </c>
       <c r="E203" t="n">
-        <v>7.642</v>
+        <v>2.98</v>
+      </c>
+      <c r="F203" t="n">
+        <v>7.078</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>7.808</v>
+        <v>6.917</v>
       </c>
       <c r="B204" t="n">
-        <v>181.5</v>
+        <v>215.7</v>
       </c>
       <c r="C204" t="n">
-        <v>0.1080288600448191</v>
+        <v>0.1349824562938866</v>
       </c>
       <c r="D204" t="n">
-        <v>277.84</v>
+        <v>3.26</v>
       </c>
       <c r="E204" t="n">
-        <v>7.516</v>
+        <v>2.98</v>
+      </c>
+      <c r="F204" t="n">
+        <v>7.338</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>9.125999999999999</v>
+        <v>6.747</v>
       </c>
       <c r="B205" t="n">
-        <v>164</v>
+        <v>223.6</v>
       </c>
       <c r="C205" t="n">
-        <v>0.1077643168717956</v>
+        <v>0.1382262986865217</v>
       </c>
       <c r="D205" t="n">
-        <v>292.41</v>
+        <v>3.29</v>
       </c>
       <c r="E205" t="n">
-        <v>7.808</v>
+        <v>2.98</v>
+      </c>
+      <c r="F205" t="n">
+        <v>6.917</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>10.523</v>
+        <v>6.619</v>
       </c>
       <c r="B206" t="n">
-        <v>154.2</v>
+        <v>231</v>
       </c>
       <c r="C206" t="n">
-        <v>0.109439893907136</v>
+        <v>0.1408263568832003</v>
       </c>
       <c r="D206" t="n">
-        <v>245.94</v>
+        <v>3.31</v>
       </c>
       <c r="E206" t="n">
-        <v>9.125999999999999</v>
+        <v>2.88</v>
+      </c>
+      <c r="F206" t="n">
+        <v>6.747</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>10.521</v>
+        <v>6.973</v>
       </c>
       <c r="B207" t="n">
-        <v>146.2</v>
+        <v>248.5</v>
       </c>
       <c r="C207" t="n">
-        <v>0.1121714641928612</v>
+        <v>0.1439165303435343</v>
       </c>
       <c r="D207" t="n">
-        <v>252.51</v>
+        <v>3.44</v>
       </c>
       <c r="E207" t="n">
-        <v>10.523</v>
+        <v>2.88</v>
+      </c>
+      <c r="F207" t="n">
+        <v>6.619</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>10.489</v>
+        <v>6.441</v>
       </c>
       <c r="B208" t="n">
-        <v>146.1</v>
+        <v>264.8</v>
       </c>
       <c r="C208" t="n">
-        <v>0.1152655253987142</v>
+        <v>0.146870478614804</v>
       </c>
       <c r="D208" t="n">
-        <v>230.07</v>
+        <v>4</v>
       </c>
       <c r="E208" t="n">
-        <v>10.521</v>
+        <v>2.87</v>
+      </c>
+      <c r="F208" t="n">
+        <v>6.973</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>10.475</v>
+        <v>6.021</v>
       </c>
       <c r="B209" t="n">
-        <v>147.9</v>
+        <v>277.1</v>
       </c>
       <c r="C209" t="n">
-        <v>0.118867048410788</v>
+        <v>0.1500167724784679</v>
       </c>
       <c r="D209" t="n">
-        <v>223.02</v>
+        <v>3.33</v>
       </c>
       <c r="E209" t="n">
-        <v>10.489</v>
+        <v>2.91</v>
+      </c>
+      <c r="F209" t="n">
+        <v>6.441</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>10.033</v>
+        <v>6.575</v>
       </c>
       <c r="B210" t="n">
-        <v>150.8</v>
+        <v>258.2</v>
       </c>
       <c r="C210" t="n">
-        <v>0.1223646513205948</v>
+        <v>0.1518601812233764</v>
       </c>
       <c r="D210" t="n">
-        <v>218.23</v>
+        <v>3.82</v>
       </c>
       <c r="E210" t="n">
-        <v>10.475</v>
+        <v>2.92</v>
+      </c>
+      <c r="F210" t="n">
+        <v>6.021</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>9.231</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="B211" t="n">
-        <v>160.6</v>
+        <v>116.6</v>
       </c>
       <c r="C211" t="n">
-        <v>0.1259721095024162</v>
+        <v>0.1949990048991489</v>
       </c>
       <c r="D211" t="n">
-        <v>166.26</v>
+        <v>3.71</v>
       </c>
       <c r="E211" t="n">
-        <v>10.033</v>
+        <v>4.03</v>
+      </c>
+      <c r="F211" t="n">
+        <v>8.137</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>7.078</v>
+        <v>8.398</v>
       </c>
       <c r="B212" t="n">
-        <v>208.6</v>
+        <v>114.5</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1293093699005927</v>
+        <v>0.1982629963295302</v>
       </c>
       <c r="D212" t="n">
-        <v>174.28</v>
+        <v>3.71</v>
       </c>
       <c r="E212" t="n">
-        <v>9.231</v>
+        <v>3.98</v>
+      </c>
+      <c r="F212" t="n">
+        <v>8.308999999999999</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>7.338</v>
+        <v>8.102</v>
       </c>
       <c r="B213" t="n">
-        <v>203.8</v>
+        <v>111.8</v>
       </c>
       <c r="C213" t="n">
-        <v>0.1321373695963384</v>
+        <v>0.2005708867904132</v>
       </c>
       <c r="D213" t="n">
-        <v>172.34</v>
+        <v>3.77</v>
       </c>
       <c r="E213" t="n">
-        <v>7.078</v>
+        <v>3.89</v>
+      </c>
+      <c r="F213" t="n">
+        <v>8.398</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>6.917</v>
+        <v>8.502000000000001</v>
       </c>
       <c r="B214" t="n">
-        <v>215.7</v>
+        <v>109.3</v>
       </c>
       <c r="C214" t="n">
-        <v>0.1349824562938866</v>
+        <v>0.2015298727738146</v>
       </c>
       <c r="D214" t="n">
-        <v>177.38</v>
+        <v>3.76</v>
       </c>
       <c r="E214" t="n">
-        <v>7.338</v>
+        <v>3.77</v>
+      </c>
+      <c r="F214" t="n">
+        <v>8.102</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>6.747</v>
+        <v>8.913</v>
       </c>
       <c r="B215" t="n">
-        <v>223.6</v>
+        <v>109.8</v>
       </c>
       <c r="C215" t="n">
-        <v>0.1382262986865217</v>
+        <v>0.2024932198588664</v>
       </c>
       <c r="D215" t="n">
-        <v>181.47</v>
+        <v>3.76</v>
       </c>
       <c r="E215" t="n">
-        <v>6.917</v>
+        <v>3.66</v>
+      </c>
+      <c r="F215" t="n">
+        <v>8.502000000000001</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>6.619</v>
+        <v>8.879</v>
       </c>
       <c r="B216" t="n">
-        <v>231</v>
+        <v>107.8</v>
       </c>
       <c r="C216" t="n">
-        <v>0.1408263568832003</v>
+        <v>0.2036140669786369</v>
       </c>
       <c r="D216" t="n">
-        <v>181.64</v>
+        <v>3.78</v>
       </c>
       <c r="E216" t="n">
-        <v>6.747</v>
+        <v>3.61</v>
+      </c>
+      <c r="F216" t="n">
+        <v>8.913</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>6.973</v>
+        <v>8.728999999999999</v>
       </c>
       <c r="B217" t="n">
-        <v>248.5</v>
+        <v>106.7</v>
       </c>
       <c r="C217" t="n">
-        <v>0.1439165303435343</v>
+        <v>0.2044174018241025</v>
       </c>
       <c r="D217" t="n">
-        <v>185.72</v>
+        <v>3.86</v>
       </c>
       <c r="E217" t="n">
-        <v>6.619</v>
+        <v>3.48</v>
+      </c>
+      <c r="F217" t="n">
+        <v>8.879</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>6.441</v>
+        <v>8.798</v>
       </c>
       <c r="B218" t="n">
-        <v>264.8</v>
+        <v>104.4</v>
       </c>
       <c r="C218" t="n">
-        <v>0.146870478614804</v>
+        <v>0.2082882699720498</v>
       </c>
       <c r="D218" t="n">
-        <v>229.78</v>
+        <v>3.83</v>
       </c>
       <c r="E218" t="n">
-        <v>6.973</v>
+        <v>3.38</v>
+      </c>
+      <c r="F218" t="n">
+        <v>8.728999999999999</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>6.021</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="B219" t="n">
-        <v>277.1</v>
+        <v>102.4</v>
       </c>
       <c r="C219" t="n">
-        <v>0.1500167724784679</v>
+        <v>0.2113806208568468</v>
       </c>
       <c r="D219" t="n">
-        <v>172.5</v>
+        <v>3.9</v>
       </c>
       <c r="E219" t="n">
-        <v>6.441</v>
+        <v>3.31</v>
+      </c>
+      <c r="F219" t="n">
+        <v>8.798</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>6.575</v>
+        <v>8.859</v>
       </c>
       <c r="B220" t="n">
-        <v>258.2</v>
+        <v>101</v>
       </c>
       <c r="C220" t="n">
-        <v>0.1518601812233764</v>
+        <v>0.2150777823129277</v>
       </c>
       <c r="D220" t="n">
-        <v>205.63</v>
+        <v>3.91</v>
       </c>
       <c r="E220" t="n">
-        <v>6.021</v>
+        <v>3.24</v>
+      </c>
+      <c r="F220" t="n">
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>6.854</v>
+        <v>8.846</v>
       </c>
       <c r="B221" t="n">
-        <v>261.6</v>
+        <v>99.3</v>
       </c>
       <c r="C221" t="n">
-        <v>0.1545886236492796</v>
+        <v>0.2186193274101381</v>
       </c>
       <c r="D221" t="n">
-        <v>203.39</v>
+        <v>3.87</v>
       </c>
       <c r="E221" t="n">
-        <v>6.575</v>
+        <v>3.22</v>
+      </c>
+      <c r="F221" t="n">
+        <v>8.859</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>8.308999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="B222" t="n">
-        <v>116.6</v>
+        <v>99.5</v>
       </c>
       <c r="C222" t="n">
-        <v>0.1949990048991489</v>
+        <v>0.2214155602633029</v>
       </c>
       <c r="D222" t="n">
-        <v>86.53</v>
+        <v>3.99</v>
       </c>
       <c r="E222" t="n">
-        <v>8.137</v>
+        <v>3.2</v>
+      </c>
+      <c r="F222" t="n">
+        <v>8.846</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>8.398</v>
+        <v>8.691000000000001</v>
       </c>
       <c r="B223" t="n">
-        <v>114.5</v>
+        <v>98</v>
       </c>
       <c r="C223" t="n">
-        <v>0.1982629963295302</v>
+        <v>0.2241164801801943</v>
       </c>
       <c r="D223" t="n">
-        <v>86.41</v>
+        <v>4.03</v>
       </c>
       <c r="E223" t="n">
-        <v>8.308999999999999</v>
+        <v>3.21</v>
+      </c>
+      <c r="F223" t="n">
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>8.102</v>
+        <v>8.654999999999999</v>
       </c>
       <c r="B224" t="n">
-        <v>111.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C224" t="n">
-        <v>0.2005708867904132</v>
+        <v>0.2263205358878139</v>
       </c>
       <c r="D224" t="n">
-        <v>88.06</v>
+        <v>4.01</v>
       </c>
       <c r="E224" t="n">
-        <v>8.398</v>
+        <v>3.17</v>
+      </c>
+      <c r="F224" t="n">
+        <v>8.691000000000001</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>8.502000000000001</v>
+        <v>8.615</v>
       </c>
       <c r="B225" t="n">
-        <v>109.3</v>
+        <v>95.3</v>
       </c>
       <c r="C225" t="n">
-        <v>0.2015298727738146</v>
+        <v>0.2289197027056319</v>
       </c>
       <c r="D225" t="n">
-        <v>88</v>
+        <v>4.05</v>
       </c>
       <c r="E225" t="n">
-        <v>8.102</v>
+        <v>3.16</v>
+      </c>
+      <c r="F225" t="n">
+        <v>8.654999999999999</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>8.913</v>
+        <v>9.564</v>
       </c>
       <c r="B226" t="n">
-        <v>109.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C226" t="n">
-        <v>0.2024932198588664</v>
+        <v>0.2323733103372605</v>
       </c>
       <c r="D226" t="n">
-        <v>88.03</v>
+        <v>4</v>
       </c>
       <c r="E226" t="n">
-        <v>8.502000000000001</v>
+        <v>3.18</v>
+      </c>
+      <c r="F226" t="n">
+        <v>8.615</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>8.879</v>
+        <v>9.282</v>
       </c>
       <c r="B227" t="n">
-        <v>107.8</v>
+        <v>93.7</v>
       </c>
       <c r="C227" t="n">
-        <v>0.2036140669786369</v>
+        <v>0.235354866456436</v>
       </c>
       <c r="D227" t="n">
-        <v>88.51000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="E227" t="n">
-        <v>8.913</v>
+        <v>3.12</v>
+      </c>
+      <c r="F227" t="n">
+        <v>9.564</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>8.728999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="B228" t="n">
-        <v>106.7</v>
+        <v>93.7</v>
       </c>
       <c r="C228" t="n">
-        <v>0.2044174018241025</v>
+        <v>0.2380378170586199</v>
       </c>
       <c r="D228" t="n">
-        <v>90.04000000000001</v>
+        <v>4.23</v>
       </c>
       <c r="E228" t="n">
-        <v>8.879</v>
+        <v>3.09</v>
+      </c>
+      <c r="F228" t="n">
+        <v>9.282</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>8.798</v>
+        <v>8.406000000000001</v>
       </c>
       <c r="B229" t="n">
-        <v>104.4</v>
+        <v>94.7</v>
       </c>
       <c r="C229" t="n">
-        <v>0.2082882699720498</v>
-      </c>
-      <c r="D229" t="n">
-        <v>90.27</v>
-      </c>
+        <v>0.2403723695298697</v>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="n">
-        <v>8.728999999999999</v>
+        <v>3.04</v>
+      </c>
+      <c r="F229" t="n">
+        <v>8.85</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>8.789999999999999</v>
+        <v>6.082</v>
       </c>
       <c r="B230" t="n">
-        <v>102.4</v>
+        <v>26.7</v>
       </c>
       <c r="C230" t="n">
-        <v>0.2113806208568468</v>
+        <v>0.1663932998003311</v>
       </c>
       <c r="D230" t="n">
-        <v>89.48</v>
+        <v>2.96</v>
       </c>
       <c r="E230" t="n">
-        <v>8.798</v>
+        <v>7.9</v>
+      </c>
+      <c r="F230" t="n">
+        <v>6.475</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>8.859</v>
+        <v>6.021</v>
       </c>
       <c r="B231" t="n">
-        <v>101</v>
+        <v>31.8</v>
       </c>
       <c r="C231" t="n">
-        <v>0.2150777823129277</v>
+        <v>0.1700006373789541</v>
       </c>
       <c r="D231" t="n">
-        <v>89.38</v>
+        <v>3.03</v>
       </c>
       <c r="E231" t="n">
-        <v>8.789999999999999</v>
+        <v>7.85</v>
+      </c>
+      <c r="F231" t="n">
+        <v>6.082</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>8.846</v>
+        <v>5.818</v>
       </c>
       <c r="B232" t="n">
-        <v>99.3</v>
+        <v>39.8</v>
       </c>
       <c r="C232" t="n">
-        <v>0.2186193274101381</v>
+        <v>0.1739456004056428</v>
       </c>
       <c r="D232" t="n">
-        <v>89.62</v>
+        <v>3.14</v>
       </c>
       <c r="E232" t="n">
-        <v>8.859</v>
+        <v>7.83</v>
+      </c>
+      <c r="F232" t="n">
+        <v>6.021</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>8.720000000000001</v>
+        <v>5.866</v>
       </c>
       <c r="B233" t="n">
-        <v>99.5</v>
+        <v>42.2</v>
       </c>
       <c r="C233" t="n">
-        <v>0.2214155602633029</v>
+        <v>0.1759618762575223</v>
       </c>
       <c r="D233" t="n">
-        <v>90.38</v>
+        <v>3.23</v>
       </c>
       <c r="E233" t="n">
-        <v>8.846</v>
+        <v>7.77</v>
+      </c>
+      <c r="F233" t="n">
+        <v>5.818</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>8.691000000000001</v>
+        <v>6.268</v>
       </c>
       <c r="B234" t="n">
-        <v>98</v>
+        <v>35.5</v>
       </c>
       <c r="C234" t="n">
-        <v>0.2241164801801943</v>
+        <v>0.1782249585497546</v>
       </c>
       <c r="D234" t="n">
-        <v>89.76000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="E234" t="n">
-        <v>8.720000000000001</v>
+        <v>6.74</v>
+      </c>
+      <c r="F234" t="n">
+        <v>5.866</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>8.654999999999999</v>
+        <v>6.224</v>
       </c>
       <c r="B235" t="n">
-        <v>96.90000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="C235" t="n">
-        <v>0.2263205358878139</v>
+        <v>0.1811724948408492</v>
       </c>
       <c r="D235" t="n">
-        <v>88.59999999999999</v>
+        <v>3.11</v>
       </c>
       <c r="E235" t="n">
-        <v>8.691000000000001</v>
+        <v>5.68</v>
+      </c>
+      <c r="F235" t="n">
+        <v>6.268</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>8.615</v>
+        <v>5.918</v>
       </c>
       <c r="B236" t="n">
-        <v>95.3</v>
+        <v>35.7</v>
       </c>
       <c r="C236" t="n">
-        <v>0.2289197027056319</v>
+        <v>0.1837169003256041</v>
       </c>
       <c r="D236" t="n">
-        <v>87.98999999999999</v>
+        <v>3.13</v>
       </c>
       <c r="E236" t="n">
-        <v>8.654999999999999</v>
+        <v>5.88</v>
+      </c>
+      <c r="F236" t="n">
+        <v>6.224</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>9.564</v>
+        <v>5.621</v>
       </c>
       <c r="B237" t="n">
-        <v>92.09999999999999</v>
+        <v>40.3</v>
       </c>
       <c r="C237" t="n">
-        <v>0.2323733103372605</v>
+        <v>0.1856140390343763</v>
       </c>
       <c r="D237" t="n">
-        <v>84.72</v>
+        <v>3.14</v>
       </c>
       <c r="E237" t="n">
-        <v>8.615</v>
+        <v>5.89</v>
+      </c>
+      <c r="F237" t="n">
+        <v>5.918</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>9.282</v>
+        <v>5.604</v>
       </c>
       <c r="B238" t="n">
-        <v>93.7</v>
+        <v>41.6</v>
       </c>
       <c r="C238" t="n">
-        <v>0.235354866456436</v>
+        <v>0.1876565414499771</v>
       </c>
       <c r="D238" t="n">
-        <v>109.39</v>
+        <v>3.19</v>
       </c>
       <c r="E238" t="n">
-        <v>9.564</v>
+        <v>5.8</v>
+      </c>
+      <c r="F238" t="n">
+        <v>5.621</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>8.85</v>
+        <v>5.664</v>
       </c>
       <c r="B239" t="n">
-        <v>93.7</v>
+        <v>42.6</v>
       </c>
       <c r="C239" t="n">
-        <v>0.2380378170586199</v>
+        <v>0.1906675500182866</v>
       </c>
       <c r="D239" t="n">
-        <v>104.89</v>
+        <v>3.22</v>
       </c>
       <c r="E239" t="n">
-        <v>9.282</v>
+        <v>5.66</v>
+      </c>
+      <c r="F239" t="n">
+        <v>5.604</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>8.406000000000001</v>
+        <v>5.849</v>
       </c>
       <c r="B240" t="n">
-        <v>94.7</v>
+        <v>43.2</v>
       </c>
       <c r="C240" t="n">
-        <v>0.2403723695298697</v>
+        <v>0.1938858947402341</v>
       </c>
       <c r="D240" t="n">
-        <v>100.42</v>
+        <v>3.2</v>
       </c>
       <c r="E240" t="n">
-        <v>8.85</v>
+        <v>5.69</v>
+      </c>
+      <c r="F240" t="n">
+        <v>5.664</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>8.444000000000001</v>
+        <v>6.352</v>
       </c>
       <c r="B241" t="n">
-        <v>93.40000000000001</v>
+        <v>43.9</v>
       </c>
       <c r="C241" t="n">
-        <v>0.2434532228681681</v>
-      </c>
-      <c r="D241" t="inlineStr"/>
+        <v>0.1963399911729916</v>
+      </c>
+      <c r="D241" t="n">
+        <v>3.21</v>
+      </c>
       <c r="E241" t="n">
-        <v>8.406000000000001</v>
+        <v>5.72</v>
+      </c>
+      <c r="F241" t="n">
+        <v>5.849</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>6.082</v>
+        <v>6.187</v>
       </c>
       <c r="B242" t="n">
-        <v>26.7</v>
+        <v>45.2</v>
       </c>
       <c r="C242" t="n">
-        <v>0.1663932998003311</v>
+        <v>0.1989158593642635</v>
       </c>
       <c r="D242" t="n">
-        <v>67.81</v>
+        <v>3.21</v>
       </c>
       <c r="E242" t="n">
-        <v>6.475</v>
+        <v>5.57</v>
+      </c>
+      <c r="F242" t="n">
+        <v>6.352</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>6.021</v>
+        <v>6.409</v>
       </c>
       <c r="B243" t="n">
-        <v>31.8</v>
+        <v>47.7</v>
       </c>
       <c r="C243" t="n">
-        <v>0.1700006373789541</v>
+        <v>0.20102368770546</v>
       </c>
       <c r="D243" t="n">
-        <v>67.92</v>
+        <v>3.3</v>
       </c>
       <c r="E243" t="n">
-        <v>6.082</v>
+        <v>5.49</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6.187</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>5.818</v>
+        <v>6.863</v>
       </c>
       <c r="B244" t="n">
-        <v>39.8</v>
+        <v>48.8</v>
       </c>
       <c r="C244" t="n">
-        <v>0.1739456004056428</v>
+        <v>0.2025966057767629</v>
       </c>
       <c r="D244" t="n">
-        <v>68.28</v>
+        <v>3.27</v>
       </c>
       <c r="E244" t="n">
-        <v>6.021</v>
+        <v>5.42</v>
+      </c>
+      <c r="F244" t="n">
+        <v>6.409</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>5.866</v>
+        <v>7.506</v>
       </c>
       <c r="B245" t="n">
-        <v>42.2</v>
+        <v>50.4</v>
       </c>
       <c r="C245" t="n">
-        <v>0.1759618762575223</v>
+        <v>0.2051780308490702</v>
       </c>
       <c r="D245" t="n">
-        <v>68.91</v>
+        <v>3.34</v>
       </c>
       <c r="E245" t="n">
-        <v>5.818</v>
+        <v>5.29</v>
+      </c>
+      <c r="F245" t="n">
+        <v>6.863</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>6.268</v>
+        <v>9.411</v>
       </c>
       <c r="B246" t="n">
-        <v>35.5</v>
+        <v>51.5</v>
       </c>
       <c r="C246" t="n">
-        <v>0.1782249585497546</v>
+        <v>0.2079512027901626</v>
       </c>
       <c r="D246" t="n">
-        <v>68.48999999999999</v>
+        <v>3.36</v>
       </c>
       <c r="E246" t="n">
-        <v>5.866</v>
+        <v>5.16</v>
+      </c>
+      <c r="F246" t="n">
+        <v>7.506</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>6.224</v>
+        <v>8.103999999999999</v>
       </c>
       <c r="B247" t="n">
-        <v>33.4</v>
+        <v>52.9</v>
       </c>
       <c r="C247" t="n">
-        <v>0.1811724948408492</v>
+        <v>0.2087813080265727</v>
       </c>
       <c r="D247" t="n">
-        <v>68.28</v>
+        <v>3.4</v>
       </c>
       <c r="E247" t="n">
-        <v>6.268</v>
+        <v>5.03</v>
+      </c>
+      <c r="F247" t="n">
+        <v>9.411</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>5.918</v>
+        <v>7.278</v>
       </c>
       <c r="B248" t="n">
-        <v>35.7</v>
+        <v>54.8</v>
       </c>
       <c r="C248" t="n">
-        <v>0.1837169003256041</v>
+        <v>0.2097272024335531</v>
       </c>
       <c r="D248" t="n">
-        <v>69.17</v>
-      </c>
-      <c r="E248" t="n">
-        <v>6.224</v>
+        <v>3.36</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="n">
+        <v>8.103999999999999</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>5.621</v>
+        <v>5.646</v>
       </c>
       <c r="B249" t="n">
-        <v>40.3</v>
+        <v>28.6</v>
       </c>
       <c r="C249" t="n">
-        <v>0.1856140390343763</v>
+        <v>0.1582972204505219</v>
       </c>
       <c r="D249" t="n">
-        <v>69.69</v>
+        <v>3.72</v>
       </c>
       <c r="E249" t="n">
-        <v>5.918</v>
+        <v>7.28</v>
+      </c>
+      <c r="F249" t="n">
+        <v>5.483</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>5.604</v>
+        <v>5.857</v>
       </c>
       <c r="B250" t="n">
-        <v>41.6</v>
+        <v>31.5</v>
       </c>
       <c r="C250" t="n">
-        <v>0.1876565414499771</v>
+        <v>0.1629075622333643</v>
       </c>
       <c r="D250" t="n">
-        <v>70.68000000000001</v>
+        <v>3.79</v>
       </c>
       <c r="E250" t="n">
-        <v>5.621</v>
+        <v>7.16</v>
+      </c>
+      <c r="F250" t="n">
+        <v>5.646</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>5.664</v>
+        <v>5.76</v>
       </c>
       <c r="B251" t="n">
-        <v>42.6</v>
+        <v>36.4</v>
       </c>
       <c r="C251" t="n">
-        <v>0.1906675500182866</v>
+        <v>0.1664854862317741</v>
       </c>
       <c r="D251" t="n">
-        <v>72.61</v>
+        <v>3.88</v>
       </c>
       <c r="E251" t="n">
-        <v>5.604</v>
+        <v>7.19</v>
+      </c>
+      <c r="F251" t="n">
+        <v>5.857</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>5.849</v>
+        <v>6.29</v>
       </c>
       <c r="B252" t="n">
-        <v>43.2</v>
+        <v>40.2</v>
       </c>
       <c r="C252" t="n">
-        <v>0.1938858947402341</v>
+        <v>0.1699359242732922</v>
       </c>
       <c r="D252" t="n">
-        <v>71.81999999999999</v>
+        <v>3.88</v>
       </c>
       <c r="E252" t="n">
-        <v>5.664</v>
+        <v>7.18</v>
+      </c>
+      <c r="F252" t="n">
+        <v>5.76</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>6.352</v>
+        <v>7.345</v>
       </c>
       <c r="B253" t="n">
-        <v>43.9</v>
+        <v>35.2</v>
       </c>
       <c r="C253" t="n">
-        <v>0.1963399911729916</v>
+        <v>0.1720395017865129</v>
       </c>
       <c r="D253" t="n">
-        <v>73.54000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="E253" t="n">
-        <v>5.849</v>
+        <v>7.18</v>
+      </c>
+      <c r="F253" t="n">
+        <v>6.29</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>6.187</v>
+        <v>6.906</v>
       </c>
       <c r="B254" t="n">
-        <v>45.2</v>
+        <v>35.6</v>
       </c>
       <c r="C254" t="n">
-        <v>0.1989158593642635</v>
+        <v>0.173424621957647</v>
       </c>
       <c r="D254" t="n">
-        <v>73.65000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="E254" t="n">
-        <v>6.352</v>
+        <v>7.16</v>
+      </c>
+      <c r="F254" t="n">
+        <v>7.345</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>6.409</v>
+        <v>6.54</v>
       </c>
       <c r="B255" t="n">
-        <v>47.7</v>
+        <v>39.6</v>
       </c>
       <c r="C255" t="n">
-        <v>0.20102368770546</v>
+        <v>0.1786376019299034</v>
       </c>
       <c r="D255" t="n">
-        <v>73.48999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="E255" t="n">
-        <v>6.187</v>
+        <v>7.43</v>
+      </c>
+      <c r="F255" t="n">
+        <v>6.906</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>6.863</v>
+        <v>6.308</v>
       </c>
       <c r="B256" t="n">
-        <v>48.8</v>
+        <v>42.8</v>
       </c>
       <c r="C256" t="n">
-        <v>0.2025966057767629</v>
+        <v>0.1808914580670593</v>
       </c>
       <c r="D256" t="n">
-        <v>71.53</v>
+        <v>4.22</v>
       </c>
       <c r="E256" t="n">
-        <v>6.409</v>
+        <v>7.44</v>
+      </c>
+      <c r="F256" t="n">
+        <v>6.54</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>7.506</v>
+        <v>6.155</v>
       </c>
       <c r="B257" t="n">
-        <v>50.4</v>
+        <v>44.9</v>
       </c>
       <c r="C257" t="n">
-        <v>0.2051780308490702</v>
+        <v>0.1821936592599366</v>
       </c>
       <c r="D257" t="n">
-        <v>74.51000000000001</v>
+        <v>4.27</v>
       </c>
       <c r="E257" t="n">
-        <v>6.863</v>
+        <v>7.3</v>
+      </c>
+      <c r="F257" t="n">
+        <v>6.308</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>9.411</v>
+        <v>6.222</v>
       </c>
       <c r="B258" t="n">
-        <v>51.5</v>
+        <v>46.2</v>
       </c>
       <c r="C258" t="n">
-        <v>0.2079512027901626</v>
+        <v>0.1838905620412353</v>
       </c>
       <c r="D258" t="n">
-        <v>76.84</v>
+        <v>4.3</v>
       </c>
       <c r="E258" t="n">
-        <v>7.506</v>
+        <v>7.25</v>
+      </c>
+      <c r="F258" t="n">
+        <v>6.155</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>8.103999999999999</v>
+        <v>6.474</v>
       </c>
       <c r="B259" t="n">
-        <v>52.9</v>
+        <v>46.3</v>
       </c>
       <c r="C259" t="n">
-        <v>0.2087813080265727</v>
+        <v>0.18664620637153</v>
       </c>
       <c r="D259" t="n">
-        <v>76.34999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="E259" t="n">
-        <v>9.411</v>
+        <v>6.95</v>
+      </c>
+      <c r="F259" t="n">
+        <v>6.222</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>7.278</v>
+        <v>6.649</v>
       </c>
       <c r="B260" t="n">
-        <v>54.8</v>
+        <v>47.4</v>
       </c>
       <c r="C260" t="n">
-        <v>0.2097272024335531</v>
+        <v>0.1891787912098918</v>
       </c>
       <c r="D260" t="n">
-        <v>75.79000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="E260" t="n">
-        <v>8.103999999999999</v>
+        <v>6.67</v>
+      </c>
+      <c r="F260" t="n">
+        <v>6.474</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>7.589</v>
+        <v>6.464</v>
       </c>
       <c r="B261" t="n">
-        <v>54.2</v>
+        <v>50.2</v>
       </c>
       <c r="C261" t="n">
-        <v>0.2133953956499395</v>
-      </c>
-      <c r="D261" t="inlineStr"/>
+        <v>0.1921571192381318</v>
+      </c>
+      <c r="D261" t="n">
+        <v>4.53</v>
+      </c>
       <c r="E261" t="n">
-        <v>7.278</v>
+        <v>6.52</v>
+      </c>
+      <c r="F261" t="n">
+        <v>6.649</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>5.646</v>
+        <v>6.469</v>
       </c>
       <c r="B262" t="n">
-        <v>28.6</v>
+        <v>53.2</v>
       </c>
       <c r="C262" t="n">
-        <v>0.1582972204505219</v>
+        <v>0.1950753662161206</v>
       </c>
       <c r="D262" t="n">
-        <v>83.03</v>
+        <v>4.57</v>
       </c>
       <c r="E262" t="n">
-        <v>5.483</v>
+        <v>6.39</v>
+      </c>
+      <c r="F262" t="n">
+        <v>6.464</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>5.857</v>
+        <v>6.945</v>
       </c>
       <c r="B263" t="n">
-        <v>31.5</v>
+        <v>55.3</v>
       </c>
       <c r="C263" t="n">
-        <v>0.1629075622333643</v>
+        <v>0.196378280349904</v>
       </c>
       <c r="D263" t="n">
-        <v>85.8</v>
+        <v>4.54</v>
       </c>
       <c r="E263" t="n">
-        <v>5.646</v>
+        <v>6.31</v>
+      </c>
+      <c r="F263" t="n">
+        <v>6.469</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>5.76</v>
+        <v>7.416</v>
       </c>
       <c r="B264" t="n">
-        <v>36.4</v>
+        <v>58.6</v>
       </c>
       <c r="C264" t="n">
-        <v>0.1664854862317741</v>
+        <v>0.1980471726281034</v>
       </c>
       <c r="D264" t="n">
-        <v>89.04000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="E264" t="n">
-        <v>5.857</v>
+        <v>5.98</v>
+      </c>
+      <c r="F264" t="n">
+        <v>6.945</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>6.29</v>
+        <v>7.732</v>
       </c>
       <c r="B265" t="n">
-        <v>40.2</v>
+        <v>60.7</v>
       </c>
       <c r="C265" t="n">
-        <v>0.1699359242732922</v>
+        <v>0.1992129533603177</v>
       </c>
       <c r="D265" t="n">
-        <v>83.59999999999999</v>
+        <v>4.46</v>
       </c>
       <c r="E265" t="n">
-        <v>5.76</v>
+        <v>6.04</v>
+      </c>
+      <c r="F265" t="n">
+        <v>7.416</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>7.345</v>
+        <v>7.244</v>
       </c>
       <c r="B266" t="n">
-        <v>35.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="C266" t="n">
-        <v>0.1720395017865129</v>
+        <v>0.199796293511257</v>
       </c>
       <c r="D266" t="n">
-        <v>84.73999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="E266" t="n">
-        <v>6.29</v>
+        <v>5.68</v>
+      </c>
+      <c r="F266" t="n">
+        <v>7.732</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>6.906</v>
+        <v>7.319</v>
       </c>
       <c r="B267" t="n">
-        <v>35.6</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C267" t="n">
-        <v>0.173424621957647</v>
+        <v>0.2000735664945565</v>
       </c>
       <c r="D267" t="n">
-        <v>84.67</v>
+        <v>4.62</v>
       </c>
       <c r="E267" t="n">
-        <v>7.345</v>
+        <v>5.48</v>
+      </c>
+      <c r="F267" t="n">
+        <v>7.244</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>6.54</v>
+        <v>7.125</v>
       </c>
       <c r="B268" t="n">
-        <v>39.6</v>
+        <v>294.1</v>
       </c>
       <c r="C268" t="n">
-        <v>0.1786376019299034</v>
+        <v>0.1408299546863821</v>
       </c>
       <c r="D268" t="n">
-        <v>95.26000000000001</v>
+        <v>2.55</v>
       </c>
       <c r="E268" t="n">
-        <v>6.906</v>
+        <v>5.79</v>
+      </c>
+      <c r="F268" t="n">
+        <v>7.28</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>6.308</v>
+        <v>6.638</v>
       </c>
       <c r="B269" t="n">
-        <v>42.8</v>
+        <v>309.8</v>
       </c>
       <c r="C269" t="n">
-        <v>0.1808914580670593</v>
+        <v>0.1406991468515368</v>
       </c>
       <c r="D269" t="n">
-        <v>95.90000000000001</v>
+        <v>2.61</v>
       </c>
       <c r="E269" t="n">
-        <v>6.54</v>
+        <v>5.65</v>
+      </c>
+      <c r="F269" t="n">
+        <v>7.125</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>6.155</v>
+        <v>6.158</v>
       </c>
       <c r="B270" t="n">
-        <v>44.9</v>
+        <v>317.3</v>
       </c>
       <c r="C270" t="n">
-        <v>0.1821936592599366</v>
+        <v>0.1403419244960488</v>
       </c>
       <c r="D270" t="n">
-        <v>96.33</v>
+        <v>2.68</v>
       </c>
       <c r="E270" t="n">
-        <v>6.308</v>
+        <v>5.67</v>
+      </c>
+      <c r="F270" t="n">
+        <v>6.638</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>6.222</v>
+        <v>6.231</v>
       </c>
       <c r="B271" t="n">
-        <v>46.2</v>
+        <v>322.1</v>
       </c>
       <c r="C271" t="n">
-        <v>0.1838905620412353</v>
+        <v>0.1399196773866833</v>
       </c>
       <c r="D271" t="n">
-        <v>98.45999999999999</v>
+        <v>2.72</v>
       </c>
       <c r="E271" t="n">
-        <v>6.155</v>
+        <v>5.57</v>
+      </c>
+      <c r="F271" t="n">
+        <v>6.158</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>6.474</v>
+        <v>6.95</v>
       </c>
       <c r="B272" t="n">
-        <v>46.3</v>
+        <v>323.5</v>
       </c>
       <c r="C272" t="n">
-        <v>0.18664620637153</v>
+        <v>0.1395987841945289</v>
       </c>
       <c r="D272" t="n">
-        <v>100.24</v>
+        <v>2.7</v>
       </c>
       <c r="E272" t="n">
-        <v>6.222</v>
+        <v>5.47</v>
+      </c>
+      <c r="F272" t="n">
+        <v>6.231</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>6.649</v>
+        <v>6.662</v>
       </c>
       <c r="B273" t="n">
-        <v>47.4</v>
+        <v>332.9</v>
       </c>
       <c r="C273" t="n">
-        <v>0.1891787912098918</v>
+        <v>0.1395155218636594</v>
       </c>
       <c r="D273" t="n">
-        <v>102.16</v>
+        <v>2.77</v>
       </c>
       <c r="E273" t="n">
-        <v>6.474</v>
+        <v>5.37</v>
+      </c>
+      <c r="F273" t="n">
+        <v>6.95</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>6.464</v>
+        <v>5.952</v>
       </c>
       <c r="B274" t="n">
-        <v>50.2</v>
+        <v>329.8</v>
       </c>
       <c r="C274" t="n">
-        <v>0.1921571192381318</v>
+        <v>0.138879337292904</v>
       </c>
       <c r="D274" t="n">
-        <v>105.65</v>
+        <v>2.78</v>
       </c>
       <c r="E274" t="n">
-        <v>6.649</v>
+        <v>5.28</v>
+      </c>
+      <c r="F274" t="n">
+        <v>6.662</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>6.469</v>
+        <v>5.294</v>
       </c>
       <c r="B275" t="n">
-        <v>53.2</v>
+        <v>336.9</v>
       </c>
       <c r="C275" t="n">
-        <v>0.1950753662161206</v>
+        <v>0.1395838453814687</v>
       </c>
       <c r="D275" t="n">
-        <v>102.55</v>
+        <v>2.81</v>
       </c>
       <c r="E275" t="n">
-        <v>6.464</v>
+        <v>5.15</v>
+      </c>
+      <c r="F275" t="n">
+        <v>5.952</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>6.945</v>
+        <v>5.236</v>
       </c>
       <c r="B276" t="n">
-        <v>55.3</v>
+        <v>342.9</v>
       </c>
       <c r="C276" t="n">
-        <v>0.196378280349904</v>
+        <v>0.1397607994950087</v>
       </c>
       <c r="D276" t="n">
-        <v>102.56</v>
+        <v>2.83</v>
       </c>
       <c r="E276" t="n">
-        <v>6.469</v>
+        <v>5.17</v>
+      </c>
+      <c r="F276" t="n">
+        <v>5.294</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>7.416</v>
+        <v>5.23</v>
       </c>
       <c r="B277" t="n">
-        <v>58.6</v>
+        <v>345.5</v>
       </c>
       <c r="C277" t="n">
-        <v>0.1980471726281034</v>
+        <v>0.1407618978314656</v>
       </c>
       <c r="D277" t="n">
-        <v>97.06999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="E277" t="n">
-        <v>6.945</v>
+        <v>5.05</v>
+      </c>
+      <c r="F277" t="n">
+        <v>5.236</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>7.732</v>
+        <v>5.081</v>
       </c>
       <c r="B278" t="n">
-        <v>60.7</v>
+        <v>342.1</v>
       </c>
       <c r="C278" t="n">
-        <v>0.1992129533603177</v>
+        <v>0.141822302907144</v>
       </c>
       <c r="D278" t="n">
-        <v>102.23</v>
+        <v>2.91</v>
       </c>
       <c r="E278" t="n">
-        <v>7.416</v>
+        <v>4.93</v>
+      </c>
+      <c r="F278" t="n">
+        <v>5.23</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>7.244</v>
+        <v>5.071</v>
       </c>
       <c r="B279" t="n">
-        <v>65.59999999999999</v>
+        <v>337.7</v>
       </c>
       <c r="C279" t="n">
-        <v>0.199796293511257</v>
+        <v>0.142224975661563</v>
       </c>
       <c r="D279" t="n">
-        <v>104.22</v>
+        <v>2.88</v>
       </c>
       <c r="E279" t="n">
-        <v>7.732</v>
+        <v>4.81</v>
+      </c>
+      <c r="F279" t="n">
+        <v>5.081</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>7.319</v>
+        <v>5.135</v>
       </c>
       <c r="B280" t="n">
-        <v>67.40000000000001</v>
+        <v>328.6</v>
       </c>
       <c r="C280" t="n">
-        <v>0.2000735664945565</v>
+        <v>0.1424338925316634</v>
       </c>
       <c r="D280" t="n">
-        <v>105.93</v>
+        <v>2.98</v>
       </c>
       <c r="E280" t="n">
-        <v>7.244</v>
+        <v>4.66</v>
+      </c>
+      <c r="F280" t="n">
+        <v>5.071</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>7.596</v>
+        <v>5.274</v>
       </c>
       <c r="B281" t="n">
-        <v>68.5</v>
+        <v>322.7</v>
       </c>
       <c r="C281" t="n">
-        <v>0.2033978414292154</v>
+        <v>0.143201468426342</v>
       </c>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="n">
-        <v>7.319</v>
+        <v>4.51</v>
+      </c>
+      <c r="F281" t="n">
+        <v>5.135</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>7.125</v>
+        <v>5.466</v>
       </c>
       <c r="B282" t="n">
-        <v>294.1</v>
+        <v>316.8</v>
       </c>
       <c r="C282" t="n">
-        <v>0.1408299546863821</v>
-      </c>
-      <c r="D282" t="n">
-        <v>59.29</v>
-      </c>
+        <v>0.1438815170045643</v>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="n">
-        <v>7.28</v>
+        <v>4.26</v>
+      </c>
+      <c r="F282" t="n">
+        <v>5.274</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>6.638</v>
+        <v>5.767</v>
       </c>
       <c r="B283" t="n">
-        <v>309.8</v>
+        <v>334.9</v>
       </c>
       <c r="C283" t="n">
-        <v>0.1406991468515368</v>
-      </c>
-      <c r="D283" t="n">
-        <v>59.46</v>
-      </c>
+        <v>0.1450021402058431</v>
+      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" t="n">
-        <v>7.125</v>
+        <v>4.19</v>
+      </c>
+      <c r="F283" t="n">
+        <v>5.466</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>6.158</v>
+        <v>5.608</v>
       </c>
       <c r="B284" t="n">
-        <v>317.3</v>
+        <v>342.5</v>
       </c>
       <c r="C284" t="n">
-        <v>0.1403419244960488</v>
-      </c>
-      <c r="D284" t="n">
-        <v>63.85</v>
-      </c>
-      <c r="E284" t="n">
-        <v>6.638</v>
+        <v>0.1461046429190364</v>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="n">
+        <v>5.767</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>6.231</v>
+        <v>5.609</v>
       </c>
       <c r="B285" t="n">
-        <v>322.1</v>
+        <v>324</v>
       </c>
       <c r="C285" t="n">
-        <v>0.1399196773866833</v>
-      </c>
-      <c r="D285" t="n">
-        <v>64.67</v>
-      </c>
-      <c r="E285" t="n">
-        <v>6.158</v>
+        <v>0.1475045592092929</v>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="n">
+        <v>5.608</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>6.95</v>
+        <v>5.668</v>
       </c>
       <c r="B286" t="n">
-        <v>323.5</v>
+        <v>320.4</v>
       </c>
       <c r="C286" t="n">
-        <v>0.1395987841945289</v>
-      </c>
-      <c r="D286" t="n">
-        <v>64.34</v>
-      </c>
-      <c r="E286" t="n">
-        <v>6.231</v>
+        <v>0.1486359901272531</v>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="n">
+        <v>5.609</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>6.662</v>
+        <v>5.791</v>
       </c>
       <c r="B287" t="n">
-        <v>332.9</v>
+        <v>29.3</v>
       </c>
       <c r="C287" t="n">
-        <v>0.1395155218636594</v>
+        <v>0.1314584452937464</v>
       </c>
       <c r="D287" t="n">
-        <v>67.44</v>
+        <v>2.14</v>
       </c>
       <c r="E287" t="n">
-        <v>6.95</v>
+        <v>5.77</v>
+      </c>
+      <c r="F287" t="n">
+        <v>5.842</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>5.952</v>
+        <v>5.781</v>
       </c>
       <c r="B288" t="n">
-        <v>329.8</v>
+        <v>31</v>
       </c>
       <c r="C288" t="n">
-        <v>0.138879337292904</v>
+        <v>0.1330244957321785</v>
       </c>
       <c r="D288" t="n">
-        <v>69.06999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="E288" t="n">
-        <v>6.662</v>
+        <v>5.72</v>
+      </c>
+      <c r="F288" t="n">
+        <v>5.791</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>5.294</v>
+        <v>5.864</v>
       </c>
       <c r="B289" t="n">
-        <v>336.9</v>
+        <v>33.4</v>
       </c>
       <c r="C289" t="n">
-        <v>0.1395838453814687</v>
+        <v>0.134201854880302</v>
       </c>
       <c r="D289" t="n">
-        <v>71.84</v>
+        <v>2.19</v>
       </c>
       <c r="E289" t="n">
-        <v>5.952</v>
+        <v>5.68</v>
+      </c>
+      <c r="F289" t="n">
+        <v>5.781</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>5.236</v>
+        <v>6.352</v>
       </c>
       <c r="B290" t="n">
-        <v>342.9</v>
+        <v>38</v>
       </c>
       <c r="C290" t="n">
-        <v>0.1397607994950087</v>
+        <v>0.1346265172347489</v>
       </c>
       <c r="D290" t="n">
-        <v>84.05</v>
+        <v>2.16</v>
       </c>
       <c r="E290" t="n">
-        <v>5.294</v>
+        <v>5.84</v>
+      </c>
+      <c r="F290" t="n">
+        <v>5.864</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>5.23</v>
+        <v>6.57</v>
       </c>
       <c r="B291" t="n">
-        <v>345.5</v>
+        <v>34.4</v>
       </c>
       <c r="C291" t="n">
-        <v>0.1407618978314656</v>
+        <v>0.134946080693151</v>
       </c>
       <c r="D291" t="n">
-        <v>88.61</v>
+        <v>2.17</v>
       </c>
       <c r="E291" t="n">
-        <v>5.236</v>
+        <v>5.89</v>
+      </c>
+      <c r="F291" t="n">
+        <v>6.352</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>5.081</v>
+        <v>6.435</v>
       </c>
       <c r="B292" t="n">
-        <v>342.1</v>
+        <v>37.8</v>
       </c>
       <c r="C292" t="n">
-        <v>0.141822302907144</v>
+        <v>0.1357045676905654</v>
       </c>
       <c r="D292" t="n">
-        <v>90.56999999999999</v>
+        <v>2.19</v>
       </c>
       <c r="E292" t="n">
-        <v>5.23</v>
+        <v>5.84</v>
+      </c>
+      <c r="F292" t="n">
+        <v>6.57</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>5.071</v>
+        <v>6.245</v>
       </c>
       <c r="B293" t="n">
-        <v>337.7</v>
+        <v>38.5</v>
       </c>
       <c r="C293" t="n">
-        <v>0.142224975661563</v>
+        <v>0.1361312662958016</v>
       </c>
       <c r="D293" t="n">
-        <v>94.31999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="E293" t="n">
-        <v>5.081</v>
+        <v>5.85</v>
+      </c>
+      <c r="F293" t="n">
+        <v>6.435</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>5.135</v>
+        <v>6.229</v>
       </c>
       <c r="B294" t="n">
-        <v>328.6</v>
+        <v>39.2</v>
       </c>
       <c r="C294" t="n">
-        <v>0.1424338925316634</v>
+        <v>0.1396397132476974</v>
       </c>
       <c r="D294" t="n">
-        <v>98.39</v>
+        <v>2.23</v>
       </c>
       <c r="E294" t="n">
-        <v>5.071</v>
+        <v>5.85</v>
+      </c>
+      <c r="F294" t="n">
+        <v>6.245</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>5.274</v>
+        <v>6.45</v>
       </c>
       <c r="B295" t="n">
-        <v>322.7</v>
+        <v>39.1</v>
       </c>
       <c r="C295" t="n">
-        <v>0.143201468426342</v>
+        <v>0.143884793800518</v>
       </c>
       <c r="D295" t="n">
-        <v>101.81</v>
+        <v>2.24</v>
       </c>
       <c r="E295" t="n">
-        <v>5.135</v>
+        <v>5.83</v>
+      </c>
+      <c r="F295" t="n">
+        <v>6.229</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>5.466</v>
+        <v>6.283</v>
       </c>
       <c r="B296" t="n">
-        <v>316.8</v>
+        <v>40.1</v>
       </c>
       <c r="C296" t="n">
-        <v>0.1438815170045643</v>
+        <v>0.1488784638460412</v>
       </c>
       <c r="D296" t="n">
-        <v>107.1</v>
+        <v>2.31</v>
       </c>
       <c r="E296" t="n">
-        <v>5.274</v>
+        <v>5.85</v>
+      </c>
+      <c r="F296" t="n">
+        <v>6.45</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>5.767</v>
+        <v>6.365</v>
       </c>
       <c r="B297" t="n">
-        <v>334.9</v>
+        <v>41</v>
       </c>
       <c r="C297" t="n">
-        <v>0.1450021402058431</v>
+        <v>0.1541800114056834</v>
       </c>
       <c r="D297" t="n">
-        <v>110.09</v>
+        <v>2.33</v>
       </c>
       <c r="E297" t="n">
-        <v>5.466</v>
+        <v>5.86</v>
+      </c>
+      <c r="F297" t="n">
+        <v>6.283</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>5.608</v>
+        <v>6.526</v>
       </c>
       <c r="B298" t="n">
-        <v>342.5</v>
+        <v>39.5</v>
       </c>
       <c r="C298" t="n">
-        <v>0.1461046429190364</v>
+        <v>0.1595976412171882</v>
       </c>
       <c r="D298" t="n">
-        <v>114.99</v>
+        <v>2.42</v>
       </c>
       <c r="E298" t="n">
-        <v>5.767</v>
+        <v>5.86</v>
+      </c>
+      <c r="F298" t="n">
+        <v>6.365</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>5.609</v>
+        <v>6.537</v>
       </c>
       <c r="B299" t="n">
-        <v>324</v>
+        <v>41.7</v>
       </c>
       <c r="C299" t="n">
-        <v>0.1475045592092929</v>
+        <v>0.1654769693511415</v>
       </c>
       <c r="D299" t="n">
-        <v>115.6</v>
+        <v>2.38</v>
       </c>
       <c r="E299" t="n">
-        <v>5.608</v>
+        <v>5.85</v>
+      </c>
+      <c r="F299" t="n">
+        <v>6.526</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>5.668</v>
+        <v>6.251</v>
       </c>
       <c r="B300" t="n">
-        <v>320.4</v>
+        <v>43.3</v>
       </c>
       <c r="C300" t="n">
-        <v>0.1486359901272531</v>
+        <v>0.171088120456637</v>
       </c>
       <c r="D300" t="n">
-        <v>116.89</v>
+        <v>2.36</v>
       </c>
       <c r="E300" t="n">
-        <v>5.609</v>
+        <v>6.54</v>
+      </c>
+      <c r="F300" t="n">
+        <v>6.537</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>5.891</v>
+        <v>6.389</v>
       </c>
       <c r="B301" t="n">
-        <v>318</v>
+        <v>44.8</v>
       </c>
       <c r="C301" t="n">
-        <v>0.1503310765568038</v>
-      </c>
-      <c r="D301" t="inlineStr"/>
+        <v>0.1766011956133246</v>
+      </c>
+      <c r="D301" t="n">
+        <v>3.3</v>
+      </c>
       <c r="E301" t="n">
-        <v>5.668</v>
+        <v>6.17</v>
+      </c>
+      <c r="F301" t="n">
+        <v>6.251</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>5.791</v>
+        <v>6.427</v>
       </c>
       <c r="B302" t="n">
-        <v>29.3</v>
+        <v>46.9</v>
       </c>
       <c r="C302" t="n">
-        <v>0.1314584452937464</v>
-      </c>
-      <c r="D302" t="inlineStr"/>
+        <v>0.1822203712942927</v>
+      </c>
+      <c r="D302" t="n">
+        <v>3.36</v>
+      </c>
       <c r="E302" t="n">
-        <v>5.842</v>
+        <v>6.25</v>
+      </c>
+      <c r="F302" t="n">
+        <v>6.389</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>5.781</v>
+        <v>6.365</v>
       </c>
       <c r="B303" t="n">
-        <v>31</v>
+        <v>47.4</v>
       </c>
       <c r="C303" t="n">
-        <v>0.1330244957321785</v>
-      </c>
-      <c r="D303" t="inlineStr"/>
+        <v>0.1894025674556528</v>
+      </c>
+      <c r="D303" t="n">
+        <v>3.51</v>
+      </c>
       <c r="E303" t="n">
-        <v>5.791</v>
+        <v>6.4</v>
+      </c>
+      <c r="F303" t="n">
+        <v>6.427</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>5.864</v>
+        <v>6.466</v>
       </c>
       <c r="B304" t="n">
-        <v>33.4</v>
+        <v>48.5</v>
       </c>
       <c r="C304" t="n">
-        <v>0.134201854880302</v>
-      </c>
-      <c r="D304" t="inlineStr"/>
+        <v>0.1935243494800631</v>
+      </c>
+      <c r="D304" t="n">
+        <v>3.57</v>
+      </c>
       <c r="E304" t="n">
-        <v>5.781</v>
+        <v>6.29</v>
+      </c>
+      <c r="F304" t="n">
+        <v>6.365</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>6.352</v>
+        <v>7.138</v>
       </c>
       <c r="B305" t="n">
-        <v>38</v>
+        <v>52.1</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1346265172347489</v>
+        <v>0.198915451751626</v>
       </c>
       <c r="D305" t="n">
-        <v>45.01</v>
+        <v>3.86</v>
       </c>
       <c r="E305" t="n">
-        <v>5.864</v>
+        <v>6.27</v>
+      </c>
+      <c r="F305" t="n">
+        <v>6.466</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>6.57</v>
+        <v>9.653</v>
       </c>
       <c r="B306" t="n">
-        <v>34.4</v>
+        <v>68.3</v>
       </c>
       <c r="C306" t="n">
-        <v>0.134946080693151</v>
+        <v>0.1718432934349926</v>
       </c>
       <c r="D306" t="n">
-        <v>44.6</v>
+        <v>3.36</v>
       </c>
       <c r="E306" t="n">
-        <v>6.352</v>
+        <v>3.56</v>
+      </c>
+      <c r="F306" t="n">
+        <v>9.532999999999999</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>6.435</v>
+        <v>9.353999999999999</v>
       </c>
       <c r="B307" t="n">
-        <v>37.8</v>
+        <v>67.7</v>
       </c>
       <c r="C307" t="n">
-        <v>0.1357045676905654</v>
+        <v>0.1735766821651623</v>
       </c>
       <c r="D307" t="n">
-        <v>46.04</v>
+        <v>3.43</v>
       </c>
       <c r="E307" t="n">
-        <v>6.57</v>
+        <v>3.48</v>
+      </c>
+      <c r="F307" t="n">
+        <v>9.653</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>6.245</v>
+        <v>9.252000000000001</v>
       </c>
       <c r="B308" t="n">
-        <v>38.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="C308" t="n">
-        <v>0.1361312662958016</v>
+        <v>0.1754249762736376</v>
       </c>
       <c r="D308" t="n">
-        <v>38.25</v>
+        <v>3.52</v>
       </c>
       <c r="E308" t="n">
-        <v>6.435</v>
+        <v>3.44</v>
+      </c>
+      <c r="F308" t="n">
+        <v>9.353999999999999</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>6.229</v>
+        <v>9.583</v>
       </c>
       <c r="B309" t="n">
-        <v>39.2</v>
+        <v>66.8</v>
       </c>
       <c r="C309" t="n">
-        <v>0.1396397132476974</v>
+        <v>0.177229216269846</v>
       </c>
       <c r="D309" t="n">
-        <v>33.3</v>
+        <v>3.61</v>
       </c>
       <c r="E309" t="n">
-        <v>6.245</v>
+        <v>3.39</v>
+      </c>
+      <c r="F309" t="n">
+        <v>9.252000000000001</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>6.45</v>
+        <v>10.131</v>
       </c>
       <c r="B310" t="n">
-        <v>39.1</v>
+        <v>68.5</v>
       </c>
       <c r="C310" t="n">
-        <v>0.143884793800518</v>
+        <v>0.1797122487956562</v>
       </c>
       <c r="D310" t="n">
-        <v>33.83</v>
+        <v>3.72</v>
       </c>
       <c r="E310" t="n">
-        <v>6.229</v>
+        <v>3.37</v>
+      </c>
+      <c r="F310" t="n">
+        <v>9.583</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>6.283</v>
+        <v>10.019</v>
       </c>
       <c r="B311" t="n">
-        <v>40.1</v>
+        <v>67.8</v>
       </c>
       <c r="C311" t="n">
-        <v>0.1488784638460412</v>
+        <v>0.1825696159230089</v>
       </c>
       <c r="D311" t="n">
-        <v>36.19</v>
+        <v>3.85</v>
       </c>
       <c r="E311" t="n">
-        <v>6.45</v>
+        <v>3.37</v>
+      </c>
+      <c r="F311" t="n">
+        <v>10.131</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>6.365</v>
+        <v>9.718</v>
       </c>
       <c r="B312" t="n">
-        <v>41</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="C312" t="n">
-        <v>0.1541800114056834</v>
+        <v>0.1869359836507556</v>
       </c>
       <c r="D312" t="n">
-        <v>38.5</v>
+        <v>3.98</v>
       </c>
       <c r="E312" t="n">
-        <v>6.283</v>
+        <v>3.37</v>
+      </c>
+      <c r="F312" t="n">
+        <v>10.019</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>6.526</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="B313" t="n">
-        <v>39.5</v>
+        <v>61.6</v>
       </c>
       <c r="C313" t="n">
-        <v>0.1595976412171882</v>
+        <v>0.1917366783629054</v>
       </c>
       <c r="D313" t="n">
-        <v>42.27</v>
+        <v>4.09</v>
       </c>
       <c r="E313" t="n">
-        <v>6.365</v>
+        <v>3.4</v>
+      </c>
+      <c r="F313" t="n">
+        <v>9.718</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>6.537</v>
+        <v>9.395</v>
       </c>
       <c r="B314" t="n">
-        <v>41.7</v>
+        <v>62.1</v>
       </c>
       <c r="C314" t="n">
-        <v>0.1654769693511415</v>
+        <v>0.1950937409944069</v>
       </c>
       <c r="D314" t="n">
-        <v>41.89</v>
+        <v>4.25</v>
       </c>
       <c r="E314" t="n">
-        <v>6.526</v>
+        <v>3.39</v>
+      </c>
+      <c r="F314" t="n">
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>6.251</v>
+        <v>9.336</v>
       </c>
       <c r="B315" t="n">
-        <v>43.3</v>
+        <v>61.9</v>
       </c>
       <c r="C315" t="n">
-        <v>0.171088120456637</v>
+        <v>0.1998930112833169</v>
       </c>
       <c r="D315" t="n">
-        <v>52.17</v>
+        <v>4.42</v>
       </c>
       <c r="E315" t="n">
-        <v>6.537</v>
+        <v>3.31</v>
+      </c>
+      <c r="F315" t="n">
+        <v>9.395</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>6.389</v>
+        <v>9.333</v>
       </c>
       <c r="B316" t="n">
-        <v>44.8</v>
+        <v>62.2</v>
       </c>
       <c r="C316" t="n">
-        <v>0.1766011956133246</v>
+        <v>0.2044670764294134</v>
       </c>
       <c r="D316" t="n">
-        <v>87.55</v>
+        <v>4.6</v>
       </c>
       <c r="E316" t="n">
-        <v>6.251</v>
+        <v>3.36</v>
+      </c>
+      <c r="F316" t="n">
+        <v>9.336</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>6.427</v>
+        <v>9.4</v>
       </c>
       <c r="B317" t="n">
-        <v>46.9</v>
+        <v>63.2</v>
       </c>
       <c r="C317" t="n">
-        <v>0.1822203712942927</v>
+        <v>0.2088054901387407</v>
       </c>
       <c r="D317" t="n">
-        <v>87.04000000000001</v>
+        <v>4.78</v>
       </c>
       <c r="E317" t="n">
-        <v>6.389</v>
+        <v>3.38</v>
+      </c>
+      <c r="F317" t="n">
+        <v>9.333</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>6.365</v>
+        <v>9.327</v>
       </c>
       <c r="B318" t="n">
-        <v>47.4</v>
+        <v>63.8</v>
       </c>
       <c r="C318" t="n">
-        <v>0.1894025674556528</v>
+        <v>0.2132975680358158</v>
       </c>
       <c r="D318" t="n">
-        <v>90.34</v>
+        <v>4.96</v>
       </c>
       <c r="E318" t="n">
-        <v>6.427</v>
+        <v>3.38</v>
+      </c>
+      <c r="F318" t="n">
+        <v>9.4</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>6.466</v>
+        <v>9.420999999999999</v>
       </c>
       <c r="B319" t="n">
-        <v>48.5</v>
+        <v>64.7</v>
       </c>
       <c r="C319" t="n">
-        <v>0.1935243494800631</v>
+        <v>0.217890103978707</v>
       </c>
       <c r="D319" t="n">
-        <v>86.65000000000001</v>
+        <v>5.13</v>
       </c>
       <c r="E319" t="n">
-        <v>6.365</v>
+        <v>3.43</v>
+      </c>
+      <c r="F319" t="n">
+        <v>9.327</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>7.138</v>
+        <v>9.509</v>
       </c>
       <c r="B320" t="n">
-        <v>52.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C320" t="n">
-        <v>0.198915451751626</v>
+        <v>0.2221724380596847</v>
       </c>
       <c r="D320" t="n">
-        <v>104.95</v>
+        <v>5.29</v>
       </c>
       <c r="E320" t="n">
-        <v>6.466</v>
+        <v>3.49</v>
+      </c>
+      <c r="F320" t="n">
+        <v>9.420999999999999</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>8.064</v>
+        <v>10.521</v>
       </c>
       <c r="B321" t="n">
-        <v>56.6</v>
+        <v>63.4</v>
       </c>
       <c r="C321" t="n">
-        <v>0.2047916535252889</v>
-      </c>
-      <c r="D321" t="inlineStr"/>
+        <v>0.2273149118660061</v>
+      </c>
+      <c r="D321" t="n">
+        <v>5.44</v>
+      </c>
       <c r="E321" t="n">
-        <v>7.138</v>
+        <v>3.47</v>
+      </c>
+      <c r="F321" t="n">
+        <v>9.509</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>9.653</v>
+        <v>11.22</v>
       </c>
       <c r="B322" t="n">
-        <v>68.3</v>
+        <v>62.5</v>
       </c>
       <c r="C322" t="n">
-        <v>0.1718432934349926</v>
+        <v>0.2320746655593928</v>
       </c>
       <c r="D322" t="n">
-        <v>171.41</v>
+        <v>5.58</v>
       </c>
       <c r="E322" t="n">
-        <v>9.532999999999999</v>
+        <v>3.49</v>
+      </c>
+      <c r="F322" t="n">
+        <v>10.521</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>9.353999999999999</v>
+        <v>10.549</v>
       </c>
       <c r="B323" t="n">
-        <v>67.7</v>
+        <v>64.5</v>
       </c>
       <c r="C323" t="n">
-        <v>0.1735766821651623</v>
+        <v>0.2362169045794227</v>
       </c>
       <c r="D323" t="n">
-        <v>175.59</v>
+        <v>5.7</v>
       </c>
       <c r="E323" t="n">
-        <v>9.653</v>
+        <v>3.46</v>
+      </c>
+      <c r="F323" t="n">
+        <v>11.22</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>9.252000000000001</v>
+        <v>10.028</v>
       </c>
       <c r="B324" t="n">
-        <v>67.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C324" t="n">
-        <v>0.1754249762736376</v>
-      </c>
-      <c r="D324" t="n">
-        <v>181.95</v>
-      </c>
-      <c r="E324" t="n">
-        <v>9.353999999999999</v>
+        <v>0.2387557752627959</v>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="n">
+        <v>10.549</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>9.583</v>
+        <v>6.616</v>
       </c>
       <c r="B325" t="n">
-        <v>66.8</v>
+        <v>32.9</v>
       </c>
       <c r="C325" t="n">
-        <v>0.177229216269846</v>
+        <v>0.1168060290152875</v>
       </c>
       <c r="D325" t="n">
-        <v>189.07</v>
+        <v>3.04</v>
       </c>
       <c r="E325" t="n">
-        <v>9.252000000000001</v>
+        <v>6.79</v>
+      </c>
+      <c r="F325" t="n">
+        <v>6.495</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>10.131</v>
+        <v>6.852</v>
       </c>
       <c r="B326" t="n">
-        <v>68.5</v>
+        <v>36.3</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1797122487956562</v>
+        <v>0.1181823020892891</v>
       </c>
       <c r="D326" t="n">
-        <v>195.68</v>
+        <v>3.17</v>
       </c>
       <c r="E326" t="n">
-        <v>9.583</v>
+        <v>6.73</v>
+      </c>
+      <c r="F326" t="n">
+        <v>6.616</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>10.019</v>
+        <v>7.175</v>
       </c>
       <c r="B327" t="n">
-        <v>67.8</v>
+        <v>42.3</v>
       </c>
       <c r="C327" t="n">
-        <v>0.1825696159230089</v>
+        <v>0.1196412552715524</v>
       </c>
       <c r="D327" t="n">
-        <v>204.87</v>
+        <v>3.39</v>
       </c>
       <c r="E327" t="n">
-        <v>10.131</v>
+        <v>6.78</v>
+      </c>
+      <c r="F327" t="n">
+        <v>6.852</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>9.718</v>
+        <v>6.96</v>
       </c>
       <c r="B328" t="n">
-        <v>64.40000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="C328" t="n">
-        <v>0.1869359836507556</v>
+        <v>0.1210273910429638</v>
       </c>
       <c r="D328" t="n">
-        <v>212.1</v>
+        <v>3.37</v>
       </c>
       <c r="E328" t="n">
-        <v>10.019</v>
+        <v>6.59</v>
+      </c>
+      <c r="F328" t="n">
+        <v>7.175</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>9.640000000000001</v>
+        <v>7.953</v>
       </c>
       <c r="B329" t="n">
-        <v>61.6</v>
+        <v>48.8</v>
       </c>
       <c r="C329" t="n">
-        <v>0.1917366783629054</v>
+        <v>0.1224416389637264</v>
       </c>
       <c r="D329" t="n">
-        <v>214.11</v>
+        <v>3.3</v>
       </c>
       <c r="E329" t="n">
-        <v>9.718</v>
+        <v>6.54</v>
+      </c>
+      <c r="F329" t="n">
+        <v>6.96</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>9.395</v>
+        <v>7.671</v>
       </c>
       <c r="B330" t="n">
-        <v>62.1</v>
+        <v>50.4</v>
       </c>
       <c r="C330" t="n">
-        <v>0.1950937409944069</v>
+        <v>0.1243766244126143</v>
       </c>
       <c r="D330" t="n">
-        <v>220.1</v>
+        <v>3.36</v>
       </c>
       <c r="E330" t="n">
-        <v>9.640000000000001</v>
+        <v>6.46</v>
+      </c>
+      <c r="F330" t="n">
+        <v>7.953</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>9.336</v>
+        <v>7.315</v>
       </c>
       <c r="B331" t="n">
-        <v>61.9</v>
+        <v>51.3</v>
       </c>
       <c r="C331" t="n">
-        <v>0.1998930112833169</v>
+        <v>0.1258145190512802</v>
       </c>
       <c r="D331" t="n">
-        <v>229.82</v>
+        <v>3.31</v>
       </c>
       <c r="E331" t="n">
-        <v>9.395</v>
+        <v>6.05</v>
+      </c>
+      <c r="F331" t="n">
+        <v>7.671</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>9.333</v>
+        <v>7.528</v>
       </c>
       <c r="B332" t="n">
-        <v>62.2</v>
+        <v>52.5</v>
       </c>
       <c r="C332" t="n">
-        <v>0.2044670764294134</v>
+        <v>0.1277980845700904</v>
       </c>
       <c r="D332" t="n">
-        <v>241.35</v>
+        <v>3.36</v>
       </c>
       <c r="E332" t="n">
-        <v>9.336</v>
+        <v>5.91</v>
+      </c>
+      <c r="F332" t="n">
+        <v>7.315</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>9.4</v>
+        <v>7.48</v>
       </c>
       <c r="B333" t="n">
-        <v>63.2</v>
+        <v>52.5</v>
       </c>
       <c r="C333" t="n">
-        <v>0.2088054901387407</v>
+        <v>0.131259199132999</v>
       </c>
       <c r="D333" t="n">
-        <v>252.58</v>
+        <v>3.39</v>
       </c>
       <c r="E333" t="n">
-        <v>9.333</v>
+        <v>5.8</v>
+      </c>
+      <c r="F333" t="n">
+        <v>7.528</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>9.327</v>
+        <v>6.865</v>
       </c>
       <c r="B334" t="n">
-        <v>63.8</v>
+        <v>52.6</v>
       </c>
       <c r="C334" t="n">
-        <v>0.2132975680358158</v>
+        <v>0.1353661195849518</v>
       </c>
       <c r="D334" t="n">
-        <v>262.02</v>
+        <v>3.43</v>
       </c>
       <c r="E334" t="n">
-        <v>9.4</v>
+        <v>5.79</v>
+      </c>
+      <c r="F334" t="n">
+        <v>7.48</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>9.420999999999999</v>
+        <v>6.741</v>
       </c>
       <c r="B335" t="n">
-        <v>64.7</v>
+        <v>53.3</v>
       </c>
       <c r="C335" t="n">
-        <v>0.217890103978707</v>
+        <v>0.1396108238004969</v>
       </c>
       <c r="D335" t="n">
-        <v>267.71</v>
+        <v>3.45</v>
       </c>
       <c r="E335" t="n">
-        <v>9.327</v>
+        <v>5.75</v>
+      </c>
+      <c r="F335" t="n">
+        <v>6.865</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>9.509</v>
+        <v>6.942</v>
       </c>
       <c r="B336" t="n">
-        <v>65.40000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="C336" t="n">
-        <v>0.2221724380596847</v>
+        <v>0.14447099028943</v>
       </c>
       <c r="D336" t="n">
-        <v>280.84</v>
+        <v>3.47</v>
       </c>
       <c r="E336" t="n">
-        <v>9.420999999999999</v>
+        <v>5.78</v>
+      </c>
+      <c r="F336" t="n">
+        <v>6.741</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>10.521</v>
+        <v>6.734</v>
       </c>
       <c r="B337" t="n">
-        <v>63.4</v>
+        <v>52.7</v>
       </c>
       <c r="C337" t="n">
-        <v>0.2273149118660061</v>
+        <v>0.1498818013876953</v>
       </c>
       <c r="D337" t="n">
-        <v>289.83</v>
+        <v>3.42</v>
       </c>
       <c r="E337" t="n">
-        <v>9.509</v>
+        <v>5.82</v>
+      </c>
+      <c r="F337" t="n">
+        <v>6.942</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>11.22</v>
+        <v>6.637</v>
       </c>
       <c r="B338" t="n">
-        <v>62.5</v>
+        <v>54.1</v>
       </c>
       <c r="C338" t="n">
-        <v>0.2320746655593928</v>
+        <v>0.1552152074545481</v>
       </c>
       <c r="D338" t="n">
-        <v>295.82</v>
+        <v>3.52</v>
       </c>
       <c r="E338" t="n">
-        <v>10.521</v>
+        <v>5.69</v>
+      </c>
+      <c r="F338" t="n">
+        <v>6.734</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>10.549</v>
+        <v>6.911</v>
       </c>
       <c r="B339" t="n">
-        <v>64.5</v>
+        <v>54.7</v>
       </c>
       <c r="C339" t="n">
-        <v>0.2362169045794227</v>
+        <v>0.1604131130420934</v>
       </c>
       <c r="D339" t="n">
-        <v>302.54</v>
+        <v>3.57</v>
       </c>
       <c r="E339" t="n">
-        <v>11.22</v>
+        <v>5.77</v>
+      </c>
+      <c r="F339" t="n">
+        <v>6.637</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>10.028</v>
+        <v>7.06</v>
       </c>
       <c r="B340" t="n">
-        <v>66.59999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="C340" t="n">
-        <v>0.2387557752627959</v>
+        <v>0.1658475746870622</v>
       </c>
       <c r="D340" t="n">
-        <v>307.85</v>
+        <v>3.67</v>
       </c>
       <c r="E340" t="n">
-        <v>10.549</v>
+        <v>5.7</v>
+      </c>
+      <c r="F340" t="n">
+        <v>6.911</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>10.241</v>
+        <v>7.629</v>
       </c>
       <c r="B341" t="n">
-        <v>67.7</v>
+        <v>56.3</v>
       </c>
       <c r="C341" t="n">
-        <v>0.2410376921360569</v>
-      </c>
-      <c r="D341" t="inlineStr"/>
+        <v>0.1707072133479346</v>
+      </c>
+      <c r="D341" t="n">
+        <v>3.68</v>
+      </c>
       <c r="E341" t="n">
-        <v>10.028</v>
+        <v>5.7</v>
+      </c>
+      <c r="F341" t="n">
+        <v>7.06</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>6.616</v>
+        <v>7.702</v>
       </c>
       <c r="B342" t="n">
-        <v>32.9</v>
+        <v>55.8</v>
       </c>
       <c r="C342" t="n">
-        <v>0.1168060290152875</v>
-      </c>
-      <c r="D342" t="inlineStr"/>
+        <v>0.1738745309779065</v>
+      </c>
+      <c r="D342" t="n">
+        <v>3.73</v>
+      </c>
       <c r="E342" t="n">
-        <v>6.495</v>
+        <v>5.68</v>
+      </c>
+      <c r="F342" t="n">
+        <v>7.629</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>6.852</v>
+        <v>7.353</v>
       </c>
       <c r="B343" t="n">
-        <v>36.3</v>
+        <v>59</v>
       </c>
       <c r="C343" t="n">
-        <v>0.1181823020892891</v>
-      </c>
-      <c r="D343" t="inlineStr"/>
+        <v>0.1785052733646822</v>
+      </c>
+      <c r="D343" t="n">
+        <v>3.82</v>
+      </c>
       <c r="E343" t="n">
-        <v>6.616</v>
+        <v>5.65</v>
+      </c>
+      <c r="F343" t="n">
+        <v>7.702</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>7.175</v>
+        <v>8.053000000000001</v>
       </c>
       <c r="B344" t="n">
-        <v>42.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="C344" t="n">
-        <v>0.1196412552715524</v>
-      </c>
-      <c r="D344" t="inlineStr"/>
+        <v>0.1534268793896645</v>
+      </c>
+      <c r="D344" t="n">
+        <v>2.35</v>
+      </c>
       <c r="E344" t="n">
-        <v>6.852</v>
+        <v>4.83</v>
+      </c>
+      <c r="F344" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>6.96</v>
+        <v>7.867</v>
       </c>
       <c r="B345" t="n">
-        <v>48.1</v>
+        <v>66.8</v>
       </c>
       <c r="C345" t="n">
-        <v>0.1210273910429638</v>
-      </c>
-      <c r="D345" t="inlineStr"/>
+        <v>0.1561747825401152</v>
+      </c>
+      <c r="D345" t="n">
+        <v>2.36</v>
+      </c>
       <c r="E345" t="n">
-        <v>7.175</v>
+        <v>4.77</v>
+      </c>
+      <c r="F345" t="n">
+        <v>8.053000000000001</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>7.953</v>
+        <v>7.541</v>
       </c>
       <c r="B346" t="n">
-        <v>48.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C346" t="n">
-        <v>0.1224416389637264</v>
-      </c>
-      <c r="D346" t="inlineStr"/>
+        <v>0.158990577389216</v>
+      </c>
+      <c r="D346" t="n">
+        <v>2.39</v>
+      </c>
       <c r="E346" t="n">
-        <v>6.96</v>
+        <v>4.68</v>
+      </c>
+      <c r="F346" t="n">
+        <v>7.867</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>7.671</v>
+        <v>7.893</v>
       </c>
       <c r="B347" t="n">
-        <v>50.4</v>
+        <v>73.5</v>
       </c>
       <c r="C347" t="n">
-        <v>0.1243766244126143</v>
-      </c>
-      <c r="D347" t="inlineStr"/>
+        <v>0.162639925303529</v>
+      </c>
+      <c r="D347" t="n">
+        <v>2.4</v>
+      </c>
       <c r="E347" t="n">
-        <v>7.953</v>
+        <v>4.74</v>
+      </c>
+      <c r="F347" t="n">
+        <v>7.541</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>7.315</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="B348" t="n">
-        <v>51.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="C348" t="n">
-        <v>0.1258145190512802</v>
-      </c>
-      <c r="D348" t="inlineStr"/>
+        <v>0.1643550706025796</v>
+      </c>
+      <c r="D348" t="n">
+        <v>2.41</v>
+      </c>
       <c r="E348" t="n">
-        <v>7.671</v>
+        <v>4.6</v>
+      </c>
+      <c r="F348" t="n">
+        <v>7.893</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>7.528</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="B349" t="n">
-        <v>52.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C349" t="n">
-        <v>0.1277980845700904</v>
-      </c>
-      <c r="D349" t="inlineStr"/>
+        <v>0.1652510825725363</v>
+      </c>
+      <c r="D349" t="n">
+        <v>2.43</v>
+      </c>
       <c r="E349" t="n">
-        <v>7.315</v>
+        <v>4.57</v>
+      </c>
+      <c r="F349" t="n">
+        <v>8.641999999999999</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>7.48</v>
+        <v>8.601000000000001</v>
       </c>
       <c r="B350" t="n">
-        <v>52.5</v>
+        <v>69.2</v>
       </c>
       <c r="C350" t="n">
-        <v>0.131259199132999</v>
-      </c>
-      <c r="D350" t="inlineStr"/>
+        <v>0.1653232945840603</v>
+      </c>
+      <c r="D350" t="n">
+        <v>2.49</v>
+      </c>
       <c r="E350" t="n">
-        <v>7.528</v>
+        <v>4.62</v>
+      </c>
+      <c r="F350" t="n">
+        <v>8.638999999999999</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>6.865</v>
+        <v>8.792999999999999</v>
       </c>
       <c r="B351" t="n">
-        <v>52.6</v>
+        <v>67.2</v>
       </c>
       <c r="C351" t="n">
-        <v>0.1353661195849518</v>
-      </c>
-      <c r="D351" t="inlineStr"/>
+        <v>0.1678427007398701</v>
+      </c>
+      <c r="D351" t="n">
+        <v>2.54</v>
+      </c>
       <c r="E351" t="n">
-        <v>7.48</v>
+        <v>4.54</v>
+      </c>
+      <c r="F351" t="n">
+        <v>8.601000000000001</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>6.741</v>
+        <v>8.84</v>
       </c>
       <c r="B352" t="n">
-        <v>53.3</v>
+        <v>66.7</v>
       </c>
       <c r="C352" t="n">
-        <v>0.1396108238004969</v>
-      </c>
-      <c r="D352" t="inlineStr"/>
+        <v>0.1710420672802541</v>
+      </c>
+      <c r="D352" t="n">
+        <v>2.63</v>
+      </c>
       <c r="E352" t="n">
-        <v>6.865</v>
+        <v>4.55</v>
+      </c>
+      <c r="F352" t="n">
+        <v>8.792999999999999</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>6.942</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="B353" t="n">
-        <v>52.8</v>
+        <v>67.3</v>
       </c>
       <c r="C353" t="n">
-        <v>0.14447099028943</v>
-      </c>
-      <c r="D353" t="inlineStr"/>
+        <v>0.174716714740052</v>
+      </c>
+      <c r="D353" t="n">
+        <v>2.77</v>
+      </c>
       <c r="E353" t="n">
-        <v>6.741</v>
+        <v>4.54</v>
+      </c>
+      <c r="F353" t="n">
+        <v>8.84</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>6.734</v>
+        <v>8.597</v>
       </c>
       <c r="B354" t="n">
-        <v>52.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="C354" t="n">
-        <v>0.1498818013876953</v>
-      </c>
-      <c r="D354" t="inlineStr"/>
+        <v>0.1790637721935513</v>
+      </c>
+      <c r="D354" t="n">
+        <v>2.83</v>
+      </c>
       <c r="E354" t="n">
-        <v>6.942</v>
+        <v>4.51</v>
+      </c>
+      <c r="F354" t="n">
+        <v>8.585000000000001</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>6.637</v>
+        <v>8.569000000000001</v>
       </c>
       <c r="B355" t="n">
-        <v>54.1</v>
+        <v>68</v>
       </c>
       <c r="C355" t="n">
-        <v>0.1552152074545481</v>
-      </c>
-      <c r="D355" t="inlineStr"/>
+        <v>0.1841411731877135</v>
+      </c>
+      <c r="D355" t="n">
+        <v>3.01</v>
+      </c>
       <c r="E355" t="n">
-        <v>6.734</v>
+        <v>4.49</v>
+      </c>
+      <c r="F355" t="n">
+        <v>8.597</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>6.911</v>
+        <v>8.259</v>
       </c>
       <c r="B356" t="n">
-        <v>54.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="C356" t="n">
-        <v>0.1604131130420934</v>
-      </c>
-      <c r="D356" t="inlineStr"/>
+        <v>0.1889863715242062</v>
+      </c>
+      <c r="D356" t="n">
+        <v>3.1</v>
+      </c>
       <c r="E356" t="n">
-        <v>6.637</v>
+        <v>4.5</v>
+      </c>
+      <c r="F356" t="n">
+        <v>8.569000000000001</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>7.06</v>
+        <v>8.352</v>
       </c>
       <c r="B357" t="n">
-        <v>56.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="C357" t="n">
-        <v>0.1658475746870622</v>
-      </c>
-      <c r="D357" t="inlineStr"/>
+        <v>0.1941389921040409</v>
+      </c>
+      <c r="D357" t="n">
+        <v>3.18</v>
+      </c>
       <c r="E357" t="n">
-        <v>6.911</v>
+        <v>4.43</v>
+      </c>
+      <c r="F357" t="n">
+        <v>8.259</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>7.629</v>
+        <v>8.566000000000001</v>
       </c>
       <c r="B358" t="n">
-        <v>56.3</v>
+        <v>72.7</v>
       </c>
       <c r="C358" t="n">
-        <v>0.1707072133479346</v>
-      </c>
-      <c r="D358" t="inlineStr"/>
+        <v>0.1984970022701628</v>
+      </c>
+      <c r="D358" t="n">
+        <v>3.26</v>
+      </c>
       <c r="E358" t="n">
-        <v>7.06</v>
+        <v>4.43</v>
+      </c>
+      <c r="F358" t="n">
+        <v>8.352</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>7.702</v>
+        <v>9.49</v>
       </c>
       <c r="B359" t="n">
-        <v>55.8</v>
+        <v>72.8</v>
       </c>
       <c r="C359" t="n">
-        <v>0.1738745309779065</v>
-      </c>
-      <c r="D359" t="inlineStr"/>
+        <v>0.2023054009784046</v>
+      </c>
+      <c r="D359" t="n">
+        <v>3.3</v>
+      </c>
       <c r="E359" t="n">
-        <v>7.629</v>
+        <v>4.28</v>
+      </c>
+      <c r="F359" t="n">
+        <v>8.566000000000001</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>7.353</v>
+        <v>9.526999999999999</v>
       </c>
       <c r="B360" t="n">
-        <v>59</v>
+        <v>74.2</v>
       </c>
       <c r="C360" t="n">
-        <v>0.1785052733646822</v>
-      </c>
-      <c r="D360" t="inlineStr"/>
+        <v>0.2066001668107333</v>
+      </c>
+      <c r="D360" t="n">
+        <v>3.34</v>
+      </c>
       <c r="E360" t="n">
-        <v>7.702</v>
+        <v>4.25</v>
+      </c>
+      <c r="F360" t="n">
+        <v>9.49</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>8.364000000000001</v>
+        <v>9.627000000000001</v>
       </c>
       <c r="B361" t="n">
-        <v>59.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="C361" t="n">
-        <v>0.1835001724523461</v>
-      </c>
-      <c r="D361" t="inlineStr"/>
+        <v>0.2110607541833161</v>
+      </c>
+      <c r="D361" t="n">
+        <v>3.37</v>
+      </c>
       <c r="E361" t="n">
-        <v>7.353</v>
+        <v>4.12</v>
+      </c>
+      <c r="F361" t="n">
+        <v>9.526999999999999</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>8.053000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="B362" t="n">
-        <v>65.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="C362" t="n">
-        <v>0.1534268793896645</v>
+        <v>0.2143193202366399</v>
       </c>
       <c r="D362" t="n">
-        <v>46.52</v>
+        <v>3.5</v>
       </c>
       <c r="E362" t="n">
-        <v>8</v>
+        <v>4.05</v>
+      </c>
+      <c r="F362" t="n">
+        <v>9.627000000000001</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>7.867</v>
+        <v>6.335</v>
       </c>
       <c r="B363" t="n">
-        <v>66.8</v>
+        <v>48.8</v>
       </c>
       <c r="C363" t="n">
-        <v>0.1561747825401152</v>
+        <v>0.1406167653133611</v>
       </c>
       <c r="D363" t="n">
-        <v>46.52</v>
+        <v>3.56</v>
       </c>
       <c r="E363" t="n">
-        <v>8.053000000000001</v>
+        <v>6.37</v>
+      </c>
+      <c r="F363" t="n">
+        <v>6.333</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>7.541</v>
+        <v>6.165</v>
       </c>
       <c r="B364" t="n">
-        <v>70.09999999999999</v>
+        <v>52</v>
       </c>
       <c r="C364" t="n">
-        <v>0.158990577389216</v>
+        <v>0.1424070068626666</v>
       </c>
       <c r="D364" t="n">
-        <v>48.01</v>
+        <v>3.57</v>
       </c>
       <c r="E364" t="n">
-        <v>7.867</v>
+        <v>6.3</v>
+      </c>
+      <c r="F364" t="n">
+        <v>6.335</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>7.893</v>
+        <v>5.99</v>
       </c>
       <c r="B365" t="n">
-        <v>73.5</v>
+        <v>54.5</v>
       </c>
       <c r="C365" t="n">
-        <v>0.162639925303529</v>
+        <v>0.1445307513492233</v>
       </c>
       <c r="D365" t="n">
-        <v>47.96</v>
+        <v>3.57</v>
       </c>
       <c r="E365" t="n">
-        <v>7.541</v>
+        <v>6.18</v>
+      </c>
+      <c r="F365" t="n">
+        <v>6.165</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>8.641999999999999</v>
+        <v>6.339</v>
       </c>
       <c r="B366" t="n">
-        <v>72.40000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="C366" t="n">
-        <v>0.1643550706025796</v>
+        <v>0.146240093462299</v>
       </c>
       <c r="D366" t="n">
-        <v>48.87</v>
+        <v>3.56</v>
       </c>
       <c r="E366" t="n">
-        <v>7.893</v>
+        <v>6.09</v>
+      </c>
+      <c r="F366" t="n">
+        <v>5.99</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>8.638999999999999</v>
+        <v>7.265</v>
       </c>
       <c r="B367" t="n">
-        <v>70.09999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="C367" t="n">
-        <v>0.1652510825725363</v>
+        <v>0.1492788599187226</v>
       </c>
       <c r="D367" t="n">
-        <v>50.17</v>
+        <v>3.58</v>
       </c>
       <c r="E367" t="n">
-        <v>8.641999999999999</v>
+        <v>6.03</v>
+      </c>
+      <c r="F367" t="n">
+        <v>6.339</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>8.601000000000001</v>
+        <v>7.478</v>
       </c>
       <c r="B368" t="n">
-        <v>69.2</v>
+        <v>60.4</v>
       </c>
       <c r="C368" t="n">
-        <v>0.1653232945840603</v>
+        <v>0.1528872630396533</v>
       </c>
       <c r="D368" t="n">
-        <v>52.14</v>
+        <v>3.63</v>
       </c>
       <c r="E368" t="n">
-        <v>8.638999999999999</v>
+        <v>5.94</v>
+      </c>
+      <c r="F368" t="n">
+        <v>7.265</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>8.792999999999999</v>
+        <v>7.473</v>
       </c>
       <c r="B369" t="n">
-        <v>67.2</v>
+        <v>61.3</v>
       </c>
       <c r="C369" t="n">
-        <v>0.1678427007398701</v>
+        <v>0.1560990741538045</v>
       </c>
       <c r="D369" t="n">
-        <v>54.16</v>
+        <v>3.7</v>
       </c>
       <c r="E369" t="n">
-        <v>8.601000000000001</v>
+        <v>5.75</v>
+      </c>
+      <c r="F369" t="n">
+        <v>7.478</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>8.84</v>
+        <v>7.54</v>
       </c>
       <c r="B370" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="C370" t="n">
-        <v>0.1710420672802541</v>
+        <v>0.16195753725806</v>
       </c>
       <c r="D370" t="n">
-        <v>57.86</v>
+        <v>3.76</v>
       </c>
       <c r="E370" t="n">
-        <v>8.792999999999999</v>
+        <v>5.6</v>
+      </c>
+      <c r="F370" t="n">
+        <v>7.473</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>8.585000000000001</v>
+        <v>7.448</v>
       </c>
       <c r="B371" t="n">
-        <v>67.3</v>
+        <v>58.2</v>
       </c>
       <c r="C371" t="n">
-        <v>0.174716714740052</v>
+        <v>0.1680864386834504</v>
       </c>
       <c r="D371" t="n">
-        <v>61.7</v>
+        <v>3.79</v>
       </c>
       <c r="E371" t="n">
-        <v>8.84</v>
+        <v>5.4</v>
+      </c>
+      <c r="F371" t="n">
+        <v>7.54</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>8.597</v>
+        <v>7.539</v>
       </c>
       <c r="B372" t="n">
-        <v>67.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="C372" t="n">
-        <v>0.1790637721935513</v>
+        <v>0.1736559397033166</v>
       </c>
       <c r="D372" t="n">
-        <v>65.55</v>
+        <v>3.83</v>
       </c>
       <c r="E372" t="n">
-        <v>8.585000000000001</v>
+        <v>5.36</v>
+      </c>
+      <c r="F372" t="n">
+        <v>7.448</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>8.569000000000001</v>
+        <v>7.293</v>
       </c>
       <c r="B373" t="n">
-        <v>68</v>
+        <v>58.4</v>
       </c>
       <c r="C373" t="n">
-        <v>0.1841411731877135</v>
+        <v>0.178435844576081</v>
       </c>
       <c r="D373" t="n">
-        <v>67.52</v>
+        <v>3.86</v>
       </c>
       <c r="E373" t="n">
-        <v>8.597</v>
+        <v>5.39</v>
+      </c>
+      <c r="F373" t="n">
+        <v>7.539</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>8.259</v>
+        <v>7.323</v>
       </c>
       <c r="B374" t="n">
-        <v>69.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="C374" t="n">
-        <v>0.1889863715242062</v>
+        <v>0.1831003171072376</v>
       </c>
       <c r="D374" t="n">
-        <v>67.28</v>
+        <v>3.92</v>
       </c>
       <c r="E374" t="n">
-        <v>8.569000000000001</v>
+        <v>5.7</v>
+      </c>
+      <c r="F374" t="n">
+        <v>7.293</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>8.352</v>
+        <v>7.242</v>
       </c>
       <c r="B375" t="n">
-        <v>71.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="C375" t="n">
-        <v>0.1941389921040409</v>
+        <v>0.1880098158395738</v>
       </c>
       <c r="D375" t="n">
-        <v>67.52</v>
+        <v>3.98</v>
       </c>
       <c r="E375" t="n">
-        <v>8.259</v>
+        <v>5.71</v>
+      </c>
+      <c r="F375" t="n">
+        <v>7.323</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>8.566000000000001</v>
+        <v>7.372</v>
       </c>
       <c r="B376" t="n">
-        <v>72.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="C376" t="n">
-        <v>0.1984970022701628</v>
+        <v>0.1922876931363692</v>
       </c>
       <c r="D376" t="n">
-        <v>67.70999999999999</v>
+        <v>4.04</v>
       </c>
       <c r="E376" t="n">
-        <v>8.352</v>
+        <v>5.68</v>
+      </c>
+      <c r="F376" t="n">
+        <v>7.242</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>9.49</v>
+        <v>7.488</v>
       </c>
       <c r="B377" t="n">
-        <v>72.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="C377" t="n">
-        <v>0.2023054009784046</v>
+        <v>0.1959301583128322</v>
       </c>
       <c r="D377" t="n">
-        <v>68.97</v>
+        <v>4.07</v>
       </c>
       <c r="E377" t="n">
-        <v>8.566000000000001</v>
+        <v>5.67</v>
+      </c>
+      <c r="F377" t="n">
+        <v>7.372</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>9.526999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="B378" t="n">
-        <v>74.2</v>
+        <v>68.8</v>
       </c>
       <c r="C378" t="n">
-        <v>0.2066001668107333</v>
+        <v>0.1993306675865647</v>
       </c>
       <c r="D378" t="n">
-        <v>69.26000000000001</v>
+        <v>4.13</v>
       </c>
       <c r="E378" t="n">
-        <v>9.49</v>
+        <v>5.86</v>
+      </c>
+      <c r="F378" t="n">
+        <v>7.488</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>9.627000000000001</v>
+        <v>9.154</v>
       </c>
       <c r="B379" t="n">
-        <v>74.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="C379" t="n">
-        <v>0.2110607541833161</v>
+        <v>0.2050374107799302</v>
       </c>
       <c r="D379" t="n">
-        <v>68.61</v>
+        <v>4.26</v>
       </c>
       <c r="E379" t="n">
-        <v>9.526999999999999</v>
+        <v>5.93</v>
+      </c>
+      <c r="F379" t="n">
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>9.300000000000001</v>
+        <v>8.471</v>
       </c>
       <c r="B380" t="n">
-        <v>78.7</v>
+        <v>73.8</v>
       </c>
       <c r="C380" t="n">
-        <v>0.2143193202366399</v>
+        <v>0.2062536305328274</v>
       </c>
       <c r="D380" t="n">
-        <v>71.26000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="E380" t="n">
-        <v>9.627000000000001</v>
+        <v>4.92</v>
+      </c>
+      <c r="F380" t="n">
+        <v>9.154</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>9.875999999999999</v>
+        <v>8.427</v>
       </c>
       <c r="B381" t="n">
-        <v>79.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C381" t="n">
-        <v>0.2177604076180737</v>
-      </c>
-      <c r="D381" t="inlineStr"/>
+        <v>0.2039106983689446</v>
+      </c>
+      <c r="D381" t="n">
+        <v>4.86</v>
+      </c>
       <c r="E381" t="n">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="n">
-        <v>6.335</v>
-      </c>
-      <c r="B382" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="C382" t="n">
-        <v>0.1406167653133611</v>
-      </c>
-      <c r="D382" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="E382" t="n">
-        <v>6.333</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="n">
-        <v>6.165</v>
-      </c>
-      <c r="B383" t="n">
-        <v>52</v>
-      </c>
-      <c r="C383" t="n">
-        <v>0.1424070068626666</v>
-      </c>
-      <c r="D383" t="n">
-        <v>69.52</v>
-      </c>
-      <c r="E383" t="n">
-        <v>6.335</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="B384" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="C384" t="n">
-        <v>0.1445307513492233</v>
-      </c>
-      <c r="D384" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="E384" t="n">
-        <v>6.165</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="n">
-        <v>6.339</v>
-      </c>
-      <c r="B385" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="C385" t="n">
-        <v>0.146240093462299</v>
-      </c>
-      <c r="D385" t="n">
-        <v>68.84999999999999</v>
-      </c>
-      <c r="E385" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="n">
-        <v>7.265</v>
-      </c>
-      <c r="B386" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="C386" t="n">
-        <v>0.1492788599187226</v>
-      </c>
-      <c r="D386" t="n">
-        <v>69.17</v>
-      </c>
-      <c r="E386" t="n">
-        <v>6.339</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="n">
-        <v>7.478</v>
-      </c>
-      <c r="B387" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="C387" t="n">
-        <v>0.1528872630396533</v>
-      </c>
-      <c r="D387" t="n">
-        <v>69.19</v>
-      </c>
-      <c r="E387" t="n">
-        <v>7.265</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="n">
-        <v>7.473</v>
-      </c>
-      <c r="B388" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="C388" t="n">
-        <v>0.1560990741538045</v>
-      </c>
-      <c r="D388" t="n">
-        <v>69.19</v>
-      </c>
-      <c r="E388" t="n">
-        <v>7.478</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="B389" t="n">
-        <v>60</v>
-      </c>
-      <c r="C389" t="n">
-        <v>0.16195753725806</v>
-      </c>
-      <c r="D389" t="n">
-        <v>69.34999999999999</v>
-      </c>
-      <c r="E389" t="n">
-        <v>7.473</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="n">
-        <v>7.448</v>
-      </c>
-      <c r="B390" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="C390" t="n">
-        <v>0.1680864386834504</v>
-      </c>
-      <c r="D390" t="n">
-        <v>69.20999999999999</v>
-      </c>
-      <c r="E390" t="n">
-        <v>7.54</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="n">
-        <v>7.539</v>
-      </c>
-      <c r="B391" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="C391" t="n">
-        <v>0.1736559397033166</v>
-      </c>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" t="n">
-        <v>7.448</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="n">
-        <v>7.293</v>
-      </c>
-      <c r="B392" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="C392" t="n">
-        <v>0.178435844576081</v>
-      </c>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="n">
-        <v>7.539</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="n">
-        <v>7.323</v>
-      </c>
-      <c r="B393" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="C393" t="n">
-        <v>0.1831003171072376</v>
-      </c>
-      <c r="D393" t="inlineStr"/>
-      <c r="E393" t="n">
-        <v>7.293</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="n">
-        <v>7.242</v>
-      </c>
-      <c r="B394" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="C394" t="n">
-        <v>0.1880098158395738</v>
-      </c>
-      <c r="D394" t="inlineStr"/>
-      <c r="E394" t="n">
-        <v>7.323</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="n">
-        <v>7.372</v>
-      </c>
-      <c r="B395" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="C395" t="n">
-        <v>0.1922876931363692</v>
-      </c>
-      <c r="D395" t="inlineStr"/>
-      <c r="E395" t="n">
-        <v>7.242</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="n">
-        <v>7.488</v>
-      </c>
-      <c r="B396" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="C396" t="n">
-        <v>0.1959301583128322</v>
-      </c>
-      <c r="D396" t="n">
-        <v>68.69</v>
-      </c>
-      <c r="E396" t="n">
-        <v>7.372</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="B397" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="C397" t="n">
-        <v>0.1993306675865647</v>
-      </c>
-      <c r="D397" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="E397" t="n">
-        <v>7.488</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="n">
-        <v>9.154</v>
-      </c>
-      <c r="B398" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="C398" t="n">
-        <v>0.2050374107799302</v>
-      </c>
-      <c r="D398" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="E398" t="n">
-        <v>8.970000000000001</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="F381" t="n">
         <v>8.471</v>
-      </c>
-      <c r="B399" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="C399" t="n">
-        <v>0.2062536305328274</v>
-      </c>
-      <c r="D399" t="n">
-        <v>77.19</v>
-      </c>
-      <c r="E399" t="n">
-        <v>9.154</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="n">
-        <v>8.427</v>
-      </c>
-      <c r="B400" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="C400" t="n">
-        <v>0.2039106983689446</v>
-      </c>
-      <c r="D400" t="n">
-        <v>76.37</v>
-      </c>
-      <c r="E400" t="n">
-        <v>8.471</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="n">
-        <v>8.507</v>
-      </c>
-      <c r="B401" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="C401" t="n">
-        <v>0.2052484483588221</v>
-      </c>
-      <c r="D401" t="inlineStr"/>
-      <c r="E401" t="n">
-        <v>8.427</v>
       </c>
     </row>
   </sheetData>
